--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132934601</v>
+        <v>132934612</v>
       </c>
       <c r="B8" t="n">
-        <v>80304</v>
+        <v>92378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>388</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521184</v>
+        <v>521071</v>
       </c>
       <c r="R8" t="n">
-        <v>7009065</v>
+        <v>7009121</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132934572</v>
+        <v>132934601</v>
       </c>
       <c r="B9" t="n">
-        <v>79952</v>
+        <v>80304</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>388</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521188</v>
+        <v>521184</v>
       </c>
       <c r="R9" t="n">
-        <v>7008858</v>
+        <v>7009065</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132934612</v>
+        <v>132934572</v>
       </c>
       <c r="B10" t="n">
-        <v>92378</v>
+        <v>79952</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521071</v>
+        <v>521188</v>
       </c>
       <c r="R10" t="n">
-        <v>7009121</v>
+        <v>7008858</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132934557</v>
+        <v>132934680</v>
       </c>
       <c r="B11" t="n">
-        <v>83181</v>
+        <v>57136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521183</v>
+        <v>521010</v>
       </c>
       <c r="R11" t="n">
-        <v>7009052</v>
+        <v>7008813</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1619,6 +1619,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1st födosökande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132934666</v>
+        <v>132934557</v>
       </c>
       <c r="B13" t="n">
-        <v>79090</v>
+        <v>83181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,34 +1758,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521215</v>
+        <v>521183</v>
       </c>
       <c r="R13" t="n">
-        <v>7008844</v>
+        <v>7009052</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132934547</v>
+        <v>132934666</v>
       </c>
       <c r="B14" t="n">
         <v>79090</v>
@@ -1870,14 +1875,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521140</v>
+        <v>521215</v>
       </c>
       <c r="R14" t="n">
-        <v>7008998</v>
+        <v>7008844</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132934634</v>
+        <v>132934547</v>
       </c>
       <c r="B15" t="n">
-        <v>80438</v>
+        <v>79090</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,34 +1952,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521157</v>
+        <v>521140</v>
       </c>
       <c r="R15" t="n">
-        <v>7008985</v>
+        <v>7008998</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2001,12 +2006,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2033,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132934680</v>
+        <v>132934634</v>
       </c>
       <c r="B16" t="n">
-        <v>57136</v>
+        <v>80438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521010</v>
+        <v>521157</v>
       </c>
       <c r="R16" t="n">
-        <v>7008813</v>
+        <v>7008985</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2098,17 +2103,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1st födosökande</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132934569</v>
+        <v>132934690</v>
       </c>
       <c r="B20" t="n">
-        <v>79952</v>
+        <v>92092</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521055</v>
+        <v>521012</v>
       </c>
       <c r="R20" t="n">
-        <v>7008912</v>
+        <v>7008951</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132934574</v>
+        <v>132934620</v>
       </c>
       <c r="B21" t="n">
-        <v>79952</v>
+        <v>91971</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2534,21 +2534,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521228</v>
+        <v>521239</v>
       </c>
       <c r="R21" t="n">
-        <v>7008805</v>
+        <v>7008816</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132934607</v>
+        <v>132934564</v>
       </c>
       <c r="B22" t="n">
-        <v>80342</v>
+        <v>97370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521198</v>
+        <v>521171</v>
       </c>
       <c r="R22" t="n">
-        <v>7008890</v>
+        <v>7009063</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2717,32 +2717,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132934690</v>
+        <v>132934613</v>
       </c>
       <c r="B23" t="n">
-        <v>92092</v>
+        <v>92217</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1503</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521012</v>
+        <v>521069</v>
       </c>
       <c r="R23" t="n">
-        <v>7008951</v>
+        <v>7009117</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,45 +2814,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132934620</v>
+        <v>132934559</v>
       </c>
       <c r="B24" t="n">
-        <v>91971</v>
+        <v>92192</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521239</v>
+        <v>521072</v>
       </c>
       <c r="R24" t="n">
-        <v>7008816</v>
+        <v>7009164</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,32 +2911,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132934676</v>
+        <v>132934569</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>79952</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521068</v>
+        <v>521055</v>
       </c>
       <c r="R25" t="n">
-        <v>7009134</v>
+        <v>7008912</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2982,11 +2982,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3013,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132934564</v>
+        <v>132934574</v>
       </c>
       <c r="B26" t="n">
-        <v>97370</v>
+        <v>79952</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,21 +3019,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3048,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521171</v>
+        <v>521228</v>
       </c>
       <c r="R26" t="n">
-        <v>7009063</v>
+        <v>7008805</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3078,12 +3073,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3110,32 +3105,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132934613</v>
+        <v>132934607</v>
       </c>
       <c r="B27" t="n">
-        <v>92217</v>
+        <v>80342</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3145,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521069</v>
+        <v>521198</v>
       </c>
       <c r="R27" t="n">
-        <v>7009117</v>
+        <v>7008890</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3207,10 +3202,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132934559</v>
+        <v>132934676</v>
       </c>
       <c r="B28" t="n">
-        <v>92192</v>
+        <v>99130</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3218,34 +3213,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>65</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521072</v>
+        <v>521068</v>
       </c>
       <c r="R28" t="n">
-        <v>7009164</v>
+        <v>7009134</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3278,6 +3273,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3401,45 +3401,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132934673</v>
+        <v>132934517</v>
       </c>
       <c r="B30" t="n">
-        <v>99130</v>
+        <v>92217</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521159</v>
+        <v>521068</v>
       </c>
       <c r="R30" t="n">
-        <v>7008976</v>
+        <v>7009094</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3466,17 +3466,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>12st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3503,32 +3498,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132934679</v>
+        <v>132934598</v>
       </c>
       <c r="B31" t="n">
-        <v>99130</v>
+        <v>80304</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3533,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521159</v>
+        <v>521134</v>
       </c>
       <c r="R31" t="n">
-        <v>7009071</v>
+        <v>7009060</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3568,17 +3563,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>3st bladrosetter</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3587,6 +3577,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3605,10 +3596,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132934517</v>
+        <v>132934534</v>
       </c>
       <c r="B32" t="n">
-        <v>92217</v>
+        <v>80438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3616,21 +3607,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3640,10 +3631,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521068</v>
+        <v>521190</v>
       </c>
       <c r="R32" t="n">
-        <v>7009094</v>
+        <v>7008892</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3676,6 +3667,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På sälghögstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3702,10 +3698,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132934598</v>
+        <v>132934664</v>
       </c>
       <c r="B33" t="n">
-        <v>80304</v>
+        <v>79090</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3713,21 +3709,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>388</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3737,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521134</v>
+        <v>521186</v>
       </c>
       <c r="R33" t="n">
-        <v>7009060</v>
+        <v>7008837</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3767,12 +3763,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3781,7 +3777,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3800,45 +3795,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132934534</v>
+        <v>132934725</v>
       </c>
       <c r="B34" t="n">
-        <v>80438</v>
+        <v>93206</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521190</v>
+        <v>521171</v>
       </c>
       <c r="R34" t="n">
-        <v>7008892</v>
+        <v>7008936</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3871,11 +3866,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På sälghögstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3902,32 +3892,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132934664</v>
+        <v>132934679</v>
       </c>
       <c r="B35" t="n">
-        <v>79090</v>
+        <v>99130</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3937,10 +3927,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521186</v>
+        <v>521159</v>
       </c>
       <c r="R35" t="n">
-        <v>7008837</v>
+        <v>7009071</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3973,6 +3963,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>3st bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3999,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132934725</v>
+        <v>132934673</v>
       </c>
       <c r="B36" t="n">
-        <v>93206</v>
+        <v>99130</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4034,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521171</v>
+        <v>521159</v>
       </c>
       <c r="R36" t="n">
-        <v>7008936</v>
+        <v>7008976</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4064,12 +4059,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>12st bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4096,10 +4096,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132934541</v>
+        <v>132934627</v>
       </c>
       <c r="B37" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4107,34 +4107,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521045</v>
+        <v>521207</v>
       </c>
       <c r="R37" t="n">
-        <v>7008824</v>
+        <v>7008846</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4193,10 +4193,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132934704</v>
+        <v>132934614</v>
       </c>
       <c r="B38" t="n">
-        <v>79333</v>
+        <v>75417</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4204,21 +4204,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1460</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521125</v>
+        <v>521110</v>
       </c>
       <c r="R38" t="n">
-        <v>7009007</v>
+        <v>7009041</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132934642</v>
+        <v>132934585</v>
       </c>
       <c r="B39" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4301,21 +4301,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>521241</v>
+        <v>521047</v>
       </c>
       <c r="R39" t="n">
-        <v>7008806</v>
+        <v>7009108</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4387,45 +4387,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132934606</v>
+        <v>132934510</v>
       </c>
       <c r="B40" t="n">
-        <v>80342</v>
+        <v>91918</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>521194</v>
+        <v>521051</v>
       </c>
       <c r="R40" t="n">
-        <v>7008902</v>
+        <v>7009102</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4484,45 +4484,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132934566</v>
+        <v>132934541</v>
       </c>
       <c r="B41" t="n">
-        <v>91881</v>
+        <v>79090</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521207</v>
+        <v>521045</v>
       </c>
       <c r="R41" t="n">
-        <v>7008851</v>
+        <v>7008824</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4581,10 +4581,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132934614</v>
+        <v>132934704</v>
       </c>
       <c r="B42" t="n">
-        <v>75417</v>
+        <v>79333</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4592,21 +4592,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1460</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521110</v>
+        <v>521125</v>
       </c>
       <c r="R42" t="n">
-        <v>7009041</v>
+        <v>7009007</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132934585</v>
+        <v>132934642</v>
       </c>
       <c r="B43" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4689,21 +4689,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521047</v>
+        <v>521241</v>
       </c>
       <c r="R43" t="n">
-        <v>7009108</v>
+        <v>7008806</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4775,45 +4775,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132934510</v>
+        <v>132934606</v>
       </c>
       <c r="B44" t="n">
-        <v>91918</v>
+        <v>80342</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521051</v>
+        <v>521194</v>
       </c>
       <c r="R44" t="n">
-        <v>7009102</v>
+        <v>7008902</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4872,32 +4872,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132934627</v>
+        <v>132934566</v>
       </c>
       <c r="B45" t="n">
-        <v>79091</v>
+        <v>91881</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4910,7 +4910,7 @@
         <v>521207</v>
       </c>
       <c r="R45" t="n">
-        <v>7008846</v>
+        <v>7008851</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4969,10 +4969,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132934545</v>
+        <v>132934506</v>
       </c>
       <c r="B46" t="n">
-        <v>79090</v>
+        <v>97370</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4980,21 +4980,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>521006</v>
+        <v>521125</v>
       </c>
       <c r="R46" t="n">
-        <v>7009011</v>
+        <v>7009003</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5066,10 +5066,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132934570</v>
+        <v>132934619</v>
       </c>
       <c r="B47" t="n">
-        <v>79952</v>
+        <v>91971</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5077,21 +5077,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520978</v>
+        <v>521192</v>
       </c>
       <c r="R47" t="n">
-        <v>7008880</v>
+        <v>7008832</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5163,45 +5163,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132934565</v>
+        <v>132934545</v>
       </c>
       <c r="B48" t="n">
-        <v>91881</v>
+        <v>79090</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>521199</v>
+        <v>521006</v>
       </c>
       <c r="R48" t="n">
-        <v>7008837</v>
+        <v>7009011</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132934619</v>
+        <v>132934570</v>
       </c>
       <c r="B49" t="n">
-        <v>91971</v>
+        <v>79952</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5271,21 +5271,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>521192</v>
+        <v>520978</v>
       </c>
       <c r="R49" t="n">
-        <v>7008832</v>
+        <v>7008880</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,45 +5357,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132934506</v>
+        <v>132934565</v>
       </c>
       <c r="B50" t="n">
-        <v>97370</v>
+        <v>91881</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>521125</v>
+        <v>521199</v>
       </c>
       <c r="R50" t="n">
-        <v>7009003</v>
+        <v>7008837</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5939,10 +5939,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132934640</v>
+        <v>132934615</v>
       </c>
       <c r="B56" t="n">
-        <v>80438</v>
+        <v>75417</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5950,21 +5950,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>521171</v>
+        <v>521138</v>
       </c>
       <c r="R56" t="n">
-        <v>7009092</v>
+        <v>7008969</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6036,32 +6036,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132934544</v>
+        <v>132934558</v>
       </c>
       <c r="B57" t="n">
-        <v>79090</v>
+        <v>92192</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>65</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6071,10 +6071,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>521030</v>
+        <v>521052</v>
       </c>
       <c r="R57" t="n">
-        <v>7008914</v>
+        <v>7008845</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6133,10 +6133,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132934615</v>
+        <v>132934640</v>
       </c>
       <c r="B58" t="n">
-        <v>75417</v>
+        <v>80438</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6144,21 +6144,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521138</v>
+        <v>521171</v>
       </c>
       <c r="R58" t="n">
-        <v>7008969</v>
+        <v>7009092</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6230,45 +6230,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132934675</v>
+        <v>132934544</v>
       </c>
       <c r="B59" t="n">
-        <v>99130</v>
+        <v>79090</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>521056</v>
+        <v>521030</v>
       </c>
       <c r="R59" t="n">
-        <v>7009075</v>
+        <v>7008914</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6301,11 +6301,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>8st bladrosetter</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6332,32 +6327,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132934626</v>
+        <v>132934675</v>
       </c>
       <c r="B60" t="n">
-        <v>79091</v>
+        <v>99130</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6367,10 +6362,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>521121</v>
+        <v>521056</v>
       </c>
       <c r="R60" t="n">
-        <v>7009153</v>
+        <v>7009075</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6403,6 +6398,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>8st bladrosetter</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6429,7 +6429,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132934532</v>
+        <v>132934626</v>
       </c>
       <c r="B61" t="n">
         <v>79091</v>
@@ -6460,14 +6460,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>521183</v>
+        <v>521121</v>
       </c>
       <c r="R61" t="n">
-        <v>7008817</v>
+        <v>7009153</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6526,32 +6526,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132934558</v>
+        <v>132934532</v>
       </c>
       <c r="B62" t="n">
-        <v>92192</v>
+        <v>79091</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>521052</v>
+        <v>521183</v>
       </c>
       <c r="R62" t="n">
-        <v>7008845</v>
+        <v>7008817</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6623,32 +6623,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132934660</v>
+        <v>132934729</v>
       </c>
       <c r="B63" t="n">
-        <v>91846</v>
+        <v>83307</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2013</v>
+        <v>308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>521085</v>
+        <v>521143</v>
       </c>
       <c r="R63" t="n">
-        <v>7008964</v>
+        <v>7008975</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6694,11 +6694,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6725,32 +6720,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132934670</v>
+        <v>132934660</v>
       </c>
       <c r="B64" t="n">
-        <v>99130</v>
+        <v>91846</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>2013</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6760,10 +6755,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>521175</v>
+        <v>521085</v>
       </c>
       <c r="R64" t="n">
-        <v>7009071</v>
+        <v>7008964</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6790,17 +6785,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>4st bladrosetter</t>
+          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6827,32 +6822,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132934729</v>
+        <v>132934724</v>
       </c>
       <c r="B65" t="n">
-        <v>83307</v>
+        <v>93206</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>308</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6862,10 +6857,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>521143</v>
+        <v>521161</v>
       </c>
       <c r="R65" t="n">
-        <v>7008975</v>
+        <v>7008948</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6892,12 +6887,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6924,32 +6919,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132934724</v>
+        <v>132934709</v>
       </c>
       <c r="B66" t="n">
-        <v>93206</v>
+        <v>79333</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6959,10 +6954,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521161</v>
+        <v>521086</v>
       </c>
       <c r="R66" t="n">
-        <v>7008948</v>
+        <v>7009170</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6989,12 +6984,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7021,10 +7016,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132934709</v>
+        <v>132934633</v>
       </c>
       <c r="B67" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7032,21 +7027,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7056,10 +7051,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521086</v>
+        <v>521131</v>
       </c>
       <c r="R67" t="n">
-        <v>7009170</v>
+        <v>7009066</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7086,12 +7081,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7118,32 +7113,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934633</v>
+        <v>132934602</v>
       </c>
       <c r="B68" t="n">
-        <v>80438</v>
+        <v>80342</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7153,10 +7148,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521131</v>
+        <v>521128</v>
       </c>
       <c r="R68" t="n">
-        <v>7009066</v>
+        <v>7009053</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7215,32 +7210,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132934602</v>
+        <v>132934670</v>
       </c>
       <c r="B69" t="n">
-        <v>80342</v>
+        <v>99130</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7250,10 +7245,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>521128</v>
+        <v>521175</v>
       </c>
       <c r="R69" t="n">
-        <v>7009053</v>
+        <v>7009071</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7286,6 +7281,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7409,10 +7409,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132934542</v>
+        <v>132934526</v>
       </c>
       <c r="B71" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7420,21 +7420,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520944</v>
+        <v>521142</v>
       </c>
       <c r="R71" t="n">
-        <v>7008802</v>
+        <v>7008938</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7506,10 +7506,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132934646</v>
+        <v>132934542</v>
       </c>
       <c r="B72" t="n">
-        <v>80438</v>
+        <v>79090</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7517,34 +7517,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>521053</v>
+        <v>520944</v>
       </c>
       <c r="R72" t="n">
-        <v>7008982</v>
+        <v>7008802</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7603,10 +7603,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132934618</v>
+        <v>132934646</v>
       </c>
       <c r="B73" t="n">
-        <v>91971</v>
+        <v>80438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7614,21 +7614,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520999</v>
+        <v>521053</v>
       </c>
       <c r="R73" t="n">
-        <v>7008967</v>
+        <v>7008982</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7700,10 +7700,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132934526</v>
+        <v>132934618</v>
       </c>
       <c r="B74" t="n">
-        <v>79091</v>
+        <v>91971</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7711,34 +7711,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>521142</v>
+        <v>520999</v>
       </c>
       <c r="R74" t="n">
-        <v>7008938</v>
+        <v>7008967</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7797,32 +7797,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132934671</v>
+        <v>132934702</v>
       </c>
       <c r="B75" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7832,10 +7832,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>521125</v>
+        <v>521069</v>
       </c>
       <c r="R75" t="n">
-        <v>7009063</v>
+        <v>7009122</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7862,17 +7862,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7899,32 +7894,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132934582</v>
+        <v>132934671</v>
       </c>
       <c r="B76" t="n">
-        <v>79923</v>
+        <v>99130</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7934,10 +7929,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>521102</v>
+        <v>521125</v>
       </c>
       <c r="R76" t="n">
-        <v>7009031</v>
+        <v>7009063</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7964,12 +7959,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -7996,10 +7996,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132934528</v>
+        <v>132934582</v>
       </c>
       <c r="B77" t="n">
-        <v>79091</v>
+        <v>79923</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8007,34 +8007,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>521188</v>
+        <v>521102</v>
       </c>
       <c r="R77" t="n">
-        <v>7008858</v>
+        <v>7009031</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8093,7 +8093,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132934629</v>
+        <v>132934528</v>
       </c>
       <c r="B78" t="n">
         <v>79091</v>
@@ -8124,14 +8124,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>521115</v>
+        <v>521188</v>
       </c>
       <c r="R78" t="n">
-        <v>7009027</v>
+        <v>7008858</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8190,10 +8190,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132934702</v>
+        <v>132934629</v>
       </c>
       <c r="B79" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8201,21 +8201,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>521069</v>
+        <v>521115</v>
       </c>
       <c r="R79" t="n">
-        <v>7009122</v>
+        <v>7009027</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8287,10 +8287,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132934599</v>
+        <v>132934703</v>
       </c>
       <c r="B80" t="n">
-        <v>80304</v>
+        <v>79333</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8298,21 +8298,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8322,10 +8322,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>521196</v>
+        <v>521068</v>
       </c>
       <c r="R80" t="n">
-        <v>7008906</v>
+        <v>7009094</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8366,7 +8366,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8385,10 +8384,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132934703</v>
+        <v>132934550</v>
       </c>
       <c r="B81" t="n">
-        <v>79333</v>
+        <v>79090</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8396,34 +8395,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>521068</v>
+        <v>521248</v>
       </c>
       <c r="R81" t="n">
-        <v>7009094</v>
+        <v>7008806</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8482,10 +8481,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132934550</v>
+        <v>132934575</v>
       </c>
       <c r="B82" t="n">
-        <v>79090</v>
+        <v>79952</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8493,34 +8492,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>521248</v>
+        <v>521035</v>
       </c>
       <c r="R82" t="n">
-        <v>7008806</v>
+        <v>7008820</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8579,10 +8578,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132934575</v>
+        <v>132934599</v>
       </c>
       <c r="B83" t="n">
-        <v>79952</v>
+        <v>80304</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8590,21 +8589,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>388</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8614,10 +8613,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>521035</v>
+        <v>521196</v>
       </c>
       <c r="R83" t="n">
-        <v>7008820</v>
+        <v>7008906</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8658,6 +8657,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8676,32 +8676,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132934611</v>
+        <v>132934674</v>
       </c>
       <c r="B84" t="n">
-        <v>80342</v>
+        <v>99130</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>521191</v>
+        <v>521168</v>
       </c>
       <c r="R84" t="n">
-        <v>7008824</v>
+        <v>7009069</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8747,6 +8747,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8773,42 +8778,42 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934641</v>
+        <v>132934552</v>
       </c>
       <c r="B85" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521052</v>
+        <v>521056</v>
       </c>
       <c r="R85" t="n">
         <v>7009135</v>
@@ -8844,6 +8849,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Över 40 plantor</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8870,45 +8880,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132934604</v>
+        <v>132934529</v>
       </c>
       <c r="B86" t="n">
-        <v>80342</v>
+        <v>79091</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>521079</v>
+        <v>521186</v>
       </c>
       <c r="R86" t="n">
-        <v>7008865</v>
+        <v>7008836</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8967,45 +8977,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132934548</v>
+        <v>132934611</v>
       </c>
       <c r="B87" t="n">
-        <v>79090</v>
+        <v>80342</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>521142</v>
+        <v>521191</v>
       </c>
       <c r="R87" t="n">
-        <v>7008938</v>
+        <v>7008824</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9064,45 +9074,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132934514</v>
+        <v>132934641</v>
       </c>
       <c r="B88" t="n">
-        <v>80342</v>
+        <v>80438</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>521008</v>
+        <v>521052</v>
       </c>
       <c r="R88" t="n">
-        <v>7008813</v>
+        <v>7009135</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9161,32 +9171,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132934701</v>
+        <v>132934604</v>
       </c>
       <c r="B89" t="n">
-        <v>79333</v>
+        <v>80342</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9196,10 +9206,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>521075</v>
+        <v>521079</v>
       </c>
       <c r="R89" t="n">
-        <v>7009147</v>
+        <v>7008865</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9258,32 +9268,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132934552</v>
+        <v>132934548</v>
       </c>
       <c r="B90" t="n">
-        <v>99130</v>
+        <v>79090</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9293,10 +9303,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>521056</v>
+        <v>521142</v>
       </c>
       <c r="R90" t="n">
-        <v>7009135</v>
+        <v>7008938</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9329,11 +9339,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Över 40 plantor</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9360,45 +9365,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934674</v>
+        <v>132934514</v>
       </c>
       <c r="B91" t="n">
-        <v>99130</v>
+        <v>80342</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521168</v>
+        <v>521008</v>
       </c>
       <c r="R91" t="n">
-        <v>7009069</v>
+        <v>7008813</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9431,11 +9436,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9462,10 +9462,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934529</v>
+        <v>132934701</v>
       </c>
       <c r="B92" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9473,34 +9473,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521186</v>
+        <v>521075</v>
       </c>
       <c r="R92" t="n">
-        <v>7008836</v>
+        <v>7009147</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9559,32 +9559,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934616</v>
+        <v>132934586</v>
       </c>
       <c r="B93" t="n">
-        <v>79357</v>
+        <v>91918</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6434</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521117</v>
+        <v>521068</v>
       </c>
       <c r="R93" t="n">
-        <v>7009023</v>
+        <v>7009176</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9656,32 +9656,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934586</v>
+        <v>132934616</v>
       </c>
       <c r="B94" t="n">
-        <v>91918</v>
+        <v>79357</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>6434</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9691,10 +9691,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521068</v>
+        <v>521117</v>
       </c>
       <c r="R94" t="n">
-        <v>7009176</v>
+        <v>7009023</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9952,32 +9952,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132934630</v>
+        <v>132934681</v>
       </c>
       <c r="B97" t="n">
-        <v>79091</v>
+        <v>106258</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>221144</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>521203</v>
+        <v>521191</v>
       </c>
       <c r="R97" t="n">
-        <v>7008836</v>
+        <v>7008908</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10049,10 +10049,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132934571</v>
+        <v>132934630</v>
       </c>
       <c r="B98" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10060,21 +10060,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>521202</v>
+        <v>521203</v>
       </c>
       <c r="R98" t="n">
-        <v>7008859</v>
+        <v>7008836</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10146,32 +10146,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132934681</v>
+        <v>132934571</v>
       </c>
       <c r="B99" t="n">
-        <v>106258</v>
+        <v>79952</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>521191</v>
+        <v>521202</v>
       </c>
       <c r="R99" t="n">
-        <v>7008908</v>
+        <v>7008859</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10243,32 +10243,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132934677</v>
+        <v>132934600</v>
       </c>
       <c r="B100" t="n">
-        <v>99130</v>
+        <v>80304</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10278,10 +10278,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>521070</v>
+        <v>521188</v>
       </c>
       <c r="R100" t="n">
-        <v>7009057</v>
+        <v>7008835</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10316,17 +10316,13 @@
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>&gt;30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10345,7 +10341,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132934600</v>
+        <v>132934513</v>
       </c>
       <c r="B101" t="n">
         <v>80304</v>
@@ -10376,14 +10372,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>521188</v>
+        <v>521186</v>
       </c>
       <c r="R101" t="n">
-        <v>7008835</v>
+        <v>7009049</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10424,7 +10420,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -10443,45 +10438,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132934513</v>
+        <v>132934605</v>
       </c>
       <c r="B102" t="n">
-        <v>80304</v>
+        <v>80342</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>388</v>
+        <v>6456</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>521186</v>
+        <v>521000</v>
       </c>
       <c r="R102" t="n">
-        <v>7009049</v>
+        <v>7008814</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10540,10 +10535,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132934605</v>
+        <v>132934728</v>
       </c>
       <c r="B103" t="n">
-        <v>80342</v>
+        <v>80473</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10551,21 +10546,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10575,10 +10570,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>521000</v>
+        <v>521142</v>
       </c>
       <c r="R103" t="n">
-        <v>7008814</v>
+        <v>7008987</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10637,45 +10632,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132934728</v>
+        <v>132934533</v>
       </c>
       <c r="B104" t="n">
-        <v>80473</v>
+        <v>80438</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>521142</v>
+        <v>521124</v>
       </c>
       <c r="R104" t="n">
-        <v>7008987</v>
+        <v>7008989</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10708,6 +10703,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>På låga av sälg</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10734,10 +10734,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132934533</v>
+        <v>132934551</v>
       </c>
       <c r="B105" t="n">
-        <v>80438</v>
+        <v>79090</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10745,21 +10745,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10769,10 +10769,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>521124</v>
+        <v>521211</v>
       </c>
       <c r="R105" t="n">
-        <v>7008989</v>
+        <v>7008824</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10805,11 +10805,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>På låga av sälg</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10836,45 +10831,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132934551</v>
+        <v>132934677</v>
       </c>
       <c r="B106" t="n">
-        <v>79090</v>
+        <v>99130</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>521211</v>
+        <v>521070</v>
       </c>
       <c r="R106" t="n">
-        <v>7008824</v>
+        <v>7009057</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10907,6 +10902,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>&gt;30 bladrosetter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11127,10 +11127,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132934587</v>
+        <v>132934524</v>
       </c>
       <c r="B109" t="n">
-        <v>91918</v>
+        <v>79091</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11138,34 +11138,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>521077</v>
+        <v>521010</v>
       </c>
       <c r="R109" t="n">
-        <v>7009118</v>
+        <v>7008924</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11224,32 +11224,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132934555</v>
+        <v>132934531</v>
       </c>
       <c r="B110" t="n">
-        <v>92092</v>
+        <v>79091</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11259,10 +11259,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>521211</v>
+        <v>521212</v>
       </c>
       <c r="R110" t="n">
-        <v>7008839</v>
+        <v>7008824</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11321,45 +11321,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132934516</v>
+        <v>132934691</v>
       </c>
       <c r="B111" t="n">
-        <v>80342</v>
+        <v>92092</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6456</v>
+        <v>1503</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>521131</v>
+        <v>521092</v>
       </c>
       <c r="R111" t="n">
-        <v>7008987</v>
+        <v>7009170</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11418,32 +11418,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132934609</v>
+        <v>132934587</v>
       </c>
       <c r="B112" t="n">
-        <v>80342</v>
+        <v>91918</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11453,10 +11453,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>521140</v>
+        <v>521077</v>
       </c>
       <c r="R112" t="n">
-        <v>7009061</v>
+        <v>7009118</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11483,12 +11483,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11515,45 +11515,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132934726</v>
+        <v>132934554</v>
       </c>
       <c r="B113" t="n">
-        <v>80473</v>
+        <v>92092</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6463</v>
+        <v>1503</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>521240</v>
+        <v>521105</v>
       </c>
       <c r="R113" t="n">
-        <v>7008810</v>
+        <v>7009010</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11612,7 +11612,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132934691</v>
+        <v>132934555</v>
       </c>
       <c r="B114" t="n">
         <v>92092</v>
@@ -11643,14 +11643,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>521092</v>
+        <v>521211</v>
       </c>
       <c r="R114" t="n">
-        <v>7009170</v>
+        <v>7008839</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11709,32 +11709,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132934554</v>
+        <v>132934516</v>
       </c>
       <c r="B115" t="n">
-        <v>92092</v>
+        <v>80342</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1503</v>
+        <v>6456</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11744,10 +11744,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>521105</v>
+        <v>521131</v>
       </c>
       <c r="R115" t="n">
-        <v>7009010</v>
+        <v>7008987</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11806,45 +11806,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132934524</v>
+        <v>132934609</v>
       </c>
       <c r="B116" t="n">
-        <v>79091</v>
+        <v>80342</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>521010</v>
+        <v>521140</v>
       </c>
       <c r="R116" t="n">
-        <v>7008924</v>
+        <v>7009061</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11871,12 +11871,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -11903,45 +11903,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132934531</v>
+        <v>132934726</v>
       </c>
       <c r="B117" t="n">
-        <v>79091</v>
+        <v>80473</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>521212</v>
+        <v>521240</v>
       </c>
       <c r="R117" t="n">
-        <v>7008824</v>
+        <v>7008810</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132934612</v>
+        <v>132934601</v>
       </c>
       <c r="B8" t="n">
-        <v>92378</v>
+        <v>80304</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>388</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521071</v>
+        <v>521184</v>
       </c>
       <c r="R8" t="n">
-        <v>7009121</v>
+        <v>7009065</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132934601</v>
+        <v>132934572</v>
       </c>
       <c r="B9" t="n">
-        <v>80304</v>
+        <v>79952</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>388</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521184</v>
+        <v>521188</v>
       </c>
       <c r="R9" t="n">
-        <v>7009065</v>
+        <v>7008858</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132934572</v>
+        <v>132934612</v>
       </c>
       <c r="B10" t="n">
-        <v>79952</v>
+        <v>92378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521188</v>
+        <v>521071</v>
       </c>
       <c r="R10" t="n">
-        <v>7008858</v>
+        <v>7009121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132934680</v>
+        <v>132934666</v>
       </c>
       <c r="B11" t="n">
-        <v>57136</v>
+        <v>79090</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521010</v>
+        <v>521215</v>
       </c>
       <c r="R11" t="n">
-        <v>7008813</v>
+        <v>7008844</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1619,11 +1619,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1st födosökande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1650,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132934525</v>
+        <v>132934547</v>
       </c>
       <c r="B12" t="n">
-        <v>79091</v>
+        <v>79090</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521152</v>
+        <v>521140</v>
       </c>
       <c r="R12" t="n">
-        <v>7008946</v>
+        <v>7008998</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132934557</v>
+        <v>132934634</v>
       </c>
       <c r="B13" t="n">
-        <v>83181</v>
+        <v>80438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,34 +1753,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521183</v>
+        <v>521157</v>
       </c>
       <c r="R13" t="n">
-        <v>7009052</v>
+        <v>7008985</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1812,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1844,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132934666</v>
+        <v>132934680</v>
       </c>
       <c r="B14" t="n">
-        <v>79090</v>
+        <v>57136</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521215</v>
+        <v>521010</v>
       </c>
       <c r="R14" t="n">
-        <v>7008844</v>
+        <v>7008813</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1915,6 +1910,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1st födosökande</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132934547</v>
+        <v>132934525</v>
       </c>
       <c r="B15" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521140</v>
+        <v>521152</v>
       </c>
       <c r="R15" t="n">
-        <v>7008998</v>
+        <v>7008946</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132934634</v>
+        <v>132934557</v>
       </c>
       <c r="B16" t="n">
-        <v>80438</v>
+        <v>83181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,34 +2049,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521157</v>
+        <v>521183</v>
       </c>
       <c r="R16" t="n">
-        <v>7008985</v>
+        <v>7009052</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2426,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132934690</v>
+        <v>132934676</v>
       </c>
       <c r="B20" t="n">
-        <v>92092</v>
+        <v>99130</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521012</v>
+        <v>521068</v>
       </c>
       <c r="R20" t="n">
-        <v>7008951</v>
+        <v>7009134</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2497,6 +2497,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2523,10 +2528,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132934620</v>
+        <v>132934564</v>
       </c>
       <c r="B21" t="n">
-        <v>91971</v>
+        <v>97370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2534,21 +2539,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2079</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521239</v>
+        <v>521171</v>
       </c>
       <c r="R21" t="n">
-        <v>7008816</v>
+        <v>7009063</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2588,12 +2593,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2620,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132934564</v>
+        <v>132934613</v>
       </c>
       <c r="B22" t="n">
-        <v>97370</v>
+        <v>92217</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2631,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521171</v>
+        <v>521069</v>
       </c>
       <c r="R22" t="n">
-        <v>7009063</v>
+        <v>7009117</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,12 +2690,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2717,45 +2722,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132934613</v>
+        <v>132934559</v>
       </c>
       <c r="B23" t="n">
-        <v>92217</v>
+        <v>92192</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>65</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521069</v>
+        <v>521072</v>
       </c>
       <c r="R23" t="n">
-        <v>7009117</v>
+        <v>7009164</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132934559</v>
+        <v>132934690</v>
       </c>
       <c r="B24" t="n">
-        <v>92192</v>
+        <v>92092</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2825,34 +2830,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521072</v>
+        <v>521012</v>
       </c>
       <c r="R24" t="n">
-        <v>7009164</v>
+        <v>7008951</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,10 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132934569</v>
+        <v>132934620</v>
       </c>
       <c r="B25" t="n">
-        <v>79952</v>
+        <v>91971</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,21 +2927,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521055</v>
+        <v>521239</v>
       </c>
       <c r="R25" t="n">
-        <v>7008912</v>
+        <v>7008816</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,32 +3207,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132934676</v>
+        <v>132934569</v>
       </c>
       <c r="B28" t="n">
-        <v>99130</v>
+        <v>79952</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3237,10 +3242,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521068</v>
+        <v>521055</v>
       </c>
       <c r="R28" t="n">
-        <v>7009134</v>
+        <v>7008912</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3273,11 +3278,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3304,32 +3304,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132934588</v>
+        <v>132934673</v>
       </c>
       <c r="B29" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521065</v>
+        <v>521159</v>
       </c>
       <c r="R29" t="n">
-        <v>7009134</v>
+        <v>7008976</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3369,12 +3369,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>12st bladrosetter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3401,45 +3406,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132934517</v>
+        <v>132934679</v>
       </c>
       <c r="B30" t="n">
-        <v>92217</v>
+        <v>99130</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521068</v>
+        <v>521159</v>
       </c>
       <c r="R30" t="n">
-        <v>7009094</v>
+        <v>7009071</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3472,6 +3477,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>3st bladrosetter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3498,10 +3508,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132934598</v>
+        <v>132934588</v>
       </c>
       <c r="B31" t="n">
-        <v>80304</v>
+        <v>91918</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3509,21 +3519,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>388</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3533,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521134</v>
+        <v>521065</v>
       </c>
       <c r="R31" t="n">
-        <v>7009060</v>
+        <v>7009134</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3563,12 +3573,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3577,7 +3587,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3596,10 +3605,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132934534</v>
+        <v>132934517</v>
       </c>
       <c r="B32" t="n">
-        <v>80438</v>
+        <v>92217</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3607,21 +3616,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3631,10 +3640,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521190</v>
+        <v>521068</v>
       </c>
       <c r="R32" t="n">
-        <v>7008892</v>
+        <v>7009094</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3667,11 +3676,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På sälghögstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3698,10 +3702,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132934664</v>
+        <v>132934598</v>
       </c>
       <c r="B33" t="n">
-        <v>79090</v>
+        <v>80304</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3709,21 +3713,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>388</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3733,10 +3737,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521186</v>
+        <v>521134</v>
       </c>
       <c r="R33" t="n">
-        <v>7008837</v>
+        <v>7009060</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3763,12 +3767,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3777,6 +3781,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3892,45 +3897,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132934679</v>
+        <v>132934534</v>
       </c>
       <c r="B35" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521159</v>
+        <v>521190</v>
       </c>
       <c r="R35" t="n">
-        <v>7009071</v>
+        <v>7008892</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3967,7 +3972,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>3st bladrosetter</t>
+          <t>På sälghögstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3994,32 +3999,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132934673</v>
+        <v>132934664</v>
       </c>
       <c r="B36" t="n">
-        <v>99130</v>
+        <v>79090</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4034,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521159</v>
+        <v>521186</v>
       </c>
       <c r="R36" t="n">
-        <v>7008976</v>
+        <v>7008837</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4059,17 +4064,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>12st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4096,10 +4096,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132934627</v>
+        <v>132934585</v>
       </c>
       <c r="B37" t="n">
-        <v>79091</v>
+        <v>91918</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4107,21 +4107,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4131,10 +4131,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521207</v>
+        <v>521047</v>
       </c>
       <c r="R37" t="n">
-        <v>7008846</v>
+        <v>7009108</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4193,10 +4193,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132934614</v>
+        <v>132934510</v>
       </c>
       <c r="B38" t="n">
-        <v>75417</v>
+        <v>91918</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4204,34 +4204,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521110</v>
+        <v>521051</v>
       </c>
       <c r="R38" t="n">
-        <v>7009041</v>
+        <v>7009102</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132934585</v>
+        <v>132934614</v>
       </c>
       <c r="B39" t="n">
-        <v>91918</v>
+        <v>75417</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4301,21 +4301,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>1460</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>521047</v>
+        <v>521110</v>
       </c>
       <c r="R39" t="n">
-        <v>7009108</v>
+        <v>7009041</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4387,10 +4387,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132934510</v>
+        <v>132934541</v>
       </c>
       <c r="B40" t="n">
-        <v>91918</v>
+        <v>79090</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4398,21 +4398,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>521051</v>
+        <v>521045</v>
       </c>
       <c r="R40" t="n">
-        <v>7009102</v>
+        <v>7008824</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132934541</v>
+        <v>132934704</v>
       </c>
       <c r="B41" t="n">
-        <v>79090</v>
+        <v>79333</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4495,34 +4495,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521045</v>
+        <v>521125</v>
       </c>
       <c r="R41" t="n">
-        <v>7008824</v>
+        <v>7009007</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4581,10 +4581,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132934704</v>
+        <v>132934642</v>
       </c>
       <c r="B42" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4592,21 +4592,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521125</v>
+        <v>521241</v>
       </c>
       <c r="R42" t="n">
-        <v>7009007</v>
+        <v>7008806</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4678,32 +4678,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132934642</v>
+        <v>132934606</v>
       </c>
       <c r="B43" t="n">
-        <v>80438</v>
+        <v>80342</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521241</v>
+        <v>521194</v>
       </c>
       <c r="R43" t="n">
-        <v>7008806</v>
+        <v>7008902</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4775,10 +4775,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132934606</v>
+        <v>132934566</v>
       </c>
       <c r="B44" t="n">
-        <v>80342</v>
+        <v>91881</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4786,21 +4786,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521194</v>
+        <v>521207</v>
       </c>
       <c r="R44" t="n">
-        <v>7008902</v>
+        <v>7008851</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4872,32 +4872,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132934566</v>
+        <v>132934627</v>
       </c>
       <c r="B45" t="n">
-        <v>91881</v>
+        <v>79091</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4910,7 +4910,7 @@
         <v>521207</v>
       </c>
       <c r="R45" t="n">
-        <v>7008851</v>
+        <v>7008846</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4969,10 +4969,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132934506</v>
+        <v>132934619</v>
       </c>
       <c r="B46" t="n">
-        <v>97370</v>
+        <v>91971</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4980,34 +4980,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>2079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>521125</v>
+        <v>521192</v>
       </c>
       <c r="R46" t="n">
-        <v>7009003</v>
+        <v>7008832</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5066,10 +5066,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132934619</v>
+        <v>132934545</v>
       </c>
       <c r="B47" t="n">
-        <v>91971</v>
+        <v>79090</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5077,34 +5077,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>521192</v>
+        <v>521006</v>
       </c>
       <c r="R47" t="n">
-        <v>7008832</v>
+        <v>7009011</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5163,10 +5163,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132934545</v>
+        <v>132934570</v>
       </c>
       <c r="B48" t="n">
-        <v>79090</v>
+        <v>79952</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5174,34 +5174,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>521006</v>
+        <v>520978</v>
       </c>
       <c r="R48" t="n">
-        <v>7009011</v>
+        <v>7008880</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,32 +5260,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132934570</v>
+        <v>132934565</v>
       </c>
       <c r="B49" t="n">
-        <v>79952</v>
+        <v>91881</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>520978</v>
+        <v>521199</v>
       </c>
       <c r="R49" t="n">
-        <v>7008880</v>
+        <v>7008837</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,45 +5357,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132934565</v>
+        <v>132934506</v>
       </c>
       <c r="B50" t="n">
-        <v>91881</v>
+        <v>97370</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>521199</v>
+        <v>521125</v>
       </c>
       <c r="R50" t="n">
-        <v>7008837</v>
+        <v>7009003</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5939,45 +5939,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132934615</v>
+        <v>132934558</v>
       </c>
       <c r="B56" t="n">
-        <v>75417</v>
+        <v>92192</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1460</v>
+        <v>65</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>521138</v>
+        <v>521052</v>
       </c>
       <c r="R56" t="n">
-        <v>7008969</v>
+        <v>7008845</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6036,45 +6036,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132934558</v>
+        <v>132934615</v>
       </c>
       <c r="B57" t="n">
-        <v>92192</v>
+        <v>75417</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>65</v>
+        <v>1460</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>521052</v>
+        <v>521138</v>
       </c>
       <c r="R57" t="n">
-        <v>7008845</v>
+        <v>7008969</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6133,32 +6133,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132934640</v>
+        <v>132934675</v>
       </c>
       <c r="B58" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521171</v>
+        <v>521056</v>
       </c>
       <c r="R58" t="n">
-        <v>7009092</v>
+        <v>7009075</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6204,6 +6204,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>8st bladrosetter</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6230,10 +6235,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132934544</v>
+        <v>132934640</v>
       </c>
       <c r="B59" t="n">
-        <v>79090</v>
+        <v>80438</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6241,34 +6246,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>521030</v>
+        <v>521171</v>
       </c>
       <c r="R59" t="n">
-        <v>7008914</v>
+        <v>7009092</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6327,45 +6332,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132934675</v>
+        <v>132934544</v>
       </c>
       <c r="B60" t="n">
-        <v>99130</v>
+        <v>79090</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>521056</v>
+        <v>521030</v>
       </c>
       <c r="R60" t="n">
-        <v>7009075</v>
+        <v>7008914</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6398,11 +6403,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>8st bladrosetter</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6429,7 +6429,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132934626</v>
+        <v>132934532</v>
       </c>
       <c r="B61" t="n">
         <v>79091</v>
@@ -6460,14 +6460,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>521121</v>
+        <v>521183</v>
       </c>
       <c r="R61" t="n">
-        <v>7009153</v>
+        <v>7008817</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6526,7 +6526,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132934532</v>
+        <v>132934626</v>
       </c>
       <c r="B62" t="n">
         <v>79091</v>
@@ -6557,14 +6557,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>521183</v>
+        <v>521121</v>
       </c>
       <c r="R62" t="n">
-        <v>7008817</v>
+        <v>7009153</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6623,32 +6623,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132934729</v>
+        <v>132934724</v>
       </c>
       <c r="B63" t="n">
-        <v>83307</v>
+        <v>93206</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>308</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>521143</v>
+        <v>521161</v>
       </c>
       <c r="R63" t="n">
-        <v>7008975</v>
+        <v>7008948</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6720,32 +6720,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132934660</v>
+        <v>132934709</v>
       </c>
       <c r="B64" t="n">
-        <v>91846</v>
+        <v>79333</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2013</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>521085</v>
+        <v>521086</v>
       </c>
       <c r="R64" t="n">
-        <v>7008964</v>
+        <v>7009170</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6791,11 +6791,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6822,32 +6817,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132934724</v>
+        <v>132934633</v>
       </c>
       <c r="B65" t="n">
-        <v>93206</v>
+        <v>80438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6857,10 +6852,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>521161</v>
+        <v>521131</v>
       </c>
       <c r="R65" t="n">
-        <v>7008948</v>
+        <v>7009066</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6919,32 +6914,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132934709</v>
+        <v>132934602</v>
       </c>
       <c r="B66" t="n">
-        <v>79333</v>
+        <v>80342</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6954,10 +6949,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521086</v>
+        <v>521128</v>
       </c>
       <c r="R66" t="n">
-        <v>7009170</v>
+        <v>7009053</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6984,12 +6979,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7016,10 +7011,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132934633</v>
+        <v>132934729</v>
       </c>
       <c r="B67" t="n">
-        <v>80438</v>
+        <v>83307</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7027,21 +7022,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7051,10 +7046,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521131</v>
+        <v>521143</v>
       </c>
       <c r="R67" t="n">
-        <v>7009066</v>
+        <v>7008975</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7081,12 +7076,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7113,32 +7108,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934602</v>
+        <v>132934660</v>
       </c>
       <c r="B68" t="n">
-        <v>80342</v>
+        <v>91846</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6456</v>
+        <v>2013</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7148,10 +7143,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521128</v>
+        <v>521085</v>
       </c>
       <c r="R68" t="n">
-        <v>7009053</v>
+        <v>7008964</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7178,12 +7173,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7210,45 +7210,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132934670</v>
+        <v>132934522</v>
       </c>
       <c r="B69" t="n">
-        <v>99130</v>
+        <v>79091</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>521175</v>
+        <v>520949</v>
       </c>
       <c r="R69" t="n">
-        <v>7009071</v>
+        <v>7008801</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7275,17 +7275,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>4st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7312,45 +7307,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132934522</v>
+        <v>132934670</v>
       </c>
       <c r="B70" t="n">
-        <v>79091</v>
+        <v>99130</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520949</v>
+        <v>521175</v>
       </c>
       <c r="R70" t="n">
-        <v>7008801</v>
+        <v>7009071</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7377,12 +7372,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7506,10 +7506,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132934542</v>
+        <v>132934618</v>
       </c>
       <c r="B72" t="n">
-        <v>79090</v>
+        <v>91971</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7517,34 +7517,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520944</v>
+        <v>520999</v>
       </c>
       <c r="R72" t="n">
-        <v>7008802</v>
+        <v>7008967</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7603,10 +7603,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132934646</v>
+        <v>132934542</v>
       </c>
       <c r="B73" t="n">
-        <v>80438</v>
+        <v>79090</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7614,34 +7614,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>521053</v>
+        <v>520944</v>
       </c>
       <c r="R73" t="n">
-        <v>7008982</v>
+        <v>7008802</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7700,10 +7700,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132934618</v>
+        <v>132934646</v>
       </c>
       <c r="B74" t="n">
-        <v>91971</v>
+        <v>80438</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7711,21 +7711,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520999</v>
+        <v>521053</v>
       </c>
       <c r="R74" t="n">
-        <v>7008967</v>
+        <v>7008982</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7797,10 +7797,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132934702</v>
+        <v>132934528</v>
       </c>
       <c r="B75" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7808,34 +7808,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>521069</v>
+        <v>521188</v>
       </c>
       <c r="R75" t="n">
-        <v>7009122</v>
+        <v>7008858</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7894,32 +7894,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132934671</v>
+        <v>132934582</v>
       </c>
       <c r="B76" t="n">
-        <v>99130</v>
+        <v>79923</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>521125</v>
+        <v>521102</v>
       </c>
       <c r="R76" t="n">
-        <v>7009063</v>
+        <v>7009031</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7959,17 +7959,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -7996,10 +7991,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132934582</v>
+        <v>132934702</v>
       </c>
       <c r="B77" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8007,21 +8002,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8031,10 +8026,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>521102</v>
+        <v>521069</v>
       </c>
       <c r="R77" t="n">
-        <v>7009031</v>
+        <v>7009122</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8093,45 +8088,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132934528</v>
+        <v>132934671</v>
       </c>
       <c r="B78" t="n">
-        <v>79091</v>
+        <v>99130</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>521188</v>
+        <v>521125</v>
       </c>
       <c r="R78" t="n">
-        <v>7008858</v>
+        <v>7009063</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8158,12 +8153,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8676,32 +8676,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132934674</v>
+        <v>132934611</v>
       </c>
       <c r="B84" t="n">
-        <v>99130</v>
+        <v>80342</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>521168</v>
+        <v>521191</v>
       </c>
       <c r="R84" t="n">
-        <v>7009069</v>
+        <v>7008824</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8747,11 +8747,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8778,42 +8773,42 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934552</v>
+        <v>132934641</v>
       </c>
       <c r="B85" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521056</v>
+        <v>521052</v>
       </c>
       <c r="R85" t="n">
         <v>7009135</v>
@@ -8849,11 +8844,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Över 40 plantor</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8880,45 +8870,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132934529</v>
+        <v>132934604</v>
       </c>
       <c r="B86" t="n">
-        <v>79091</v>
+        <v>80342</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>521186</v>
+        <v>521079</v>
       </c>
       <c r="R86" t="n">
-        <v>7008836</v>
+        <v>7008865</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8977,45 +8967,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132934611</v>
+        <v>132934548</v>
       </c>
       <c r="B87" t="n">
-        <v>80342</v>
+        <v>79090</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>521191</v>
+        <v>521142</v>
       </c>
       <c r="R87" t="n">
-        <v>7008824</v>
+        <v>7008938</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9074,45 +9064,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132934641</v>
+        <v>132934514</v>
       </c>
       <c r="B88" t="n">
-        <v>80438</v>
+        <v>80342</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>521052</v>
+        <v>521008</v>
       </c>
       <c r="R88" t="n">
-        <v>7009135</v>
+        <v>7008813</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9171,32 +9161,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132934604</v>
+        <v>132934701</v>
       </c>
       <c r="B89" t="n">
-        <v>80342</v>
+        <v>79333</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9206,10 +9196,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>521079</v>
+        <v>521075</v>
       </c>
       <c r="R89" t="n">
-        <v>7008865</v>
+        <v>7009147</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9268,10 +9258,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132934548</v>
+        <v>132934529</v>
       </c>
       <c r="B90" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9279,21 +9269,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9303,10 +9293,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>521142</v>
+        <v>521186</v>
       </c>
       <c r="R90" t="n">
-        <v>7008938</v>
+        <v>7008836</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9365,32 +9355,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934514</v>
+        <v>132934552</v>
       </c>
       <c r="B91" t="n">
-        <v>80342</v>
+        <v>99130</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9400,10 +9390,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521008</v>
+        <v>521056</v>
       </c>
       <c r="R91" t="n">
-        <v>7008813</v>
+        <v>7009135</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9436,6 +9426,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Över 40 plantor</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9462,32 +9457,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934701</v>
+        <v>132934674</v>
       </c>
       <c r="B92" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9497,10 +9492,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521075</v>
+        <v>521168</v>
       </c>
       <c r="R92" t="n">
-        <v>7009147</v>
+        <v>7009069</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9533,6 +9528,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9559,10 +9559,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934586</v>
+        <v>132934530</v>
       </c>
       <c r="B93" t="n">
-        <v>91918</v>
+        <v>79091</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9570,34 +9570,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521068</v>
+        <v>521248</v>
       </c>
       <c r="R93" t="n">
-        <v>7009176</v>
+        <v>7008805</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9656,32 +9656,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934616</v>
+        <v>132934586</v>
       </c>
       <c r="B94" t="n">
-        <v>79357</v>
+        <v>91918</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6434</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9691,10 +9691,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521117</v>
+        <v>521068</v>
       </c>
       <c r="R94" t="n">
-        <v>7009023</v>
+        <v>7009176</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9753,32 +9753,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132934678</v>
+        <v>132934616</v>
       </c>
       <c r="B95" t="n">
-        <v>99130</v>
+        <v>79357</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9788,10 +9788,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521234</v>
+        <v>521117</v>
       </c>
       <c r="R95" t="n">
-        <v>7009077</v>
+        <v>7009023</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9824,11 +9824,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9855,45 +9850,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132934530</v>
+        <v>132934678</v>
       </c>
       <c r="B96" t="n">
-        <v>79091</v>
+        <v>99130</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521248</v>
+        <v>521234</v>
       </c>
       <c r="R96" t="n">
-        <v>7008805</v>
+        <v>7009077</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9926,6 +9921,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -9952,32 +9952,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132934681</v>
+        <v>132934571</v>
       </c>
       <c r="B97" t="n">
-        <v>106258</v>
+        <v>79952</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>521191</v>
+        <v>521202</v>
       </c>
       <c r="R97" t="n">
-        <v>7008908</v>
+        <v>7008859</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10049,32 +10049,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132934630</v>
+        <v>132934681</v>
       </c>
       <c r="B98" t="n">
-        <v>79091</v>
+        <v>106258</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>221144</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>521203</v>
+        <v>521191</v>
       </c>
       <c r="R98" t="n">
-        <v>7008836</v>
+        <v>7008908</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10146,10 +10146,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132934571</v>
+        <v>132934630</v>
       </c>
       <c r="B99" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10157,21 +10157,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>521202</v>
+        <v>521203</v>
       </c>
       <c r="R99" t="n">
-        <v>7008859</v>
+        <v>7008836</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11127,10 +11127,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132934524</v>
+        <v>132934587</v>
       </c>
       <c r="B109" t="n">
-        <v>79091</v>
+        <v>91918</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11138,34 +11138,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>521010</v>
+        <v>521077</v>
       </c>
       <c r="R109" t="n">
-        <v>7008924</v>
+        <v>7009118</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11224,45 +11224,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132934531</v>
+        <v>132934691</v>
       </c>
       <c r="B110" t="n">
-        <v>79091</v>
+        <v>92092</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>521212</v>
+        <v>521092</v>
       </c>
       <c r="R110" t="n">
-        <v>7008824</v>
+        <v>7009170</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11321,7 +11321,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132934691</v>
+        <v>132934554</v>
       </c>
       <c r="B111" t="n">
         <v>92092</v>
@@ -11352,14 +11352,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>521092</v>
+        <v>521105</v>
       </c>
       <c r="R111" t="n">
-        <v>7009170</v>
+        <v>7009010</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11418,45 +11418,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132934587</v>
+        <v>132934555</v>
       </c>
       <c r="B112" t="n">
-        <v>91918</v>
+        <v>92092</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>1503</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>521077</v>
+        <v>521211</v>
       </c>
       <c r="R112" t="n">
-        <v>7009118</v>
+        <v>7008839</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11515,32 +11515,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132934554</v>
+        <v>132934516</v>
       </c>
       <c r="B113" t="n">
-        <v>92092</v>
+        <v>80342</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1503</v>
+        <v>6456</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11550,10 +11550,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>521105</v>
+        <v>521131</v>
       </c>
       <c r="R113" t="n">
-        <v>7009010</v>
+        <v>7008987</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11612,45 +11612,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132934555</v>
+        <v>132934609</v>
       </c>
       <c r="B114" t="n">
-        <v>92092</v>
+        <v>80342</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1503</v>
+        <v>6456</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>521211</v>
+        <v>521140</v>
       </c>
       <c r="R114" t="n">
-        <v>7008839</v>
+        <v>7009061</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11677,12 +11677,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11709,10 +11709,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132934516</v>
+        <v>132934726</v>
       </c>
       <c r="B115" t="n">
-        <v>80342</v>
+        <v>80473</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11720,34 +11720,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>521131</v>
+        <v>521240</v>
       </c>
       <c r="R115" t="n">
-        <v>7008987</v>
+        <v>7008810</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11806,45 +11806,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132934609</v>
+        <v>132934524</v>
       </c>
       <c r="B116" t="n">
-        <v>80342</v>
+        <v>79091</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>521140</v>
+        <v>521010</v>
       </c>
       <c r="R116" t="n">
-        <v>7009061</v>
+        <v>7008924</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11871,12 +11871,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -11903,45 +11903,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132934726</v>
+        <v>132934531</v>
       </c>
       <c r="B117" t="n">
-        <v>80473</v>
+        <v>79091</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>521240</v>
+        <v>521212</v>
       </c>
       <c r="R117" t="n">
-        <v>7008810</v>
+        <v>7008824</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132934601</v>
+        <v>132934612</v>
       </c>
       <c r="B8" t="n">
-        <v>80304</v>
+        <v>92378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>388</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521184</v>
+        <v>521071</v>
       </c>
       <c r="R8" t="n">
-        <v>7009065</v>
+        <v>7009121</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132934572</v>
+        <v>132934601</v>
       </c>
       <c r="B9" t="n">
-        <v>79952</v>
+        <v>80304</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>388</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521188</v>
+        <v>521184</v>
       </c>
       <c r="R9" t="n">
-        <v>7008858</v>
+        <v>7009065</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132934612</v>
+        <v>132934572</v>
       </c>
       <c r="B10" t="n">
-        <v>92378</v>
+        <v>79952</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521071</v>
+        <v>521188</v>
       </c>
       <c r="R10" t="n">
-        <v>7009121</v>
+        <v>7008858</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132934666</v>
+        <v>132934557</v>
       </c>
       <c r="B11" t="n">
-        <v>79090</v>
+        <v>83181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521215</v>
+        <v>521183</v>
       </c>
       <c r="R11" t="n">
-        <v>7008844</v>
+        <v>7009052</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132934547</v>
+        <v>132934680</v>
       </c>
       <c r="B12" t="n">
-        <v>79090</v>
+        <v>57136</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,34 +1656,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521140</v>
+        <v>521010</v>
       </c>
       <c r="R12" t="n">
-        <v>7008998</v>
+        <v>7008813</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1716,6 +1716,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1st födosökande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1742,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132934634</v>
+        <v>132934666</v>
       </c>
       <c r="B13" t="n">
-        <v>80438</v>
+        <v>79090</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521157</v>
+        <v>521215</v>
       </c>
       <c r="R13" t="n">
-        <v>7008985</v>
+        <v>7008844</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1807,12 +1812,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1839,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132934680</v>
+        <v>132934547</v>
       </c>
       <c r="B14" t="n">
-        <v>57136</v>
+        <v>79090</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,34 +1855,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521010</v>
+        <v>521140</v>
       </c>
       <c r="R14" t="n">
-        <v>7008813</v>
+        <v>7008998</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1910,11 +1915,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1st födosökande</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132934525</v>
+        <v>132934634</v>
       </c>
       <c r="B15" t="n">
-        <v>79091</v>
+        <v>80438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,34 +1952,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521152</v>
+        <v>521157</v>
       </c>
       <c r="R15" t="n">
-        <v>7008946</v>
+        <v>7008985</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132934557</v>
+        <v>132934525</v>
       </c>
       <c r="B16" t="n">
-        <v>83181</v>
+        <v>79091</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521183</v>
+        <v>521152</v>
       </c>
       <c r="R16" t="n">
-        <v>7009052</v>
+        <v>7008946</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132934676</v>
+        <v>132934613</v>
       </c>
       <c r="B20" t="n">
-        <v>99130</v>
+        <v>92217</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521068</v>
+        <v>521069</v>
       </c>
       <c r="R20" t="n">
-        <v>7009134</v>
+        <v>7009117</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2497,11 +2497,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2625,45 +2620,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132934613</v>
+        <v>132934559</v>
       </c>
       <c r="B22" t="n">
-        <v>92217</v>
+        <v>92192</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>65</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521069</v>
+        <v>521072</v>
       </c>
       <c r="R22" t="n">
-        <v>7009117</v>
+        <v>7009164</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2722,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132934559</v>
+        <v>132934690</v>
       </c>
       <c r="B23" t="n">
-        <v>92192</v>
+        <v>92092</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,34 +2728,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>65</v>
+        <v>1503</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521072</v>
+        <v>521012</v>
       </c>
       <c r="R23" t="n">
-        <v>7009164</v>
+        <v>7008951</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2819,32 +2814,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132934690</v>
+        <v>132934620</v>
       </c>
       <c r="B24" t="n">
-        <v>92092</v>
+        <v>91971</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521012</v>
+        <v>521239</v>
       </c>
       <c r="R24" t="n">
-        <v>7008951</v>
+        <v>7008816</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132934620</v>
+        <v>132934569</v>
       </c>
       <c r="B25" t="n">
-        <v>91971</v>
+        <v>79952</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2927,21 +2922,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2951,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521239</v>
+        <v>521055</v>
       </c>
       <c r="R25" t="n">
-        <v>7008816</v>
+        <v>7008912</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3207,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132934569</v>
+        <v>132934676</v>
       </c>
       <c r="B28" t="n">
-        <v>79952</v>
+        <v>99130</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3242,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521055</v>
+        <v>521068</v>
       </c>
       <c r="R28" t="n">
-        <v>7008912</v>
+        <v>7009134</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3278,6 +3273,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3304,32 +3304,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132934673</v>
+        <v>132934588</v>
       </c>
       <c r="B29" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521159</v>
+        <v>521065</v>
       </c>
       <c r="R29" t="n">
-        <v>7008976</v>
+        <v>7009134</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3369,17 +3369,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>12st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3406,32 +3401,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132934679</v>
+        <v>132934598</v>
       </c>
       <c r="B30" t="n">
-        <v>99130</v>
+        <v>80304</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3436,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521159</v>
+        <v>521134</v>
       </c>
       <c r="R30" t="n">
-        <v>7009071</v>
+        <v>7009060</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3471,17 +3466,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>3st bladrosetter</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3490,6 +3480,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3508,10 +3499,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132934588</v>
+        <v>132934517</v>
       </c>
       <c r="B31" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3519,34 +3510,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521065</v>
+        <v>521068</v>
       </c>
       <c r="R31" t="n">
-        <v>7009134</v>
+        <v>7009094</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3605,10 +3596,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132934517</v>
+        <v>132934534</v>
       </c>
       <c r="B32" t="n">
-        <v>92217</v>
+        <v>80438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3616,21 +3607,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3640,10 +3631,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521068</v>
+        <v>521190</v>
       </c>
       <c r="R32" t="n">
-        <v>7009094</v>
+        <v>7008892</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3676,6 +3667,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På sälghögstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3702,10 +3698,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132934598</v>
+        <v>132934664</v>
       </c>
       <c r="B33" t="n">
-        <v>80304</v>
+        <v>79090</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3713,21 +3709,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>388</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3737,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521134</v>
+        <v>521186</v>
       </c>
       <c r="R33" t="n">
-        <v>7009060</v>
+        <v>7008837</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3767,12 +3763,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3781,7 +3777,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3897,45 +3892,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132934534</v>
+        <v>132934673</v>
       </c>
       <c r="B35" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521190</v>
+        <v>521159</v>
       </c>
       <c r="R35" t="n">
-        <v>7008892</v>
+        <v>7008976</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3962,17 +3957,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På sälghögstubbe</t>
+          <t>12st bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3999,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132934664</v>
+        <v>132934679</v>
       </c>
       <c r="B36" t="n">
-        <v>79090</v>
+        <v>99130</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4034,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521186</v>
+        <v>521159</v>
       </c>
       <c r="R36" t="n">
-        <v>7008837</v>
+        <v>7009071</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4070,6 +4065,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>3st bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4096,7 +4096,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132934585</v>
+        <v>132934510</v>
       </c>
       <c r="B37" t="n">
         <v>91918</v>
@@ -4127,14 +4127,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521047</v>
+        <v>521051</v>
       </c>
       <c r="R37" t="n">
-        <v>7009108</v>
+        <v>7009102</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4193,7 +4193,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132934510</v>
+        <v>132934585</v>
       </c>
       <c r="B38" t="n">
         <v>91918</v>
@@ -4224,14 +4224,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521051</v>
+        <v>521047</v>
       </c>
       <c r="R38" t="n">
-        <v>7009102</v>
+        <v>7009108</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132934614</v>
+        <v>132934541</v>
       </c>
       <c r="B39" t="n">
-        <v>75417</v>
+        <v>79090</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4301,34 +4301,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1460</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>521110</v>
+        <v>521045</v>
       </c>
       <c r="R39" t="n">
-        <v>7009041</v>
+        <v>7008824</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4387,10 +4387,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132934541</v>
+        <v>132934614</v>
       </c>
       <c r="B40" t="n">
-        <v>79090</v>
+        <v>75417</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4398,34 +4398,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>1460</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>521045</v>
+        <v>521110</v>
       </c>
       <c r="R40" t="n">
-        <v>7008824</v>
+        <v>7009041</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4969,10 +4969,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132934619</v>
+        <v>132934506</v>
       </c>
       <c r="B46" t="n">
-        <v>91971</v>
+        <v>97370</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4980,34 +4980,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2079</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>521192</v>
+        <v>521125</v>
       </c>
       <c r="R46" t="n">
-        <v>7008832</v>
+        <v>7009003</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5260,32 +5260,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132934565</v>
+        <v>132934619</v>
       </c>
       <c r="B49" t="n">
-        <v>91881</v>
+        <v>91971</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>521199</v>
+        <v>521192</v>
       </c>
       <c r="R49" t="n">
-        <v>7008837</v>
+        <v>7008832</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,45 +5357,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132934506</v>
+        <v>132934565</v>
       </c>
       <c r="B50" t="n">
-        <v>97370</v>
+        <v>91881</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>521125</v>
+        <v>521199</v>
       </c>
       <c r="R50" t="n">
-        <v>7009003</v>
+        <v>7008837</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5454,32 +5454,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132934610</v>
+        <v>132934631</v>
       </c>
       <c r="B51" t="n">
-        <v>80342</v>
+        <v>79091</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>521212</v>
+        <v>521241</v>
       </c>
       <c r="R51" t="n">
-        <v>7009093</v>
+        <v>7008805</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5551,10 +5551,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132934562</v>
+        <v>132934647</v>
       </c>
       <c r="B52" t="n">
-        <v>83315</v>
+        <v>78345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5562,21 +5562,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5586,10 +5586,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>521180</v>
+        <v>521237</v>
       </c>
       <c r="R52" t="n">
-        <v>7009050</v>
+        <v>7008806</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5648,10 +5648,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132934730</v>
+        <v>132934610</v>
       </c>
       <c r="B53" t="n">
-        <v>101338</v>
+        <v>80342</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5659,21 +5659,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521062</v>
+        <v>521212</v>
       </c>
       <c r="R53" t="n">
-        <v>7009070</v>
+        <v>7009093</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5745,10 +5745,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132934631</v>
+        <v>132934562</v>
       </c>
       <c r="B54" t="n">
-        <v>79091</v>
+        <v>83315</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5756,21 +5756,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>521241</v>
+        <v>521180</v>
       </c>
       <c r="R54" t="n">
-        <v>7008805</v>
+        <v>7009050</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5842,32 +5842,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132934647</v>
+        <v>132934730</v>
       </c>
       <c r="B55" t="n">
-        <v>78345</v>
+        <v>101338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228579</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>521237</v>
+        <v>521062</v>
       </c>
       <c r="R55" t="n">
-        <v>7008806</v>
+        <v>7009070</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5939,45 +5939,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132934558</v>
+        <v>132934615</v>
       </c>
       <c r="B56" t="n">
-        <v>92192</v>
+        <v>75417</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>65</v>
+        <v>1460</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>521052</v>
+        <v>521138</v>
       </c>
       <c r="R56" t="n">
-        <v>7008845</v>
+        <v>7008969</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6036,10 +6036,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132934615</v>
+        <v>132934640</v>
       </c>
       <c r="B57" t="n">
-        <v>75417</v>
+        <v>80438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6047,21 +6047,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6071,10 +6071,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>521138</v>
+        <v>521171</v>
       </c>
       <c r="R57" t="n">
-        <v>7008969</v>
+        <v>7009092</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6133,45 +6133,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132934675</v>
+        <v>132934544</v>
       </c>
       <c r="B58" t="n">
-        <v>99130</v>
+        <v>79090</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521056</v>
+        <v>521030</v>
       </c>
       <c r="R58" t="n">
-        <v>7009075</v>
+        <v>7008914</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6204,11 +6204,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>8st bladrosetter</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6235,45 +6230,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132934640</v>
+        <v>132934558</v>
       </c>
       <c r="B59" t="n">
-        <v>80438</v>
+        <v>92192</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>65</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>521171</v>
+        <v>521052</v>
       </c>
       <c r="R59" t="n">
-        <v>7009092</v>
+        <v>7008845</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6332,45 +6327,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132934544</v>
+        <v>132934675</v>
       </c>
       <c r="B60" t="n">
-        <v>79090</v>
+        <v>99130</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>521030</v>
+        <v>521056</v>
       </c>
       <c r="R60" t="n">
-        <v>7008914</v>
+        <v>7009075</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6403,6 +6398,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>8st bladrosetter</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6429,7 +6429,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132934532</v>
+        <v>132934626</v>
       </c>
       <c r="B61" t="n">
         <v>79091</v>
@@ -6460,14 +6460,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>521183</v>
+        <v>521121</v>
       </c>
       <c r="R61" t="n">
-        <v>7008817</v>
+        <v>7009153</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6526,7 +6526,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132934626</v>
+        <v>132934532</v>
       </c>
       <c r="B62" t="n">
         <v>79091</v>
@@ -6557,14 +6557,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>521121</v>
+        <v>521183</v>
       </c>
       <c r="R62" t="n">
-        <v>7009153</v>
+        <v>7008817</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6623,32 +6623,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132934724</v>
+        <v>132934729</v>
       </c>
       <c r="B63" t="n">
-        <v>93206</v>
+        <v>83307</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>521161</v>
+        <v>521143</v>
       </c>
       <c r="R63" t="n">
-        <v>7008948</v>
+        <v>7008975</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6720,32 +6720,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132934709</v>
+        <v>132934724</v>
       </c>
       <c r="B64" t="n">
-        <v>79333</v>
+        <v>93206</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>521086</v>
+        <v>521161</v>
       </c>
       <c r="R64" t="n">
-        <v>7009170</v>
+        <v>7008948</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6785,12 +6785,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6817,32 +6817,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132934633</v>
+        <v>132934660</v>
       </c>
       <c r="B65" t="n">
-        <v>80438</v>
+        <v>91846</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>2013</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6852,10 +6852,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>521131</v>
+        <v>521085</v>
       </c>
       <c r="R65" t="n">
-        <v>7009066</v>
+        <v>7008964</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6882,12 +6882,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6914,32 +6919,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132934602</v>
+        <v>132934709</v>
       </c>
       <c r="B66" t="n">
-        <v>80342</v>
+        <v>79333</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6949,10 +6954,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521128</v>
+        <v>521086</v>
       </c>
       <c r="R66" t="n">
-        <v>7009053</v>
+        <v>7009170</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6979,12 +6984,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7011,10 +7016,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132934729</v>
+        <v>132934633</v>
       </c>
       <c r="B67" t="n">
-        <v>83307</v>
+        <v>80438</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7022,21 +7027,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7046,10 +7051,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521143</v>
+        <v>521131</v>
       </c>
       <c r="R67" t="n">
-        <v>7008975</v>
+        <v>7009066</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7076,12 +7081,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7108,32 +7113,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934660</v>
+        <v>132934602</v>
       </c>
       <c r="B68" t="n">
-        <v>91846</v>
+        <v>80342</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2013</v>
+        <v>6456</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7143,10 +7148,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521085</v>
+        <v>521128</v>
       </c>
       <c r="R68" t="n">
-        <v>7008964</v>
+        <v>7009053</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7173,17 +7178,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Mikroskoperad</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7210,45 +7210,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132934522</v>
+        <v>132934670</v>
       </c>
       <c r="B69" t="n">
-        <v>79091</v>
+        <v>99130</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520949</v>
+        <v>521175</v>
       </c>
       <c r="R69" t="n">
-        <v>7008801</v>
+        <v>7009071</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7275,12 +7275,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7307,45 +7312,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132934670</v>
+        <v>132934522</v>
       </c>
       <c r="B70" t="n">
-        <v>99130</v>
+        <v>79091</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>521175</v>
+        <v>520949</v>
       </c>
       <c r="R70" t="n">
-        <v>7009071</v>
+        <v>7008801</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7372,17 +7377,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>4st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7409,10 +7409,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132934526</v>
+        <v>132934542</v>
       </c>
       <c r="B71" t="n">
-        <v>79091</v>
+        <v>79090</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7420,21 +7420,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>521142</v>
+        <v>520944</v>
       </c>
       <c r="R71" t="n">
-        <v>7008938</v>
+        <v>7008802</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7603,10 +7603,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132934542</v>
+        <v>132934646</v>
       </c>
       <c r="B73" t="n">
-        <v>79090</v>
+        <v>80438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7614,34 +7614,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520944</v>
+        <v>521053</v>
       </c>
       <c r="R73" t="n">
-        <v>7008802</v>
+        <v>7008982</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7700,10 +7700,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132934646</v>
+        <v>132934526</v>
       </c>
       <c r="B74" t="n">
-        <v>80438</v>
+        <v>79091</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7711,34 +7711,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>521053</v>
+        <v>521142</v>
       </c>
       <c r="R74" t="n">
-        <v>7008982</v>
+        <v>7008938</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7797,10 +7797,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132934528</v>
+        <v>132934702</v>
       </c>
       <c r="B75" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7808,34 +7808,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>521188</v>
+        <v>521069</v>
       </c>
       <c r="R75" t="n">
-        <v>7008858</v>
+        <v>7009122</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7991,32 +7991,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132934702</v>
+        <v>132934671</v>
       </c>
       <c r="B77" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>521069</v>
+        <v>521125</v>
       </c>
       <c r="R77" t="n">
-        <v>7009122</v>
+        <v>7009063</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8056,12 +8056,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8088,45 +8093,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132934671</v>
+        <v>132934528</v>
       </c>
       <c r="B78" t="n">
-        <v>99130</v>
+        <v>79091</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>521125</v>
+        <v>521188</v>
       </c>
       <c r="R78" t="n">
-        <v>7009063</v>
+        <v>7008858</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8153,17 +8158,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8287,10 +8287,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132934703</v>
+        <v>132934599</v>
       </c>
       <c r="B80" t="n">
-        <v>79333</v>
+        <v>80304</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8298,21 +8298,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>388</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8322,10 +8322,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>521068</v>
+        <v>521196</v>
       </c>
       <c r="R80" t="n">
-        <v>7009094</v>
+        <v>7008906</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8366,6 +8366,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8384,10 +8385,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132934550</v>
+        <v>132934703</v>
       </c>
       <c r="B81" t="n">
-        <v>79090</v>
+        <v>79333</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8395,34 +8396,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>521248</v>
+        <v>521068</v>
       </c>
       <c r="R81" t="n">
-        <v>7008806</v>
+        <v>7009094</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8481,10 +8482,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132934575</v>
+        <v>132934550</v>
       </c>
       <c r="B82" t="n">
-        <v>79952</v>
+        <v>79090</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8492,34 +8493,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>521035</v>
+        <v>521248</v>
       </c>
       <c r="R82" t="n">
-        <v>7008820</v>
+        <v>7008806</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8578,10 +8579,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132934599</v>
+        <v>132934575</v>
       </c>
       <c r="B83" t="n">
-        <v>80304</v>
+        <v>79952</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8589,21 +8590,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>388</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8613,10 +8614,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>521196</v>
+        <v>521035</v>
       </c>
       <c r="R83" t="n">
-        <v>7008906</v>
+        <v>7008820</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8657,7 +8658,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8676,45 +8676,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132934611</v>
+        <v>132934529</v>
       </c>
       <c r="B84" t="n">
-        <v>80342</v>
+        <v>79091</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>521191</v>
+        <v>521186</v>
       </c>
       <c r="R84" t="n">
-        <v>7008824</v>
+        <v>7008836</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8773,32 +8773,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934641</v>
+        <v>132934611</v>
       </c>
       <c r="B85" t="n">
-        <v>80438</v>
+        <v>80342</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521052</v>
+        <v>521191</v>
       </c>
       <c r="R85" t="n">
-        <v>7009135</v>
+        <v>7008824</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8870,32 +8870,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132934604</v>
+        <v>132934641</v>
       </c>
       <c r="B86" t="n">
-        <v>80342</v>
+        <v>80438</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>521079</v>
+        <v>521052</v>
       </c>
       <c r="R86" t="n">
-        <v>7008865</v>
+        <v>7009135</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8967,45 +8967,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132934548</v>
+        <v>132934604</v>
       </c>
       <c r="B87" t="n">
-        <v>79090</v>
+        <v>80342</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>521142</v>
+        <v>521079</v>
       </c>
       <c r="R87" t="n">
-        <v>7008938</v>
+        <v>7008865</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9064,32 +9064,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132934514</v>
+        <v>132934548</v>
       </c>
       <c r="B88" t="n">
-        <v>80342</v>
+        <v>79090</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9099,10 +9099,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>521008</v>
+        <v>521142</v>
       </c>
       <c r="R88" t="n">
-        <v>7008813</v>
+        <v>7008938</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9161,45 +9161,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132934701</v>
+        <v>132934514</v>
       </c>
       <c r="B89" t="n">
-        <v>79333</v>
+        <v>80342</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>521075</v>
+        <v>521008</v>
       </c>
       <c r="R89" t="n">
-        <v>7009147</v>
+        <v>7008813</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9258,10 +9258,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132934529</v>
+        <v>132934701</v>
       </c>
       <c r="B90" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9269,34 +9269,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>521186</v>
+        <v>521075</v>
       </c>
       <c r="R90" t="n">
-        <v>7008836</v>
+        <v>7009147</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9559,45 +9559,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934530</v>
+        <v>132934616</v>
       </c>
       <c r="B93" t="n">
-        <v>79091</v>
+        <v>79357</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521248</v>
+        <v>521117</v>
       </c>
       <c r="R93" t="n">
-        <v>7008805</v>
+        <v>7009023</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9753,32 +9753,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132934616</v>
+        <v>132934678</v>
       </c>
       <c r="B95" t="n">
-        <v>79357</v>
+        <v>99130</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9788,10 +9788,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521117</v>
+        <v>521234</v>
       </c>
       <c r="R95" t="n">
-        <v>7009023</v>
+        <v>7009077</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9824,6 +9824,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9850,45 +9855,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132934678</v>
+        <v>132934530</v>
       </c>
       <c r="B96" t="n">
-        <v>99130</v>
+        <v>79091</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521234</v>
+        <v>521248</v>
       </c>
       <c r="R96" t="n">
-        <v>7009077</v>
+        <v>7008805</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9921,11 +9926,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11127,10 +11127,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132934587</v>
+        <v>132934524</v>
       </c>
       <c r="B109" t="n">
-        <v>91918</v>
+        <v>79091</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11138,34 +11138,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>521077</v>
+        <v>521010</v>
       </c>
       <c r="R109" t="n">
-        <v>7009118</v>
+        <v>7008924</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11224,45 +11224,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132934691</v>
+        <v>132934531</v>
       </c>
       <c r="B110" t="n">
-        <v>92092</v>
+        <v>79091</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>521092</v>
+        <v>521212</v>
       </c>
       <c r="R110" t="n">
-        <v>7009170</v>
+        <v>7008824</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11321,45 +11321,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132934554</v>
+        <v>132934587</v>
       </c>
       <c r="B111" t="n">
-        <v>92092</v>
+        <v>91918</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1503</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>521105</v>
+        <v>521077</v>
       </c>
       <c r="R111" t="n">
-        <v>7009010</v>
+        <v>7009118</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11418,7 +11418,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132934555</v>
+        <v>132934691</v>
       </c>
       <c r="B112" t="n">
         <v>92092</v>
@@ -11449,14 +11449,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>521211</v>
+        <v>521092</v>
       </c>
       <c r="R112" t="n">
-        <v>7008839</v>
+        <v>7009170</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11612,45 +11612,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132934609</v>
+        <v>132934554</v>
       </c>
       <c r="B114" t="n">
-        <v>80342</v>
+        <v>92092</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6456</v>
+        <v>1503</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>521140</v>
+        <v>521105</v>
       </c>
       <c r="R114" t="n">
-        <v>7009061</v>
+        <v>7009010</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11677,12 +11677,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11709,45 +11709,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132934726</v>
+        <v>132934555</v>
       </c>
       <c r="B115" t="n">
-        <v>80473</v>
+        <v>92092</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6463</v>
+        <v>1503</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>521240</v>
+        <v>521211</v>
       </c>
       <c r="R115" t="n">
-        <v>7008810</v>
+        <v>7008839</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11806,45 +11806,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132934524</v>
+        <v>132934609</v>
       </c>
       <c r="B116" t="n">
-        <v>79091</v>
+        <v>80342</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>521010</v>
+        <v>521140</v>
       </c>
       <c r="R116" t="n">
-        <v>7008924</v>
+        <v>7009061</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11871,12 +11871,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -11903,45 +11903,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132934531</v>
+        <v>132934726</v>
       </c>
       <c r="B117" t="n">
-        <v>79091</v>
+        <v>80473</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>521212</v>
+        <v>521240</v>
       </c>
       <c r="R117" t="n">
-        <v>7008824</v>
+        <v>7008810</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132934576</v>
+        <v>132934583</v>
       </c>
       <c r="B2" t="n">
-        <v>79952</v>
+        <v>79923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521217</v>
+        <v>521109</v>
       </c>
       <c r="R2" t="n">
-        <v>7008823</v>
+        <v>7009014</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,45 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132934567</v>
+        <v>132934523</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>79091</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521236</v>
+        <v>521025</v>
       </c>
       <c r="R3" t="n">
-        <v>7008806</v>
+        <v>7008930</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132934515</v>
+        <v>132934521</v>
       </c>
       <c r="B4" t="n">
-        <v>80342</v>
+        <v>79091</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521069</v>
+        <v>521045</v>
       </c>
       <c r="R4" t="n">
-        <v>7009143</v>
+        <v>7008824</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132934583</v>
+        <v>132934576</v>
       </c>
       <c r="B5" t="n">
-        <v>79923</v>
+        <v>79952</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521109</v>
+        <v>521217</v>
       </c>
       <c r="R5" t="n">
-        <v>7009014</v>
+        <v>7008823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,45 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132934523</v>
+        <v>132934567</v>
       </c>
       <c r="B6" t="n">
-        <v>79091</v>
+        <v>91881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521025</v>
+        <v>521236</v>
       </c>
       <c r="R6" t="n">
-        <v>7008930</v>
+        <v>7008806</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132934521</v>
+        <v>132934515</v>
       </c>
       <c r="B7" t="n">
-        <v>79091</v>
+        <v>80342</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521045</v>
+        <v>521069</v>
       </c>
       <c r="R7" t="n">
-        <v>7008824</v>
+        <v>7009143</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132934612</v>
+        <v>132934572</v>
       </c>
       <c r="B8" t="n">
-        <v>92378</v>
+        <v>79952</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521071</v>
+        <v>521188</v>
       </c>
       <c r="R8" t="n">
-        <v>7009121</v>
+        <v>7008858</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132934601</v>
+        <v>132934612</v>
       </c>
       <c r="B9" t="n">
-        <v>80304</v>
+        <v>92378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>388</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521184</v>
+        <v>521071</v>
       </c>
       <c r="R9" t="n">
-        <v>7009065</v>
+        <v>7009121</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132934572</v>
+        <v>132934601</v>
       </c>
       <c r="B10" t="n">
-        <v>79952</v>
+        <v>80304</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>388</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521188</v>
+        <v>521184</v>
       </c>
       <c r="R10" t="n">
-        <v>7008858</v>
+        <v>7009065</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132934557</v>
+        <v>132934680</v>
       </c>
       <c r="B11" t="n">
-        <v>83181</v>
+        <v>57136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521183</v>
+        <v>521010</v>
       </c>
       <c r="R11" t="n">
-        <v>7009052</v>
+        <v>7008813</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1619,6 +1619,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1st födosökande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1645,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132934680</v>
+        <v>132934666</v>
       </c>
       <c r="B12" t="n">
-        <v>57136</v>
+        <v>79090</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521010</v>
+        <v>521215</v>
       </c>
       <c r="R12" t="n">
-        <v>7008813</v>
+        <v>7008844</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1716,11 +1721,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1st födosökande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1747,7 +1747,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132934666</v>
+        <v>132934547</v>
       </c>
       <c r="B13" t="n">
         <v>79090</v>
@@ -1778,14 +1778,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521215</v>
+        <v>521140</v>
       </c>
       <c r="R13" t="n">
-        <v>7008844</v>
+        <v>7008998</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132934547</v>
+        <v>132934634</v>
       </c>
       <c r="B14" t="n">
-        <v>79090</v>
+        <v>80438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,34 +1855,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521140</v>
+        <v>521157</v>
       </c>
       <c r="R14" t="n">
-        <v>7008998</v>
+        <v>7008985</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132934634</v>
+        <v>132934557</v>
       </c>
       <c r="B15" t="n">
-        <v>80438</v>
+        <v>83181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,34 +1952,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521157</v>
+        <v>521183</v>
       </c>
       <c r="R15" t="n">
-        <v>7008985</v>
+        <v>7009052</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2426,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132934613</v>
+        <v>132934564</v>
       </c>
       <c r="B20" t="n">
-        <v>92217</v>
+        <v>97370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521069</v>
+        <v>521171</v>
       </c>
       <c r="R20" t="n">
-        <v>7009117</v>
+        <v>7009063</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2523,32 +2523,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132934564</v>
+        <v>132934676</v>
       </c>
       <c r="B21" t="n">
-        <v>97370</v>
+        <v>99130</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521171</v>
+        <v>521068</v>
       </c>
       <c r="R21" t="n">
-        <v>7009063</v>
+        <v>7009134</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2588,12 +2588,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2620,45 +2625,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132934559</v>
+        <v>132934569</v>
       </c>
       <c r="B22" t="n">
-        <v>92192</v>
+        <v>79952</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521072</v>
+        <v>521055</v>
       </c>
       <c r="R22" t="n">
-        <v>7009164</v>
+        <v>7008912</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,32 +2722,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132934690</v>
+        <v>132934574</v>
       </c>
       <c r="B23" t="n">
-        <v>92092</v>
+        <v>79952</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521012</v>
+        <v>521228</v>
       </c>
       <c r="R23" t="n">
-        <v>7008951</v>
+        <v>7008805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,32 +2819,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132934620</v>
+        <v>132934607</v>
       </c>
       <c r="B24" t="n">
-        <v>91971</v>
+        <v>80342</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2079</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521239</v>
+        <v>521198</v>
       </c>
       <c r="R24" t="n">
-        <v>7008816</v>
+        <v>7008890</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,32 +2916,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132934569</v>
+        <v>132934690</v>
       </c>
       <c r="B25" t="n">
-        <v>79952</v>
+        <v>92092</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521055</v>
+        <v>521012</v>
       </c>
       <c r="R25" t="n">
-        <v>7008912</v>
+        <v>7008951</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3008,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132934574</v>
+        <v>132934620</v>
       </c>
       <c r="B26" t="n">
-        <v>79952</v>
+        <v>91971</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3019,21 +3024,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3043,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521228</v>
+        <v>521239</v>
       </c>
       <c r="R26" t="n">
-        <v>7008805</v>
+        <v>7008816</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3105,32 +3110,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132934607</v>
+        <v>132934613</v>
       </c>
       <c r="B27" t="n">
-        <v>80342</v>
+        <v>92217</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3140,10 +3145,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521198</v>
+        <v>521069</v>
       </c>
       <c r="R27" t="n">
-        <v>7008890</v>
+        <v>7009117</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3202,10 +3207,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132934676</v>
+        <v>132934559</v>
       </c>
       <c r="B28" t="n">
-        <v>99130</v>
+        <v>92192</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3213,34 +3218,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521068</v>
+        <v>521072</v>
       </c>
       <c r="R28" t="n">
-        <v>7009134</v>
+        <v>7009164</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3273,11 +3278,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3304,32 +3304,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132934588</v>
+        <v>132934673</v>
       </c>
       <c r="B29" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521065</v>
+        <v>521159</v>
       </c>
       <c r="R29" t="n">
-        <v>7009134</v>
+        <v>7008976</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3369,12 +3369,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>12st bladrosetter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3401,32 +3406,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132934598</v>
+        <v>132934679</v>
       </c>
       <c r="B30" t="n">
-        <v>80304</v>
+        <v>99130</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3436,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521134</v>
+        <v>521159</v>
       </c>
       <c r="R30" t="n">
-        <v>7009060</v>
+        <v>7009071</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3466,12 +3471,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>3st bladrosetter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3480,7 +3490,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3499,10 +3508,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132934517</v>
+        <v>132934534</v>
       </c>
       <c r="B31" t="n">
-        <v>92217</v>
+        <v>80438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3510,21 +3519,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3534,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521068</v>
+        <v>521190</v>
       </c>
       <c r="R31" t="n">
-        <v>7009094</v>
+        <v>7008892</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3570,6 +3579,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På sälghögstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3596,10 +3610,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132934534</v>
+        <v>132934664</v>
       </c>
       <c r="B32" t="n">
-        <v>80438</v>
+        <v>79090</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3607,34 +3621,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521190</v>
+        <v>521186</v>
       </c>
       <c r="R32" t="n">
-        <v>7008892</v>
+        <v>7008837</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3667,11 +3681,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På sälghögstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3698,10 +3707,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132934664</v>
+        <v>132934588</v>
       </c>
       <c r="B33" t="n">
-        <v>79090</v>
+        <v>91918</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3709,21 +3718,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3733,10 +3742,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521186</v>
+        <v>521065</v>
       </c>
       <c r="R33" t="n">
-        <v>7008837</v>
+        <v>7009134</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3795,45 +3804,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132934725</v>
+        <v>132934517</v>
       </c>
       <c r="B34" t="n">
-        <v>93206</v>
+        <v>92217</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521171</v>
+        <v>521068</v>
       </c>
       <c r="R34" t="n">
-        <v>7008936</v>
+        <v>7009094</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3892,32 +3901,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132934673</v>
+        <v>132934598</v>
       </c>
       <c r="B35" t="n">
-        <v>99130</v>
+        <v>80304</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3927,10 +3936,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521159</v>
+        <v>521134</v>
       </c>
       <c r="R35" t="n">
-        <v>7008976</v>
+        <v>7009060</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3965,17 +3974,13 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>12st bladrosetter</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -3994,32 +3999,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132934679</v>
+        <v>132934725</v>
       </c>
       <c r="B36" t="n">
-        <v>99130</v>
+        <v>93206</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4034,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521159</v>
+        <v>521171</v>
       </c>
       <c r="R36" t="n">
-        <v>7009071</v>
+        <v>7008936</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4065,11 +4070,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>3st bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4096,10 +4096,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132934510</v>
+        <v>132934627</v>
       </c>
       <c r="B37" t="n">
-        <v>91918</v>
+        <v>79091</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4107,34 +4107,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521051</v>
+        <v>521207</v>
       </c>
       <c r="R37" t="n">
-        <v>7009102</v>
+        <v>7008846</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4193,10 +4193,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132934585</v>
+        <v>132934541</v>
       </c>
       <c r="B38" t="n">
-        <v>91918</v>
+        <v>79090</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4204,34 +4204,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521047</v>
+        <v>521045</v>
       </c>
       <c r="R38" t="n">
-        <v>7009108</v>
+        <v>7008824</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132934541</v>
+        <v>132934704</v>
       </c>
       <c r="B39" t="n">
-        <v>79090</v>
+        <v>79333</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4301,34 +4301,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>521045</v>
+        <v>521125</v>
       </c>
       <c r="R39" t="n">
-        <v>7008824</v>
+        <v>7009007</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4387,10 +4387,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132934614</v>
+        <v>132934642</v>
       </c>
       <c r="B40" t="n">
-        <v>75417</v>
+        <v>80438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4398,21 +4398,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>521110</v>
+        <v>521241</v>
       </c>
       <c r="R40" t="n">
-        <v>7009041</v>
+        <v>7008806</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4484,32 +4484,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132934704</v>
+        <v>132934606</v>
       </c>
       <c r="B41" t="n">
-        <v>79333</v>
+        <v>80342</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521125</v>
+        <v>521194</v>
       </c>
       <c r="R41" t="n">
-        <v>7009007</v>
+        <v>7008902</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4581,32 +4581,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132934642</v>
+        <v>132934566</v>
       </c>
       <c r="B42" t="n">
-        <v>80438</v>
+        <v>91881</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521241</v>
+        <v>521207</v>
       </c>
       <c r="R42" t="n">
-        <v>7008806</v>
+        <v>7008851</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4678,32 +4678,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132934606</v>
+        <v>132934614</v>
       </c>
       <c r="B43" t="n">
-        <v>80342</v>
+        <v>75417</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>1460</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521194</v>
+        <v>521110</v>
       </c>
       <c r="R43" t="n">
-        <v>7008902</v>
+        <v>7009041</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4775,32 +4775,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132934566</v>
+        <v>132934585</v>
       </c>
       <c r="B44" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521207</v>
+        <v>521047</v>
       </c>
       <c r="R44" t="n">
-        <v>7008851</v>
+        <v>7009108</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4872,10 +4872,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132934627</v>
+        <v>132934510</v>
       </c>
       <c r="B45" t="n">
-        <v>79091</v>
+        <v>91918</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4883,34 +4883,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>521207</v>
+        <v>521051</v>
       </c>
       <c r="R45" t="n">
-        <v>7008846</v>
+        <v>7009102</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4969,10 +4969,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132934506</v>
+        <v>132934545</v>
       </c>
       <c r="B46" t="n">
-        <v>97370</v>
+        <v>79090</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4980,21 +4980,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>521125</v>
+        <v>521006</v>
       </c>
       <c r="R46" t="n">
-        <v>7009003</v>
+        <v>7009011</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5066,10 +5066,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132934545</v>
+        <v>132934570</v>
       </c>
       <c r="B47" t="n">
-        <v>79090</v>
+        <v>79952</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5077,34 +5077,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>521006</v>
+        <v>520978</v>
       </c>
       <c r="R47" t="n">
-        <v>7009011</v>
+        <v>7008880</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5163,32 +5163,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132934570</v>
+        <v>132934565</v>
       </c>
       <c r="B48" t="n">
-        <v>79952</v>
+        <v>91881</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>520978</v>
+        <v>521199</v>
       </c>
       <c r="R48" t="n">
-        <v>7008880</v>
+        <v>7008837</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132934619</v>
+        <v>132934506</v>
       </c>
       <c r="B49" t="n">
-        <v>91971</v>
+        <v>97370</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5271,34 +5271,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2079</v>
+        <v>53</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>521192</v>
+        <v>521125</v>
       </c>
       <c r="R49" t="n">
-        <v>7008832</v>
+        <v>7009003</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,32 +5357,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132934565</v>
+        <v>132934619</v>
       </c>
       <c r="B50" t="n">
-        <v>91881</v>
+        <v>91971</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>521199</v>
+        <v>521192</v>
       </c>
       <c r="R50" t="n">
-        <v>7008837</v>
+        <v>7008832</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5454,32 +5454,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132934631</v>
+        <v>132934730</v>
       </c>
       <c r="B51" t="n">
-        <v>79091</v>
+        <v>101338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>521241</v>
+        <v>521062</v>
       </c>
       <c r="R51" t="n">
-        <v>7008805</v>
+        <v>7009070</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5551,32 +5551,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132934647</v>
+        <v>132934610</v>
       </c>
       <c r="B52" t="n">
-        <v>78345</v>
+        <v>80342</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228579</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5586,10 +5586,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>521237</v>
+        <v>521212</v>
       </c>
       <c r="R52" t="n">
-        <v>7008806</v>
+        <v>7009093</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5648,32 +5648,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132934610</v>
+        <v>132934562</v>
       </c>
       <c r="B53" t="n">
-        <v>80342</v>
+        <v>83315</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521212</v>
+        <v>521180</v>
       </c>
       <c r="R53" t="n">
-        <v>7009093</v>
+        <v>7009050</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5745,10 +5745,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132934562</v>
+        <v>132934631</v>
       </c>
       <c r="B54" t="n">
-        <v>83315</v>
+        <v>79091</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5756,21 +5756,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>521180</v>
+        <v>521241</v>
       </c>
       <c r="R54" t="n">
-        <v>7009050</v>
+        <v>7008805</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5842,32 +5842,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132934730</v>
+        <v>132934647</v>
       </c>
       <c r="B55" t="n">
-        <v>101338</v>
+        <v>78345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>228579</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>521062</v>
+        <v>521237</v>
       </c>
       <c r="R55" t="n">
-        <v>7009070</v>
+        <v>7008806</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5939,10 +5939,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132934615</v>
+        <v>132934640</v>
       </c>
       <c r="B56" t="n">
-        <v>75417</v>
+        <v>80438</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5950,21 +5950,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>521138</v>
+        <v>521171</v>
       </c>
       <c r="R56" t="n">
-        <v>7008969</v>
+        <v>7009092</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6036,10 +6036,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132934640</v>
+        <v>132934544</v>
       </c>
       <c r="B57" t="n">
-        <v>80438</v>
+        <v>79090</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6047,34 +6047,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>521171</v>
+        <v>521030</v>
       </c>
       <c r="R57" t="n">
-        <v>7009092</v>
+        <v>7008914</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6133,10 +6133,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132934544</v>
+        <v>132934615</v>
       </c>
       <c r="B58" t="n">
-        <v>79090</v>
+        <v>75417</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6144,34 +6144,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>1460</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521030</v>
+        <v>521138</v>
       </c>
       <c r="R58" t="n">
-        <v>7008914</v>
+        <v>7008969</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6623,10 +6623,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132934729</v>
+        <v>132934522</v>
       </c>
       <c r="B63" t="n">
-        <v>83307</v>
+        <v>79091</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6634,34 +6634,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>308</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>521143</v>
+        <v>520949</v>
       </c>
       <c r="R63" t="n">
-        <v>7008975</v>
+        <v>7008801</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6720,32 +6720,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132934724</v>
+        <v>132934729</v>
       </c>
       <c r="B64" t="n">
-        <v>93206</v>
+        <v>83307</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>521161</v>
+        <v>521143</v>
       </c>
       <c r="R64" t="n">
-        <v>7008948</v>
+        <v>7008975</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6785,12 +6785,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6817,32 +6817,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132934660</v>
+        <v>132934724</v>
       </c>
       <c r="B65" t="n">
-        <v>91846</v>
+        <v>93206</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2013</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6852,10 +6852,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>521085</v>
+        <v>521161</v>
       </c>
       <c r="R65" t="n">
-        <v>7008964</v>
+        <v>7008948</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6882,17 +6882,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Mikroskoperad</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6919,32 +6914,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132934709</v>
+        <v>132934660</v>
       </c>
       <c r="B66" t="n">
-        <v>79333</v>
+        <v>91846</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>2013</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6954,10 +6949,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521086</v>
+        <v>521085</v>
       </c>
       <c r="R66" t="n">
-        <v>7009170</v>
+        <v>7008964</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6990,6 +6985,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7016,10 +7016,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132934633</v>
+        <v>132934709</v>
       </c>
       <c r="B67" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7027,21 +7027,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521131</v>
+        <v>521086</v>
       </c>
       <c r="R67" t="n">
-        <v>7009066</v>
+        <v>7009170</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7081,12 +7081,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7113,32 +7113,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934602</v>
+        <v>132934633</v>
       </c>
       <c r="B68" t="n">
-        <v>80342</v>
+        <v>80438</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521128</v>
+        <v>521131</v>
       </c>
       <c r="R68" t="n">
-        <v>7009053</v>
+        <v>7009066</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7210,32 +7210,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132934670</v>
+        <v>132934602</v>
       </c>
       <c r="B69" t="n">
-        <v>99130</v>
+        <v>80342</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7245,10 +7245,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>521175</v>
+        <v>521128</v>
       </c>
       <c r="R69" t="n">
-        <v>7009071</v>
+        <v>7009053</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7281,11 +7281,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7312,45 +7307,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132934522</v>
+        <v>132934670</v>
       </c>
       <c r="B70" t="n">
-        <v>79091</v>
+        <v>99130</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520949</v>
+        <v>521175</v>
       </c>
       <c r="R70" t="n">
-        <v>7008801</v>
+        <v>7009071</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7377,12 +7372,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7991,45 +7991,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132934671</v>
+        <v>132934528</v>
       </c>
       <c r="B77" t="n">
-        <v>99130</v>
+        <v>79091</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>521125</v>
+        <v>521188</v>
       </c>
       <c r="R77" t="n">
-        <v>7009063</v>
+        <v>7008858</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8056,17 +8056,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8093,7 +8088,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132934528</v>
+        <v>132934629</v>
       </c>
       <c r="B78" t="n">
         <v>79091</v>
@@ -8124,14 +8119,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>521188</v>
+        <v>521115</v>
       </c>
       <c r="R78" t="n">
-        <v>7008858</v>
+        <v>7009027</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8190,32 +8185,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132934629</v>
+        <v>132934671</v>
       </c>
       <c r="B79" t="n">
-        <v>79091</v>
+        <v>99130</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8225,10 +8220,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>521115</v>
+        <v>521125</v>
       </c>
       <c r="R79" t="n">
-        <v>7009027</v>
+        <v>7009063</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8255,12 +8250,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8287,10 +8287,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132934599</v>
+        <v>132934703</v>
       </c>
       <c r="B80" t="n">
-        <v>80304</v>
+        <v>79333</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8298,21 +8298,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8322,10 +8322,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>521196</v>
+        <v>521068</v>
       </c>
       <c r="R80" t="n">
-        <v>7008906</v>
+        <v>7009094</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8366,7 +8366,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8385,10 +8384,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132934703</v>
+        <v>132934550</v>
       </c>
       <c r="B81" t="n">
-        <v>79333</v>
+        <v>79090</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8396,34 +8395,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>521068</v>
+        <v>521248</v>
       </c>
       <c r="R81" t="n">
-        <v>7009094</v>
+        <v>7008806</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8482,10 +8481,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132934550</v>
+        <v>132934575</v>
       </c>
       <c r="B82" t="n">
-        <v>79090</v>
+        <v>79952</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8493,34 +8492,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>521248</v>
+        <v>521035</v>
       </c>
       <c r="R82" t="n">
-        <v>7008806</v>
+        <v>7008820</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8579,10 +8578,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132934575</v>
+        <v>132934599</v>
       </c>
       <c r="B83" t="n">
-        <v>79952</v>
+        <v>80304</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8590,21 +8589,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>388</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8614,10 +8613,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>521035</v>
+        <v>521196</v>
       </c>
       <c r="R83" t="n">
-        <v>7008820</v>
+        <v>7008906</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8658,6 +8657,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8676,32 +8676,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132934529</v>
+        <v>132934552</v>
       </c>
       <c r="B84" t="n">
-        <v>79091</v>
+        <v>99130</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>521186</v>
+        <v>521056</v>
       </c>
       <c r="R84" t="n">
-        <v>7008836</v>
+        <v>7009135</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8747,6 +8747,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Över 40 plantor</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8773,32 +8778,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934611</v>
+        <v>132934674</v>
       </c>
       <c r="B85" t="n">
-        <v>80342</v>
+        <v>99130</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8808,10 +8813,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521191</v>
+        <v>521168</v>
       </c>
       <c r="R85" t="n">
-        <v>7008824</v>
+        <v>7009069</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8844,6 +8849,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8870,32 +8880,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132934641</v>
+        <v>132934611</v>
       </c>
       <c r="B86" t="n">
-        <v>80438</v>
+        <v>80342</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8905,10 +8915,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>521052</v>
+        <v>521191</v>
       </c>
       <c r="R86" t="n">
-        <v>7009135</v>
+        <v>7008824</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8967,32 +8977,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132934604</v>
+        <v>132934641</v>
       </c>
       <c r="B87" t="n">
-        <v>80342</v>
+        <v>80438</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9002,10 +9012,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>521079</v>
+        <v>521052</v>
       </c>
       <c r="R87" t="n">
-        <v>7008865</v>
+        <v>7009135</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9064,45 +9074,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132934548</v>
+        <v>132934604</v>
       </c>
       <c r="B88" t="n">
-        <v>79090</v>
+        <v>80342</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>521142</v>
+        <v>521079</v>
       </c>
       <c r="R88" t="n">
-        <v>7008938</v>
+        <v>7008865</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9161,32 +9171,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132934514</v>
+        <v>132934548</v>
       </c>
       <c r="B89" t="n">
-        <v>80342</v>
+        <v>79090</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9196,10 +9206,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>521008</v>
+        <v>521142</v>
       </c>
       <c r="R89" t="n">
-        <v>7008813</v>
+        <v>7008938</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9258,45 +9268,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132934701</v>
+        <v>132934514</v>
       </c>
       <c r="B90" t="n">
-        <v>79333</v>
+        <v>80342</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>521075</v>
+        <v>521008</v>
       </c>
       <c r="R90" t="n">
-        <v>7009147</v>
+        <v>7008813</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9355,45 +9365,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934552</v>
+        <v>132934701</v>
       </c>
       <c r="B91" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521056</v>
+        <v>521075</v>
       </c>
       <c r="R91" t="n">
-        <v>7009135</v>
+        <v>7009147</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9426,11 +9436,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Över 40 plantor</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9457,45 +9462,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934674</v>
+        <v>132934529</v>
       </c>
       <c r="B92" t="n">
-        <v>99130</v>
+        <v>79091</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521168</v>
+        <v>521186</v>
       </c>
       <c r="R92" t="n">
-        <v>7009069</v>
+        <v>7008836</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9528,11 +9533,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9559,32 +9559,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934616</v>
+        <v>132934586</v>
       </c>
       <c r="B93" t="n">
-        <v>79357</v>
+        <v>91918</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6434</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521117</v>
+        <v>521068</v>
       </c>
       <c r="R93" t="n">
-        <v>7009023</v>
+        <v>7009176</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9656,10 +9656,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934586</v>
+        <v>132934530</v>
       </c>
       <c r="B94" t="n">
-        <v>91918</v>
+        <v>79091</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9667,34 +9667,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521068</v>
+        <v>521248</v>
       </c>
       <c r="R94" t="n">
-        <v>7009176</v>
+        <v>7008805</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9753,32 +9753,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132934678</v>
+        <v>132934616</v>
       </c>
       <c r="B95" t="n">
-        <v>99130</v>
+        <v>79357</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9788,10 +9788,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521234</v>
+        <v>521117</v>
       </c>
       <c r="R95" t="n">
-        <v>7009077</v>
+        <v>7009023</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9824,11 +9824,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9855,45 +9850,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132934530</v>
+        <v>132934678</v>
       </c>
       <c r="B96" t="n">
-        <v>79091</v>
+        <v>99130</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521248</v>
+        <v>521234</v>
       </c>
       <c r="R96" t="n">
-        <v>7008805</v>
+        <v>7009077</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9926,6 +9921,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10243,32 +10243,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132934600</v>
+        <v>132934677</v>
       </c>
       <c r="B100" t="n">
-        <v>80304</v>
+        <v>99130</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10278,10 +10278,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>521188</v>
+        <v>521070</v>
       </c>
       <c r="R100" t="n">
-        <v>7008835</v>
+        <v>7009057</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10316,13 +10316,17 @@
           <t>2026-04-25</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>&gt;30 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10341,45 +10345,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132934513</v>
+        <v>132934605</v>
       </c>
       <c r="B101" t="n">
-        <v>80304</v>
+        <v>80342</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>388</v>
+        <v>6456</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>521186</v>
+        <v>521000</v>
       </c>
       <c r="R101" t="n">
-        <v>7009049</v>
+        <v>7008814</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10438,10 +10442,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132934605</v>
+        <v>132934728</v>
       </c>
       <c r="B102" t="n">
-        <v>80342</v>
+        <v>80473</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10449,21 +10453,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10473,10 +10477,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>521000</v>
+        <v>521142</v>
       </c>
       <c r="R102" t="n">
-        <v>7008814</v>
+        <v>7008987</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10535,45 +10539,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132934728</v>
+        <v>132934533</v>
       </c>
       <c r="B103" t="n">
-        <v>80473</v>
+        <v>80438</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>521142</v>
+        <v>521124</v>
       </c>
       <c r="R103" t="n">
-        <v>7008987</v>
+        <v>7008989</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10606,6 +10610,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På låga av sälg</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10632,10 +10641,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132934533</v>
+        <v>132934551</v>
       </c>
       <c r="B104" t="n">
-        <v>80438</v>
+        <v>79090</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10643,21 +10652,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10667,10 +10676,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>521124</v>
+        <v>521211</v>
       </c>
       <c r="R104" t="n">
-        <v>7008989</v>
+        <v>7008824</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10703,11 +10712,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>På låga av sälg</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10734,10 +10738,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132934551</v>
+        <v>132934600</v>
       </c>
       <c r="B105" t="n">
-        <v>79090</v>
+        <v>80304</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10745,34 +10749,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>388</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>521211</v>
+        <v>521188</v>
       </c>
       <c r="R105" t="n">
-        <v>7008824</v>
+        <v>7008835</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10813,6 +10817,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -10831,45 +10836,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132934677</v>
+        <v>132934513</v>
       </c>
       <c r="B106" t="n">
-        <v>99130</v>
+        <v>80304</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>521070</v>
+        <v>521186</v>
       </c>
       <c r="R106" t="n">
-        <v>7009057</v>
+        <v>7009049</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10902,11 +10907,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>&gt;30 bladrosetter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11127,32 +11127,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132934524</v>
+        <v>132934516</v>
       </c>
       <c r="B109" t="n">
-        <v>79091</v>
+        <v>80342</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11162,10 +11162,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>521010</v>
+        <v>521131</v>
       </c>
       <c r="R109" t="n">
-        <v>7008924</v>
+        <v>7008987</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11224,45 +11224,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132934531</v>
+        <v>132934609</v>
       </c>
       <c r="B110" t="n">
-        <v>79091</v>
+        <v>80342</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>521212</v>
+        <v>521140</v>
       </c>
       <c r="R110" t="n">
-        <v>7008824</v>
+        <v>7009061</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11289,12 +11289,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11321,32 +11321,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132934587</v>
+        <v>132934726</v>
       </c>
       <c r="B111" t="n">
-        <v>91918</v>
+        <v>80473</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11356,10 +11356,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>521077</v>
+        <v>521240</v>
       </c>
       <c r="R111" t="n">
-        <v>7009118</v>
+        <v>7008810</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11515,45 +11515,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132934516</v>
+        <v>132934587</v>
       </c>
       <c r="B113" t="n">
-        <v>80342</v>
+        <v>91918</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>521131</v>
+        <v>521077</v>
       </c>
       <c r="R113" t="n">
-        <v>7008987</v>
+        <v>7009118</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11806,45 +11806,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132934609</v>
+        <v>132934524</v>
       </c>
       <c r="B116" t="n">
-        <v>80342</v>
+        <v>79091</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>521140</v>
+        <v>521010</v>
       </c>
       <c r="R116" t="n">
-        <v>7009061</v>
+        <v>7008924</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11871,12 +11871,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -11903,45 +11903,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132934726</v>
+        <v>132934531</v>
       </c>
       <c r="B117" t="n">
-        <v>80473</v>
+        <v>79091</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>521240</v>
+        <v>521212</v>
       </c>
       <c r="R117" t="n">
-        <v>7008810</v>
+        <v>7008824</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -1650,7 +1650,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132934666</v>
+        <v>132934547</v>
       </c>
       <c r="B12" t="n">
         <v>79090</v>
@@ -1681,14 +1681,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521215</v>
+        <v>521140</v>
       </c>
       <c r="R12" t="n">
-        <v>7008844</v>
+        <v>7008998</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132934547</v>
+        <v>132934557</v>
       </c>
       <c r="B13" t="n">
-        <v>79090</v>
+        <v>83181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521140</v>
+        <v>521183</v>
       </c>
       <c r="R13" t="n">
-        <v>7008998</v>
+        <v>7009052</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132934634</v>
+        <v>132934525</v>
       </c>
       <c r="B14" t="n">
-        <v>80438</v>
+        <v>79091</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,34 +1855,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521157</v>
+        <v>521152</v>
       </c>
       <c r="R14" t="n">
-        <v>7008985</v>
+        <v>7008946</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132934557</v>
+        <v>132934666</v>
       </c>
       <c r="B15" t="n">
-        <v>83181</v>
+        <v>79090</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,34 +1952,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521183</v>
+        <v>521215</v>
       </c>
       <c r="R15" t="n">
-        <v>7009052</v>
+        <v>7008844</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132934525</v>
+        <v>132934634</v>
       </c>
       <c r="B16" t="n">
-        <v>79091</v>
+        <v>80438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,34 +2049,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521152</v>
+        <v>521157</v>
       </c>
       <c r="R16" t="n">
-        <v>7008946</v>
+        <v>7008985</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132934564</v>
+        <v>132934690</v>
       </c>
       <c r="B20" t="n">
-        <v>97370</v>
+        <v>92092</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>1503</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521171</v>
+        <v>521012</v>
       </c>
       <c r="R20" t="n">
-        <v>7009063</v>
+        <v>7008951</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2523,32 +2523,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132934676</v>
+        <v>132934620</v>
       </c>
       <c r="B21" t="n">
-        <v>99130</v>
+        <v>91971</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521068</v>
+        <v>521239</v>
       </c>
       <c r="R21" t="n">
-        <v>7009134</v>
+        <v>7008816</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2594,11 +2594,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2625,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132934569</v>
+        <v>132934564</v>
       </c>
       <c r="B22" t="n">
-        <v>79952</v>
+        <v>97370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2631,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521055</v>
+        <v>521171</v>
       </c>
       <c r="R22" t="n">
-        <v>7008912</v>
+        <v>7009063</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2690,12 +2685,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2722,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132934574</v>
+        <v>132934613</v>
       </c>
       <c r="B23" t="n">
-        <v>79952</v>
+        <v>92217</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2728,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521228</v>
+        <v>521069</v>
       </c>
       <c r="R23" t="n">
-        <v>7008805</v>
+        <v>7009117</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2819,45 +2814,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132934607</v>
+        <v>132934559</v>
       </c>
       <c r="B24" t="n">
-        <v>80342</v>
+        <v>92192</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>65</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521198</v>
+        <v>521072</v>
       </c>
       <c r="R24" t="n">
-        <v>7008890</v>
+        <v>7009164</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,32 +2911,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132934690</v>
+        <v>132934569</v>
       </c>
       <c r="B25" t="n">
-        <v>92092</v>
+        <v>79952</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2951,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521012</v>
+        <v>521055</v>
       </c>
       <c r="R25" t="n">
-        <v>7008951</v>
+        <v>7008912</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132934620</v>
+        <v>132934574</v>
       </c>
       <c r="B26" t="n">
-        <v>91971</v>
+        <v>79952</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,21 +3019,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3048,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521239</v>
+        <v>521228</v>
       </c>
       <c r="R26" t="n">
-        <v>7008816</v>
+        <v>7008805</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,32 +3105,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132934613</v>
+        <v>132934607</v>
       </c>
       <c r="B27" t="n">
-        <v>92217</v>
+        <v>80342</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3145,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521069</v>
+        <v>521198</v>
       </c>
       <c r="R27" t="n">
-        <v>7009117</v>
+        <v>7008890</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3207,10 +3202,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132934559</v>
+        <v>132934676</v>
       </c>
       <c r="B28" t="n">
-        <v>92192</v>
+        <v>99130</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3218,34 +3213,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>65</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521072</v>
+        <v>521068</v>
       </c>
       <c r="R28" t="n">
-        <v>7009164</v>
+        <v>7009134</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3278,6 +3273,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3304,45 +3304,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132934673</v>
+        <v>132934534</v>
       </c>
       <c r="B29" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521159</v>
+        <v>521190</v>
       </c>
       <c r="R29" t="n">
-        <v>7008976</v>
+        <v>7008892</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3369,17 +3369,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>12st bladrosetter</t>
+          <t>På sälghögstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3406,32 +3406,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132934679</v>
+        <v>132934664</v>
       </c>
       <c r="B30" t="n">
-        <v>99130</v>
+        <v>79090</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521159</v>
+        <v>521186</v>
       </c>
       <c r="R30" t="n">
-        <v>7009071</v>
+        <v>7008837</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3477,11 +3477,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>3st bladrosetter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3508,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132934534</v>
+        <v>132934588</v>
       </c>
       <c r="B31" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3519,34 +3514,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521190</v>
+        <v>521065</v>
       </c>
       <c r="R31" t="n">
-        <v>7008892</v>
+        <v>7009134</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3579,11 +3574,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På sälghögstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3610,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132934664</v>
+        <v>132934517</v>
       </c>
       <c r="B32" t="n">
-        <v>79090</v>
+        <v>92217</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3621,34 +3611,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521186</v>
+        <v>521068</v>
       </c>
       <c r="R32" t="n">
-        <v>7008837</v>
+        <v>7009094</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3707,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132934588</v>
+        <v>132934598</v>
       </c>
       <c r="B33" t="n">
-        <v>91918</v>
+        <v>80304</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3718,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>388</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3742,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521065</v>
+        <v>521134</v>
       </c>
       <c r="R33" t="n">
-        <v>7009134</v>
+        <v>7009060</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3772,12 +3762,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3786,6 +3776,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3804,45 +3795,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132934517</v>
+        <v>132934725</v>
       </c>
       <c r="B34" t="n">
-        <v>92217</v>
+        <v>93206</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521068</v>
+        <v>521171</v>
       </c>
       <c r="R34" t="n">
-        <v>7009094</v>
+        <v>7008936</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3901,32 +3892,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132934598</v>
+        <v>132934673</v>
       </c>
       <c r="B35" t="n">
-        <v>80304</v>
+        <v>99130</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3936,10 +3927,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521134</v>
+        <v>521159</v>
       </c>
       <c r="R35" t="n">
-        <v>7009060</v>
+        <v>7008976</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3974,13 +3965,17 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>12st bladrosetter</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -3999,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132934725</v>
+        <v>132934679</v>
       </c>
       <c r="B36" t="n">
-        <v>93206</v>
+        <v>99130</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4034,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521171</v>
+        <v>521159</v>
       </c>
       <c r="R36" t="n">
-        <v>7008936</v>
+        <v>7009071</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4070,6 +4065,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>3st bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4096,10 +4096,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132934627</v>
+        <v>132934541</v>
       </c>
       <c r="B37" t="n">
-        <v>79091</v>
+        <v>79090</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4107,34 +4107,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521207</v>
+        <v>521045</v>
       </c>
       <c r="R37" t="n">
-        <v>7008846</v>
+        <v>7008824</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4193,10 +4193,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132934541</v>
+        <v>132934704</v>
       </c>
       <c r="B38" t="n">
-        <v>79090</v>
+        <v>79333</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4204,34 +4204,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521045</v>
+        <v>521125</v>
       </c>
       <c r="R38" t="n">
-        <v>7008824</v>
+        <v>7009007</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132934704</v>
+        <v>132934642</v>
       </c>
       <c r="B39" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4301,21 +4301,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>521125</v>
+        <v>521241</v>
       </c>
       <c r="R39" t="n">
-        <v>7009007</v>
+        <v>7008806</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4387,32 +4387,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132934642</v>
+        <v>132934606</v>
       </c>
       <c r="B40" t="n">
-        <v>80438</v>
+        <v>80342</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>521241</v>
+        <v>521194</v>
       </c>
       <c r="R40" t="n">
-        <v>7008806</v>
+        <v>7008902</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132934606</v>
+        <v>132934566</v>
       </c>
       <c r="B41" t="n">
-        <v>80342</v>
+        <v>91881</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4495,21 +4495,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521194</v>
+        <v>521207</v>
       </c>
       <c r="R41" t="n">
-        <v>7008902</v>
+        <v>7008851</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4581,32 +4581,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132934566</v>
+        <v>132934614</v>
       </c>
       <c r="B42" t="n">
-        <v>91881</v>
+        <v>75417</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>1460</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521207</v>
+        <v>521110</v>
       </c>
       <c r="R42" t="n">
-        <v>7008851</v>
+        <v>7009041</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132934614</v>
+        <v>132934585</v>
       </c>
       <c r="B43" t="n">
-        <v>75417</v>
+        <v>91918</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4689,21 +4689,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521110</v>
+        <v>521047</v>
       </c>
       <c r="R43" t="n">
-        <v>7009041</v>
+        <v>7009108</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4775,7 +4775,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132934585</v>
+        <v>132934510</v>
       </c>
       <c r="B44" t="n">
         <v>91918</v>
@@ -4806,14 +4806,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521047</v>
+        <v>521051</v>
       </c>
       <c r="R44" t="n">
-        <v>7009108</v>
+        <v>7009102</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4872,10 +4872,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132934510</v>
+        <v>132934627</v>
       </c>
       <c r="B45" t="n">
-        <v>91918</v>
+        <v>79091</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4883,34 +4883,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>521051</v>
+        <v>521207</v>
       </c>
       <c r="R45" t="n">
-        <v>7009102</v>
+        <v>7008846</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5454,10 +5454,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132934730</v>
+        <v>132934610</v>
       </c>
       <c r="B51" t="n">
-        <v>101338</v>
+        <v>80342</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5465,21 +5465,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>521062</v>
+        <v>521212</v>
       </c>
       <c r="R51" t="n">
-        <v>7009070</v>
+        <v>7009093</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5551,32 +5551,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132934610</v>
+        <v>132934562</v>
       </c>
       <c r="B52" t="n">
-        <v>80342</v>
+        <v>83315</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5586,10 +5586,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>521212</v>
+        <v>521180</v>
       </c>
       <c r="R52" t="n">
-        <v>7009093</v>
+        <v>7009050</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5648,32 +5648,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132934562</v>
+        <v>132934730</v>
       </c>
       <c r="B53" t="n">
-        <v>83315</v>
+        <v>101338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521180</v>
+        <v>521062</v>
       </c>
       <c r="R53" t="n">
-        <v>7009050</v>
+        <v>7009070</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6720,32 +6720,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132934729</v>
+        <v>132934670</v>
       </c>
       <c r="B64" t="n">
-        <v>83307</v>
+        <v>99130</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>521143</v>
+        <v>521175</v>
       </c>
       <c r="R64" t="n">
-        <v>7008975</v>
+        <v>7009071</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6785,12 +6785,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6817,10 +6822,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132934724</v>
+        <v>132934602</v>
       </c>
       <c r="B65" t="n">
-        <v>93206</v>
+        <v>80342</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6828,21 +6833,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6852,10 +6857,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>521161</v>
+        <v>521128</v>
       </c>
       <c r="R65" t="n">
-        <v>7008948</v>
+        <v>7009053</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6914,32 +6919,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132934660</v>
+        <v>132934709</v>
       </c>
       <c r="B66" t="n">
-        <v>91846</v>
+        <v>79333</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2013</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6949,10 +6954,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521085</v>
+        <v>521086</v>
       </c>
       <c r="R66" t="n">
-        <v>7008964</v>
+        <v>7009170</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6985,11 +6990,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7016,10 +7016,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132934709</v>
+        <v>132934633</v>
       </c>
       <c r="B67" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7027,21 +7027,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521086</v>
+        <v>521131</v>
       </c>
       <c r="R67" t="n">
-        <v>7009170</v>
+        <v>7009066</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7081,12 +7081,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7113,10 +7113,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934633</v>
+        <v>132934729</v>
       </c>
       <c r="B68" t="n">
-        <v>80438</v>
+        <v>83307</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7124,21 +7124,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521131</v>
+        <v>521143</v>
       </c>
       <c r="R68" t="n">
-        <v>7009066</v>
+        <v>7008975</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7210,10 +7210,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132934602</v>
+        <v>132934724</v>
       </c>
       <c r="B69" t="n">
-        <v>80342</v>
+        <v>93206</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7221,21 +7221,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7245,10 +7245,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>521128</v>
+        <v>521161</v>
       </c>
       <c r="R69" t="n">
-        <v>7009053</v>
+        <v>7008948</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7307,32 +7307,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132934670</v>
+        <v>132934660</v>
       </c>
       <c r="B70" t="n">
-        <v>99130</v>
+        <v>91846</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>2013</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7342,10 +7342,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>521175</v>
+        <v>521085</v>
       </c>
       <c r="R70" t="n">
-        <v>7009071</v>
+        <v>7008964</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7372,17 +7372,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>4st bladrosetter</t>
+          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7797,32 +7797,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132934702</v>
+        <v>132934671</v>
       </c>
       <c r="B75" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7832,10 +7832,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>521069</v>
+        <v>521125</v>
       </c>
       <c r="R75" t="n">
-        <v>7009122</v>
+        <v>7009063</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7862,12 +7862,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8185,32 +8190,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132934671</v>
+        <v>132934702</v>
       </c>
       <c r="B79" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8220,10 +8225,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>521125</v>
+        <v>521069</v>
       </c>
       <c r="R79" t="n">
-        <v>7009063</v>
+        <v>7009122</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8250,17 +8255,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132934583</v>
+        <v>132934576</v>
       </c>
       <c r="B2" t="n">
-        <v>79923</v>
+        <v>79952</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521109</v>
+        <v>521217</v>
       </c>
       <c r="R2" t="n">
-        <v>7009014</v>
+        <v>7008823</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132934523</v>
+        <v>132934515</v>
       </c>
       <c r="B3" t="n">
-        <v>79091</v>
+        <v>80342</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521025</v>
+        <v>521069</v>
       </c>
       <c r="R3" t="n">
-        <v>7008930</v>
+        <v>7009143</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,45 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132934521</v>
+        <v>132934567</v>
       </c>
       <c r="B4" t="n">
-        <v>79091</v>
+        <v>91881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521045</v>
+        <v>521236</v>
       </c>
       <c r="R4" t="n">
-        <v>7008824</v>
+        <v>7008806</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132934576</v>
+        <v>132934583</v>
       </c>
       <c r="B5" t="n">
-        <v>79952</v>
+        <v>79923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521217</v>
+        <v>521109</v>
       </c>
       <c r="R5" t="n">
-        <v>7008823</v>
+        <v>7009014</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,45 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132934567</v>
+        <v>132934523</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>79091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521236</v>
+        <v>521025</v>
       </c>
       <c r="R6" t="n">
-        <v>7008806</v>
+        <v>7008930</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132934515</v>
+        <v>132934521</v>
       </c>
       <c r="B7" t="n">
-        <v>80342</v>
+        <v>79091</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521069</v>
+        <v>521045</v>
       </c>
       <c r="R7" t="n">
-        <v>7009143</v>
+        <v>7008824</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132934680</v>
+        <v>132934666</v>
       </c>
       <c r="B11" t="n">
-        <v>57136</v>
+        <v>79090</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521010</v>
+        <v>521215</v>
       </c>
       <c r="R11" t="n">
-        <v>7008813</v>
+        <v>7008844</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1619,11 +1619,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1st födosökande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1747,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132934557</v>
+        <v>132934634</v>
       </c>
       <c r="B13" t="n">
-        <v>83181</v>
+        <v>80438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,34 +1753,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521183</v>
+        <v>521157</v>
       </c>
       <c r="R13" t="n">
-        <v>7009052</v>
+        <v>7008985</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1812,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1844,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132934525</v>
+        <v>132934557</v>
       </c>
       <c r="B14" t="n">
-        <v>79091</v>
+        <v>83181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521152</v>
+        <v>521183</v>
       </c>
       <c r="R14" t="n">
-        <v>7008946</v>
+        <v>7009052</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132934666</v>
+        <v>132934525</v>
       </c>
       <c r="B15" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,34 +1947,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521215</v>
+        <v>521152</v>
       </c>
       <c r="R15" t="n">
-        <v>7008844</v>
+        <v>7008946</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132934634</v>
+        <v>132934680</v>
       </c>
       <c r="B16" t="n">
-        <v>80438</v>
+        <v>57136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521157</v>
+        <v>521010</v>
       </c>
       <c r="R16" t="n">
-        <v>7008985</v>
+        <v>7008813</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2103,12 +2098,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1st födosökande</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132934690</v>
+        <v>132934569</v>
       </c>
       <c r="B20" t="n">
-        <v>92092</v>
+        <v>79952</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521012</v>
+        <v>521055</v>
       </c>
       <c r="R20" t="n">
-        <v>7008951</v>
+        <v>7008912</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132934620</v>
+        <v>132934574</v>
       </c>
       <c r="B21" t="n">
-        <v>91971</v>
+        <v>79952</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2534,21 +2534,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521239</v>
+        <v>521228</v>
       </c>
       <c r="R21" t="n">
-        <v>7008816</v>
+        <v>7008805</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132934564</v>
+        <v>132934607</v>
       </c>
       <c r="B22" t="n">
-        <v>97370</v>
+        <v>80342</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521171</v>
+        <v>521198</v>
       </c>
       <c r="R22" t="n">
-        <v>7009063</v>
+        <v>7008890</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2717,32 +2717,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132934613</v>
+        <v>132934690</v>
       </c>
       <c r="B23" t="n">
-        <v>92217</v>
+        <v>92092</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1503</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521069</v>
+        <v>521012</v>
       </c>
       <c r="R23" t="n">
-        <v>7009117</v>
+        <v>7008951</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,45 +2814,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132934559</v>
+        <v>132934620</v>
       </c>
       <c r="B24" t="n">
-        <v>92192</v>
+        <v>91971</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521072</v>
+        <v>521239</v>
       </c>
       <c r="R24" t="n">
-        <v>7009164</v>
+        <v>7008816</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132934569</v>
+        <v>132934564</v>
       </c>
       <c r="B25" t="n">
-        <v>79952</v>
+        <v>97370</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521055</v>
+        <v>521171</v>
       </c>
       <c r="R25" t="n">
-        <v>7008912</v>
+        <v>7009063</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2976,12 +2976,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3008,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132934574</v>
+        <v>132934613</v>
       </c>
       <c r="B26" t="n">
-        <v>79952</v>
+        <v>92217</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521228</v>
+        <v>521069</v>
       </c>
       <c r="R26" t="n">
-        <v>7008805</v>
+        <v>7009117</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3105,45 +3105,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132934607</v>
+        <v>132934559</v>
       </c>
       <c r="B27" t="n">
-        <v>80342</v>
+        <v>92192</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>65</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521198</v>
+        <v>521072</v>
       </c>
       <c r="R27" t="n">
-        <v>7008890</v>
+        <v>7009164</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4096,10 +4096,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132934541</v>
+        <v>132934614</v>
       </c>
       <c r="B37" t="n">
-        <v>79090</v>
+        <v>75417</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4107,34 +4107,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>1460</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521045</v>
+        <v>521110</v>
       </c>
       <c r="R37" t="n">
-        <v>7008824</v>
+        <v>7009041</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4193,10 +4193,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132934704</v>
+        <v>132934585</v>
       </c>
       <c r="B38" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4204,21 +4204,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521125</v>
+        <v>521047</v>
       </c>
       <c r="R38" t="n">
-        <v>7009007</v>
+        <v>7009108</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132934642</v>
+        <v>132934510</v>
       </c>
       <c r="B39" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4301,34 +4301,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>521241</v>
+        <v>521051</v>
       </c>
       <c r="R39" t="n">
-        <v>7008806</v>
+        <v>7009102</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4387,10 +4387,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132934606</v>
+        <v>132934566</v>
       </c>
       <c r="B40" t="n">
-        <v>80342</v>
+        <v>91881</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4398,21 +4398,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>521194</v>
+        <v>521207</v>
       </c>
       <c r="R40" t="n">
-        <v>7008902</v>
+        <v>7008851</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4484,45 +4484,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132934566</v>
+        <v>132934541</v>
       </c>
       <c r="B41" t="n">
-        <v>91881</v>
+        <v>79090</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521207</v>
+        <v>521045</v>
       </c>
       <c r="R41" t="n">
-        <v>7008851</v>
+        <v>7008824</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4581,10 +4581,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132934614</v>
+        <v>132934704</v>
       </c>
       <c r="B42" t="n">
-        <v>75417</v>
+        <v>79333</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4592,21 +4592,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1460</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521110</v>
+        <v>521125</v>
       </c>
       <c r="R42" t="n">
-        <v>7009041</v>
+        <v>7009007</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132934585</v>
+        <v>132934642</v>
       </c>
       <c r="B43" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4689,21 +4689,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521047</v>
+        <v>521241</v>
       </c>
       <c r="R43" t="n">
-        <v>7009108</v>
+        <v>7008806</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4775,45 +4775,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132934510</v>
+        <v>132934606</v>
       </c>
       <c r="B44" t="n">
-        <v>91918</v>
+        <v>80342</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521051</v>
+        <v>521194</v>
       </c>
       <c r="R44" t="n">
-        <v>7009102</v>
+        <v>7008902</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5163,45 +5163,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132934565</v>
+        <v>132934506</v>
       </c>
       <c r="B48" t="n">
-        <v>91881</v>
+        <v>97370</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>521199</v>
+        <v>521125</v>
       </c>
       <c r="R48" t="n">
-        <v>7008837</v>
+        <v>7009003</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132934506</v>
+        <v>132934619</v>
       </c>
       <c r="B49" t="n">
-        <v>97370</v>
+        <v>91971</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5271,34 +5271,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>2079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>521125</v>
+        <v>521192</v>
       </c>
       <c r="R49" t="n">
-        <v>7009003</v>
+        <v>7008832</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,32 +5357,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132934619</v>
+        <v>132934565</v>
       </c>
       <c r="B50" t="n">
-        <v>91971</v>
+        <v>91881</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>521192</v>
+        <v>521199</v>
       </c>
       <c r="R50" t="n">
-        <v>7008832</v>
+        <v>7008837</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5648,32 +5648,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132934730</v>
+        <v>132934631</v>
       </c>
       <c r="B53" t="n">
-        <v>101338</v>
+        <v>79091</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521062</v>
+        <v>521241</v>
       </c>
       <c r="R53" t="n">
-        <v>7009070</v>
+        <v>7008805</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5745,32 +5745,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132934631</v>
+        <v>132934730</v>
       </c>
       <c r="B54" t="n">
-        <v>79091</v>
+        <v>101338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>521241</v>
+        <v>521062</v>
       </c>
       <c r="R54" t="n">
-        <v>7008805</v>
+        <v>7009070</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5939,10 +5939,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132934640</v>
+        <v>132934615</v>
       </c>
       <c r="B56" t="n">
-        <v>80438</v>
+        <v>75417</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5950,21 +5950,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>521171</v>
+        <v>521138</v>
       </c>
       <c r="R56" t="n">
-        <v>7009092</v>
+        <v>7008969</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6036,32 +6036,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132934544</v>
+        <v>132934558</v>
       </c>
       <c r="B57" t="n">
-        <v>79090</v>
+        <v>92192</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>65</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6071,10 +6071,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>521030</v>
+        <v>521052</v>
       </c>
       <c r="R57" t="n">
-        <v>7008914</v>
+        <v>7008845</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6133,10 +6133,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132934615</v>
+        <v>132934640</v>
       </c>
       <c r="B58" t="n">
-        <v>75417</v>
+        <v>80438</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6144,21 +6144,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521138</v>
+        <v>521171</v>
       </c>
       <c r="R58" t="n">
-        <v>7008969</v>
+        <v>7009092</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6230,32 +6230,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132934558</v>
+        <v>132934544</v>
       </c>
       <c r="B59" t="n">
-        <v>92192</v>
+        <v>79090</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6265,10 +6265,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>521052</v>
+        <v>521030</v>
       </c>
       <c r="R59" t="n">
-        <v>7008845</v>
+        <v>7008914</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6623,45 +6623,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132934522</v>
+        <v>132934670</v>
       </c>
       <c r="B63" t="n">
-        <v>79091</v>
+        <v>99130</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520949</v>
+        <v>521175</v>
       </c>
       <c r="R63" t="n">
-        <v>7008801</v>
+        <v>7009071</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6688,12 +6688,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6720,45 +6725,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132934670</v>
+        <v>132934522</v>
       </c>
       <c r="B64" t="n">
-        <v>99130</v>
+        <v>79091</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>521175</v>
+        <v>520949</v>
       </c>
       <c r="R64" t="n">
-        <v>7009071</v>
+        <v>7008801</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6785,17 +6790,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>4st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6822,32 +6822,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132934602</v>
+        <v>132934633</v>
       </c>
       <c r="B65" t="n">
-        <v>80342</v>
+        <v>80438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>521128</v>
+        <v>521131</v>
       </c>
       <c r="R65" t="n">
-        <v>7009053</v>
+        <v>7009066</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6919,32 +6919,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132934709</v>
+        <v>132934602</v>
       </c>
       <c r="B66" t="n">
-        <v>79333</v>
+        <v>80342</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521086</v>
+        <v>521128</v>
       </c>
       <c r="R66" t="n">
-        <v>7009170</v>
+        <v>7009053</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7016,10 +7016,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132934633</v>
+        <v>132934729</v>
       </c>
       <c r="B67" t="n">
-        <v>80438</v>
+        <v>83307</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7027,21 +7027,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521131</v>
+        <v>521143</v>
       </c>
       <c r="R67" t="n">
-        <v>7009066</v>
+        <v>7008975</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7081,12 +7081,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7113,32 +7113,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934729</v>
+        <v>132934724</v>
       </c>
       <c r="B68" t="n">
-        <v>83307</v>
+        <v>93206</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>308</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521143</v>
+        <v>521161</v>
       </c>
       <c r="R68" t="n">
-        <v>7008975</v>
+        <v>7008948</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7210,32 +7210,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132934724</v>
+        <v>132934660</v>
       </c>
       <c r="B69" t="n">
-        <v>93206</v>
+        <v>91846</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>2013</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7245,10 +7245,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>521161</v>
+        <v>521085</v>
       </c>
       <c r="R69" t="n">
-        <v>7008948</v>
+        <v>7008964</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7275,12 +7275,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7307,32 +7312,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132934660</v>
+        <v>132934709</v>
       </c>
       <c r="B70" t="n">
-        <v>91846</v>
+        <v>79333</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2013</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7342,10 +7347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>521085</v>
+        <v>521086</v>
       </c>
       <c r="R70" t="n">
-        <v>7008964</v>
+        <v>7009170</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7378,11 +7383,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7506,10 +7506,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132934618</v>
+        <v>132934646</v>
       </c>
       <c r="B72" t="n">
-        <v>91971</v>
+        <v>80438</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7517,21 +7517,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520999</v>
+        <v>521053</v>
       </c>
       <c r="R72" t="n">
-        <v>7008967</v>
+        <v>7008982</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7603,10 +7603,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132934646</v>
+        <v>132934618</v>
       </c>
       <c r="B73" t="n">
-        <v>80438</v>
+        <v>91971</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7614,21 +7614,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>521053</v>
+        <v>520999</v>
       </c>
       <c r="R73" t="n">
-        <v>7008982</v>
+        <v>7008967</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8287,10 +8287,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132934703</v>
+        <v>132934550</v>
       </c>
       <c r="B80" t="n">
-        <v>79333</v>
+        <v>79090</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8298,34 +8298,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>521068</v>
+        <v>521248</v>
       </c>
       <c r="R80" t="n">
-        <v>7009094</v>
+        <v>7008806</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8384,10 +8384,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132934550</v>
+        <v>132934575</v>
       </c>
       <c r="B81" t="n">
-        <v>79090</v>
+        <v>79952</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8395,34 +8395,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>521248</v>
+        <v>521035</v>
       </c>
       <c r="R81" t="n">
-        <v>7008806</v>
+        <v>7008820</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8481,10 +8481,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132934575</v>
+        <v>132934703</v>
       </c>
       <c r="B82" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8492,21 +8492,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8516,10 +8516,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>521035</v>
+        <v>521068</v>
       </c>
       <c r="R82" t="n">
-        <v>7008820</v>
+        <v>7009094</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8880,45 +8880,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132934611</v>
+        <v>132934529</v>
       </c>
       <c r="B86" t="n">
-        <v>80342</v>
+        <v>79091</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>521191</v>
+        <v>521186</v>
       </c>
       <c r="R86" t="n">
-        <v>7008824</v>
+        <v>7008836</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8977,32 +8977,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132934641</v>
+        <v>132934611</v>
       </c>
       <c r="B87" t="n">
-        <v>80438</v>
+        <v>80342</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9012,10 +9012,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>521052</v>
+        <v>521191</v>
       </c>
       <c r="R87" t="n">
-        <v>7009135</v>
+        <v>7008824</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9074,32 +9074,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132934604</v>
+        <v>132934641</v>
       </c>
       <c r="B88" t="n">
-        <v>80342</v>
+        <v>80438</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9109,10 +9109,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>521079</v>
+        <v>521052</v>
       </c>
       <c r="R88" t="n">
-        <v>7008865</v>
+        <v>7009135</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9171,45 +9171,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132934548</v>
+        <v>132934604</v>
       </c>
       <c r="B89" t="n">
-        <v>79090</v>
+        <v>80342</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>521142</v>
+        <v>521079</v>
       </c>
       <c r="R89" t="n">
-        <v>7008938</v>
+        <v>7008865</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9268,32 +9268,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132934514</v>
+        <v>132934548</v>
       </c>
       <c r="B90" t="n">
-        <v>80342</v>
+        <v>79090</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>521008</v>
+        <v>521142</v>
       </c>
       <c r="R90" t="n">
-        <v>7008813</v>
+        <v>7008938</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9365,45 +9365,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934701</v>
+        <v>132934514</v>
       </c>
       <c r="B91" t="n">
-        <v>79333</v>
+        <v>80342</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521075</v>
+        <v>521008</v>
       </c>
       <c r="R91" t="n">
-        <v>7009147</v>
+        <v>7008813</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9462,10 +9462,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934529</v>
+        <v>132934701</v>
       </c>
       <c r="B92" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9473,34 +9473,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521186</v>
+        <v>521075</v>
       </c>
       <c r="R92" t="n">
-        <v>7008836</v>
+        <v>7009147</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9559,32 +9559,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934586</v>
+        <v>132934678</v>
       </c>
       <c r="B93" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521068</v>
+        <v>521234</v>
       </c>
       <c r="R93" t="n">
-        <v>7009176</v>
+        <v>7009077</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9630,6 +9630,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9850,32 +9855,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132934678</v>
+        <v>132934586</v>
       </c>
       <c r="B96" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9885,10 +9890,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521234</v>
+        <v>521068</v>
       </c>
       <c r="R96" t="n">
-        <v>7009077</v>
+        <v>7009176</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9921,11 +9926,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10243,32 +10243,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132934677</v>
+        <v>132934605</v>
       </c>
       <c r="B100" t="n">
-        <v>99130</v>
+        <v>80342</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10278,10 +10278,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>521070</v>
+        <v>521000</v>
       </c>
       <c r="R100" t="n">
-        <v>7009057</v>
+        <v>7008814</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10314,11 +10314,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>&gt;30 bladrosetter</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10345,10 +10340,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132934605</v>
+        <v>132934728</v>
       </c>
       <c r="B101" t="n">
-        <v>80342</v>
+        <v>80473</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10356,21 +10351,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10380,10 +10375,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>521000</v>
+        <v>521142</v>
       </c>
       <c r="R101" t="n">
-        <v>7008814</v>
+        <v>7008987</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10442,45 +10437,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132934728</v>
+        <v>132934533</v>
       </c>
       <c r="B102" t="n">
-        <v>80473</v>
+        <v>80438</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>521142</v>
+        <v>521124</v>
       </c>
       <c r="R102" t="n">
-        <v>7008987</v>
+        <v>7008989</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10513,6 +10508,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>På låga av sälg</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10539,10 +10539,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132934533</v>
+        <v>132934551</v>
       </c>
       <c r="B103" t="n">
-        <v>80438</v>
+        <v>79090</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10550,21 +10550,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10574,10 +10574,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>521124</v>
+        <v>521211</v>
       </c>
       <c r="R103" t="n">
-        <v>7008989</v>
+        <v>7008824</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10610,11 +10610,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>På låga av sälg</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10641,45 +10636,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132934551</v>
+        <v>132934677</v>
       </c>
       <c r="B104" t="n">
-        <v>79090</v>
+        <v>99130</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>521211</v>
+        <v>521070</v>
       </c>
       <c r="R104" t="n">
-        <v>7008824</v>
+        <v>7009057</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10712,6 +10707,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>&gt;30 bladrosetter</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132934525</v>
+        <v>132934680</v>
       </c>
       <c r="B15" t="n">
-        <v>79091</v>
+        <v>57136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,34 +1947,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521152</v>
+        <v>521010</v>
       </c>
       <c r="R15" t="n">
-        <v>7008946</v>
+        <v>7008813</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2007,6 +2007,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1st födosökande</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2033,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132934680</v>
+        <v>132934525</v>
       </c>
       <c r="B16" t="n">
-        <v>57136</v>
+        <v>79091</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,34 +2049,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521010</v>
+        <v>521152</v>
       </c>
       <c r="R16" t="n">
-        <v>7008813</v>
+        <v>7008946</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2104,11 +2109,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1st födosökande</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -4096,10 +4096,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132934614</v>
+        <v>132934541</v>
       </c>
       <c r="B37" t="n">
-        <v>75417</v>
+        <v>79090</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4107,34 +4107,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1460</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521110</v>
+        <v>521045</v>
       </c>
       <c r="R37" t="n">
-        <v>7009041</v>
+        <v>7008824</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4193,10 +4193,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132934585</v>
+        <v>132934704</v>
       </c>
       <c r="B38" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4204,21 +4204,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521047</v>
+        <v>521125</v>
       </c>
       <c r="R38" t="n">
-        <v>7009108</v>
+        <v>7009007</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132934510</v>
+        <v>132934642</v>
       </c>
       <c r="B39" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4301,34 +4301,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>521051</v>
+        <v>521241</v>
       </c>
       <c r="R39" t="n">
-        <v>7009102</v>
+        <v>7008806</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4387,10 +4387,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132934566</v>
+        <v>132934606</v>
       </c>
       <c r="B40" t="n">
-        <v>91881</v>
+        <v>80342</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4398,21 +4398,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>521207</v>
+        <v>521194</v>
       </c>
       <c r="R40" t="n">
-        <v>7008851</v>
+        <v>7008902</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132934541</v>
+        <v>132934614</v>
       </c>
       <c r="B41" t="n">
-        <v>79090</v>
+        <v>75417</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4495,34 +4495,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>1460</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521045</v>
+        <v>521110</v>
       </c>
       <c r="R41" t="n">
-        <v>7008824</v>
+        <v>7009041</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4581,10 +4581,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132934704</v>
+        <v>132934585</v>
       </c>
       <c r="B42" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4592,21 +4592,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521125</v>
+        <v>521047</v>
       </c>
       <c r="R42" t="n">
-        <v>7009007</v>
+        <v>7009108</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132934642</v>
+        <v>132934510</v>
       </c>
       <c r="B43" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4689,34 +4689,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521241</v>
+        <v>521051</v>
       </c>
       <c r="R43" t="n">
-        <v>7008806</v>
+        <v>7009102</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4775,10 +4775,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132934606</v>
+        <v>132934566</v>
       </c>
       <c r="B44" t="n">
-        <v>80342</v>
+        <v>91881</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4786,21 +4786,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521194</v>
+        <v>521207</v>
       </c>
       <c r="R44" t="n">
-        <v>7008902</v>
+        <v>7008851</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5648,32 +5648,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132934631</v>
+        <v>132934730</v>
       </c>
       <c r="B53" t="n">
-        <v>79091</v>
+        <v>101338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521241</v>
+        <v>521062</v>
       </c>
       <c r="R53" t="n">
-        <v>7008805</v>
+        <v>7009070</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5745,32 +5745,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132934730</v>
+        <v>132934647</v>
       </c>
       <c r="B54" t="n">
-        <v>101338</v>
+        <v>78345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>228579</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>521062</v>
+        <v>521237</v>
       </c>
       <c r="R54" t="n">
-        <v>7009070</v>
+        <v>7008806</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132934647</v>
+        <v>132934631</v>
       </c>
       <c r="B55" t="n">
-        <v>78345</v>
+        <v>79091</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5853,21 +5853,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228579</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>521237</v>
+        <v>521241</v>
       </c>
       <c r="R55" t="n">
-        <v>7008806</v>
+        <v>7008805</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7409,10 +7409,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132934542</v>
+        <v>132934526</v>
       </c>
       <c r="B71" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7420,21 +7420,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520944</v>
+        <v>521142</v>
       </c>
       <c r="R71" t="n">
-        <v>7008802</v>
+        <v>7008938</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7506,10 +7506,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132934646</v>
+        <v>132934542</v>
       </c>
       <c r="B72" t="n">
-        <v>80438</v>
+        <v>79090</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7517,34 +7517,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>521053</v>
+        <v>520944</v>
       </c>
       <c r="R72" t="n">
-        <v>7008982</v>
+        <v>7008802</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7603,10 +7603,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132934618</v>
+        <v>132934646</v>
       </c>
       <c r="B73" t="n">
-        <v>91971</v>
+        <v>80438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7614,21 +7614,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520999</v>
+        <v>521053</v>
       </c>
       <c r="R73" t="n">
-        <v>7008967</v>
+        <v>7008982</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7700,10 +7700,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132934526</v>
+        <v>132934618</v>
       </c>
       <c r="B74" t="n">
-        <v>79091</v>
+        <v>91971</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7711,34 +7711,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>521142</v>
+        <v>520999</v>
       </c>
       <c r="R74" t="n">
-        <v>7008938</v>
+        <v>7008967</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9661,45 +9661,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934530</v>
+        <v>132934616</v>
       </c>
       <c r="B94" t="n">
-        <v>79091</v>
+        <v>79357</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521248</v>
+        <v>521117</v>
       </c>
       <c r="R94" t="n">
-        <v>7008805</v>
+        <v>7009023</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9758,32 +9758,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132934616</v>
+        <v>132934586</v>
       </c>
       <c r="B95" t="n">
-        <v>79357</v>
+        <v>91918</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6434</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9793,10 +9793,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521117</v>
+        <v>521068</v>
       </c>
       <c r="R95" t="n">
-        <v>7009023</v>
+        <v>7009176</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9855,10 +9855,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132934586</v>
+        <v>132934530</v>
       </c>
       <c r="B96" t="n">
-        <v>91918</v>
+        <v>79091</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9866,34 +9866,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521068</v>
+        <v>521248</v>
       </c>
       <c r="R96" t="n">
-        <v>7009176</v>
+        <v>7008805</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9952,10 +9952,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132934571</v>
+        <v>132934630</v>
       </c>
       <c r="B97" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9963,21 +9963,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>521202</v>
+        <v>521203</v>
       </c>
       <c r="R97" t="n">
-        <v>7008859</v>
+        <v>7008836</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10049,32 +10049,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132934681</v>
+        <v>132934571</v>
       </c>
       <c r="B98" t="n">
-        <v>106258</v>
+        <v>79952</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>521191</v>
+        <v>521202</v>
       </c>
       <c r="R98" t="n">
-        <v>7008908</v>
+        <v>7008859</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10146,32 +10146,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132934630</v>
+        <v>132934681</v>
       </c>
       <c r="B99" t="n">
-        <v>79091</v>
+        <v>106258</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>221144</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>521203</v>
+        <v>521191</v>
       </c>
       <c r="R99" t="n">
-        <v>7008836</v>
+        <v>7008908</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11127,45 +11127,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132934516</v>
+        <v>132934691</v>
       </c>
       <c r="B109" t="n">
-        <v>80342</v>
+        <v>92092</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6456</v>
+        <v>1503</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>521131</v>
+        <v>521092</v>
       </c>
       <c r="R109" t="n">
-        <v>7008987</v>
+        <v>7009170</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11224,32 +11224,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132934609</v>
+        <v>132934587</v>
       </c>
       <c r="B110" t="n">
-        <v>80342</v>
+        <v>91918</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11259,10 +11259,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>521140</v>
+        <v>521077</v>
       </c>
       <c r="R110" t="n">
-        <v>7009061</v>
+        <v>7009118</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11289,12 +11289,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11321,45 +11321,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132934726</v>
+        <v>132934554</v>
       </c>
       <c r="B111" t="n">
-        <v>80473</v>
+        <v>92092</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6463</v>
+        <v>1503</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>521240</v>
+        <v>521105</v>
       </c>
       <c r="R111" t="n">
-        <v>7008810</v>
+        <v>7009010</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11418,7 +11418,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132934691</v>
+        <v>132934555</v>
       </c>
       <c r="B112" t="n">
         <v>92092</v>
@@ -11449,14 +11449,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>521092</v>
+        <v>521211</v>
       </c>
       <c r="R112" t="n">
-        <v>7009170</v>
+        <v>7008839</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11515,45 +11515,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132934587</v>
+        <v>132934516</v>
       </c>
       <c r="B113" t="n">
-        <v>91918</v>
+        <v>80342</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>521077</v>
+        <v>521131</v>
       </c>
       <c r="R113" t="n">
-        <v>7009118</v>
+        <v>7008987</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11612,45 +11612,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132934554</v>
+        <v>132934609</v>
       </c>
       <c r="B114" t="n">
-        <v>92092</v>
+        <v>80342</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1503</v>
+        <v>6456</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>521105</v>
+        <v>521140</v>
       </c>
       <c r="R114" t="n">
-        <v>7009010</v>
+        <v>7009061</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11677,12 +11677,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11709,45 +11709,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132934555</v>
+        <v>132934726</v>
       </c>
       <c r="B115" t="n">
-        <v>92092</v>
+        <v>80473</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1503</v>
+        <v>6463</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>521211</v>
+        <v>521240</v>
       </c>
       <c r="R115" t="n">
-        <v>7008839</v>
+        <v>7008810</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -4096,10 +4096,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132934541</v>
+        <v>132934614</v>
       </c>
       <c r="B37" t="n">
-        <v>79090</v>
+        <v>75417</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4107,34 +4107,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>1460</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521045</v>
+        <v>521110</v>
       </c>
       <c r="R37" t="n">
-        <v>7008824</v>
+        <v>7009041</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4193,10 +4193,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132934704</v>
+        <v>132934585</v>
       </c>
       <c r="B38" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4204,21 +4204,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521125</v>
+        <v>521047</v>
       </c>
       <c r="R38" t="n">
-        <v>7009007</v>
+        <v>7009108</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132934642</v>
+        <v>132934510</v>
       </c>
       <c r="B39" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4301,34 +4301,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>521241</v>
+        <v>521051</v>
       </c>
       <c r="R39" t="n">
-        <v>7008806</v>
+        <v>7009102</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4387,10 +4387,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132934606</v>
+        <v>132934566</v>
       </c>
       <c r="B40" t="n">
-        <v>80342</v>
+        <v>91881</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4398,21 +4398,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>521194</v>
+        <v>521207</v>
       </c>
       <c r="R40" t="n">
-        <v>7008902</v>
+        <v>7008851</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132934614</v>
+        <v>132934541</v>
       </c>
       <c r="B41" t="n">
-        <v>75417</v>
+        <v>79090</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4495,34 +4495,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1460</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521110</v>
+        <v>521045</v>
       </c>
       <c r="R41" t="n">
-        <v>7009041</v>
+        <v>7008824</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4581,10 +4581,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132934585</v>
+        <v>132934704</v>
       </c>
       <c r="B42" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4592,21 +4592,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521047</v>
+        <v>521125</v>
       </c>
       <c r="R42" t="n">
-        <v>7009108</v>
+        <v>7009007</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132934510</v>
+        <v>132934642</v>
       </c>
       <c r="B43" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4689,34 +4689,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521051</v>
+        <v>521241</v>
       </c>
       <c r="R43" t="n">
-        <v>7009102</v>
+        <v>7008806</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4775,10 +4775,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132934566</v>
+        <v>132934606</v>
       </c>
       <c r="B44" t="n">
-        <v>91881</v>
+        <v>80342</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4786,21 +4786,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521207</v>
+        <v>521194</v>
       </c>
       <c r="R44" t="n">
-        <v>7008851</v>
+        <v>7008902</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5648,32 +5648,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132934730</v>
+        <v>132934631</v>
       </c>
       <c r="B53" t="n">
-        <v>101338</v>
+        <v>79091</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521062</v>
+        <v>521241</v>
       </c>
       <c r="R53" t="n">
-        <v>7009070</v>
+        <v>7008805</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5745,32 +5745,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132934647</v>
+        <v>132934730</v>
       </c>
       <c r="B54" t="n">
-        <v>78345</v>
+        <v>101338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228579</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>521237</v>
+        <v>521062</v>
       </c>
       <c r="R54" t="n">
-        <v>7008806</v>
+        <v>7009070</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132934631</v>
+        <v>132934647</v>
       </c>
       <c r="B55" t="n">
-        <v>79091</v>
+        <v>78345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5853,21 +5853,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>228579</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>521241</v>
+        <v>521237</v>
       </c>
       <c r="R55" t="n">
-        <v>7008805</v>
+        <v>7008806</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -10636,32 +10636,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132934677</v>
+        <v>132934600</v>
       </c>
       <c r="B104" t="n">
-        <v>99130</v>
+        <v>80304</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>521070</v>
+        <v>521188</v>
       </c>
       <c r="R104" t="n">
-        <v>7009057</v>
+        <v>7008835</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10709,17 +10709,13 @@
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>&gt;30 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -10738,7 +10734,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132934600</v>
+        <v>132934513</v>
       </c>
       <c r="B105" t="n">
         <v>80304</v>
@@ -10769,14 +10765,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>521188</v>
+        <v>521186</v>
       </c>
       <c r="R105" t="n">
-        <v>7008835</v>
+        <v>7009049</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10817,7 +10813,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -10836,45 +10831,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132934513</v>
+        <v>132934677</v>
       </c>
       <c r="B106" t="n">
-        <v>80304</v>
+        <v>99130</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>521186</v>
+        <v>521070</v>
       </c>
       <c r="R106" t="n">
-        <v>7009049</v>
+        <v>7009057</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10907,6 +10902,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>&gt;30 bladrosetter</t>
         </is>
       </c>
       <c r="AD106" t="b">

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -4969,10 +4969,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132934545</v>
+        <v>132934506</v>
       </c>
       <c r="B46" t="n">
-        <v>79090</v>
+        <v>97370</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4980,21 +4980,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>521006</v>
+        <v>521125</v>
       </c>
       <c r="R46" t="n">
-        <v>7009011</v>
+        <v>7009003</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5066,10 +5066,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132934570</v>
+        <v>132934619</v>
       </c>
       <c r="B47" t="n">
-        <v>79952</v>
+        <v>91971</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5077,21 +5077,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520978</v>
+        <v>521192</v>
       </c>
       <c r="R47" t="n">
-        <v>7008880</v>
+        <v>7008832</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5163,45 +5163,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132934506</v>
+        <v>132934565</v>
       </c>
       <c r="B48" t="n">
-        <v>97370</v>
+        <v>91881</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>521125</v>
+        <v>521199</v>
       </c>
       <c r="R48" t="n">
-        <v>7009003</v>
+        <v>7008837</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132934619</v>
+        <v>132934545</v>
       </c>
       <c r="B49" t="n">
-        <v>91971</v>
+        <v>79090</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5271,34 +5271,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>521192</v>
+        <v>521006</v>
       </c>
       <c r="R49" t="n">
-        <v>7008832</v>
+        <v>7009011</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,32 +5357,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132934565</v>
+        <v>132934570</v>
       </c>
       <c r="B50" t="n">
-        <v>91881</v>
+        <v>79952</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>521199</v>
+        <v>520978</v>
       </c>
       <c r="R50" t="n">
-        <v>7008837</v>
+        <v>7008880</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5648,32 +5648,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132934631</v>
+        <v>132934730</v>
       </c>
       <c r="B53" t="n">
-        <v>79091</v>
+        <v>101338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521241</v>
+        <v>521062</v>
       </c>
       <c r="R53" t="n">
-        <v>7008805</v>
+        <v>7009070</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5745,32 +5745,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132934730</v>
+        <v>132934647</v>
       </c>
       <c r="B54" t="n">
-        <v>101338</v>
+        <v>78345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>228579</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>521062</v>
+        <v>521237</v>
       </c>
       <c r="R54" t="n">
-        <v>7009070</v>
+        <v>7008806</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132934647</v>
+        <v>132934631</v>
       </c>
       <c r="B55" t="n">
-        <v>78345</v>
+        <v>79091</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5853,21 +5853,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228579</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>521237</v>
+        <v>521241</v>
       </c>
       <c r="R55" t="n">
-        <v>7008806</v>
+        <v>7008805</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5939,10 +5939,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132934615</v>
+        <v>132934626</v>
       </c>
       <c r="B56" t="n">
-        <v>75417</v>
+        <v>79091</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5950,21 +5950,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1460</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>521138</v>
+        <v>521121</v>
       </c>
       <c r="R56" t="n">
-        <v>7008969</v>
+        <v>7009153</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6036,32 +6036,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132934558</v>
+        <v>132934532</v>
       </c>
       <c r="B57" t="n">
-        <v>92192</v>
+        <v>79091</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6071,10 +6071,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>521052</v>
+        <v>521183</v>
       </c>
       <c r="R57" t="n">
-        <v>7008845</v>
+        <v>7008817</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6133,10 +6133,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132934640</v>
+        <v>132934615</v>
       </c>
       <c r="B58" t="n">
-        <v>80438</v>
+        <v>75417</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6144,21 +6144,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521171</v>
+        <v>521138</v>
       </c>
       <c r="R58" t="n">
-        <v>7009092</v>
+        <v>7008969</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6230,32 +6230,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132934544</v>
+        <v>132934558</v>
       </c>
       <c r="B59" t="n">
-        <v>79090</v>
+        <v>92192</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>65</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6265,10 +6265,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>521030</v>
+        <v>521052</v>
       </c>
       <c r="R59" t="n">
-        <v>7008914</v>
+        <v>7008845</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6429,10 +6429,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132934626</v>
+        <v>132934640</v>
       </c>
       <c r="B61" t="n">
-        <v>79091</v>
+        <v>80438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6440,21 +6440,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6464,10 +6464,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>521121</v>
+        <v>521171</v>
       </c>
       <c r="R61" t="n">
-        <v>7009153</v>
+        <v>7009092</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6526,10 +6526,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132934532</v>
+        <v>132934544</v>
       </c>
       <c r="B62" t="n">
-        <v>79091</v>
+        <v>79090</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6537,21 +6537,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>521183</v>
+        <v>521030</v>
       </c>
       <c r="R62" t="n">
-        <v>7008817</v>
+        <v>7008914</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6623,32 +6623,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132934670</v>
+        <v>132934729</v>
       </c>
       <c r="B63" t="n">
-        <v>99130</v>
+        <v>83307</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>521175</v>
+        <v>521143</v>
       </c>
       <c r="R63" t="n">
-        <v>7009071</v>
+        <v>7008975</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6688,17 +6688,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>4st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6725,45 +6720,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132934522</v>
+        <v>132934724</v>
       </c>
       <c r="B64" t="n">
-        <v>79091</v>
+        <v>93206</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520949</v>
+        <v>521161</v>
       </c>
       <c r="R64" t="n">
-        <v>7008801</v>
+        <v>7008948</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6790,12 +6785,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6822,32 +6817,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132934633</v>
+        <v>132934660</v>
       </c>
       <c r="B65" t="n">
-        <v>80438</v>
+        <v>91846</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>2013</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6857,10 +6852,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>521131</v>
+        <v>521085</v>
       </c>
       <c r="R65" t="n">
-        <v>7009066</v>
+        <v>7008964</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6887,12 +6882,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6919,32 +6919,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132934602</v>
+        <v>132934709</v>
       </c>
       <c r="B66" t="n">
-        <v>80342</v>
+        <v>79333</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521128</v>
+        <v>521086</v>
       </c>
       <c r="R66" t="n">
-        <v>7009053</v>
+        <v>7009170</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7016,32 +7016,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132934729</v>
+        <v>132934670</v>
       </c>
       <c r="B67" t="n">
-        <v>83307</v>
+        <v>99130</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521143</v>
+        <v>521175</v>
       </c>
       <c r="R67" t="n">
-        <v>7008975</v>
+        <v>7009071</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7081,12 +7081,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7113,32 +7118,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934724</v>
+        <v>132934633</v>
       </c>
       <c r="B68" t="n">
-        <v>93206</v>
+        <v>80438</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7148,10 +7153,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521161</v>
+        <v>521131</v>
       </c>
       <c r="R68" t="n">
-        <v>7008948</v>
+        <v>7009066</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7210,32 +7215,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132934660</v>
+        <v>132934602</v>
       </c>
       <c r="B69" t="n">
-        <v>91846</v>
+        <v>80342</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2013</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7245,10 +7250,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>521085</v>
+        <v>521128</v>
       </c>
       <c r="R69" t="n">
-        <v>7008964</v>
+        <v>7009053</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7275,17 +7280,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Mikroskoperad</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7312,10 +7312,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132934709</v>
+        <v>132934522</v>
       </c>
       <c r="B70" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7323,34 +7323,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>521086</v>
+        <v>520949</v>
       </c>
       <c r="R70" t="n">
-        <v>7009170</v>
+        <v>7008801</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7409,10 +7409,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132934526</v>
+        <v>132934542</v>
       </c>
       <c r="B71" t="n">
-        <v>79091</v>
+        <v>79090</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7420,21 +7420,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>521142</v>
+        <v>520944</v>
       </c>
       <c r="R71" t="n">
-        <v>7008938</v>
+        <v>7008802</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7506,10 +7506,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132934542</v>
+        <v>132934646</v>
       </c>
       <c r="B72" t="n">
-        <v>79090</v>
+        <v>80438</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7517,34 +7517,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520944</v>
+        <v>521053</v>
       </c>
       <c r="R72" t="n">
-        <v>7008802</v>
+        <v>7008982</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7603,10 +7603,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132934646</v>
+        <v>132934618</v>
       </c>
       <c r="B73" t="n">
-        <v>80438</v>
+        <v>91971</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7614,21 +7614,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>521053</v>
+        <v>520999</v>
       </c>
       <c r="R73" t="n">
-        <v>7008982</v>
+        <v>7008967</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7700,10 +7700,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132934618</v>
+        <v>132934526</v>
       </c>
       <c r="B74" t="n">
-        <v>91971</v>
+        <v>79091</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7711,34 +7711,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520999</v>
+        <v>521142</v>
       </c>
       <c r="R74" t="n">
-        <v>7008967</v>
+        <v>7008938</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8676,45 +8676,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132934552</v>
+        <v>132934701</v>
       </c>
       <c r="B84" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>521056</v>
+        <v>521075</v>
       </c>
       <c r="R84" t="n">
-        <v>7009135</v>
+        <v>7009147</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8747,11 +8747,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Över 40 plantor</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8778,32 +8773,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934674</v>
+        <v>132934611</v>
       </c>
       <c r="B85" t="n">
-        <v>99130</v>
+        <v>80342</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8813,10 +8808,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521168</v>
+        <v>521191</v>
       </c>
       <c r="R85" t="n">
-        <v>7009069</v>
+        <v>7008824</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8849,11 +8844,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8880,10 +8870,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132934529</v>
+        <v>132934641</v>
       </c>
       <c r="B86" t="n">
-        <v>79091</v>
+        <v>80438</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8891,34 +8881,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>521186</v>
+        <v>521052</v>
       </c>
       <c r="R86" t="n">
-        <v>7008836</v>
+        <v>7009135</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8977,7 +8967,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132934611</v>
+        <v>132934604</v>
       </c>
       <c r="B87" t="n">
         <v>80342</v>
@@ -9012,10 +9002,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>521191</v>
+        <v>521079</v>
       </c>
       <c r="R87" t="n">
-        <v>7008824</v>
+        <v>7008865</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9074,10 +9064,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132934641</v>
+        <v>132934548</v>
       </c>
       <c r="B88" t="n">
-        <v>80438</v>
+        <v>79090</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9085,34 +9075,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>521052</v>
+        <v>521142</v>
       </c>
       <c r="R88" t="n">
-        <v>7009135</v>
+        <v>7008938</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9171,7 +9161,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132934604</v>
+        <v>132934514</v>
       </c>
       <c r="B89" t="n">
         <v>80342</v>
@@ -9202,14 +9192,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>521079</v>
+        <v>521008</v>
       </c>
       <c r="R89" t="n">
-        <v>7008865</v>
+        <v>7008813</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9268,32 +9258,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132934548</v>
+        <v>132934552</v>
       </c>
       <c r="B90" t="n">
-        <v>79090</v>
+        <v>99130</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9303,10 +9293,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>521142</v>
+        <v>521056</v>
       </c>
       <c r="R90" t="n">
-        <v>7008938</v>
+        <v>7009135</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9339,6 +9329,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Över 40 plantor</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9365,45 +9360,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934514</v>
+        <v>132934674</v>
       </c>
       <c r="B91" t="n">
-        <v>80342</v>
+        <v>99130</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521008</v>
+        <v>521168</v>
       </c>
       <c r="R91" t="n">
-        <v>7008813</v>
+        <v>7009069</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9436,6 +9431,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9462,10 +9462,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934701</v>
+        <v>132934529</v>
       </c>
       <c r="B92" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9473,34 +9473,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521075</v>
+        <v>521186</v>
       </c>
       <c r="R92" t="n">
-        <v>7009147</v>
+        <v>7008836</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132934680</v>
+        <v>132934525</v>
       </c>
       <c r="B15" t="n">
-        <v>57136</v>
+        <v>79091</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,34 +1947,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521010</v>
+        <v>521152</v>
       </c>
       <c r="R15" t="n">
-        <v>7008813</v>
+        <v>7008946</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2007,11 +2007,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1st födosökande</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2038,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132934525</v>
+        <v>132934680</v>
       </c>
       <c r="B16" t="n">
-        <v>79091</v>
+        <v>57136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,34 +2044,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521152</v>
+        <v>521010</v>
       </c>
       <c r="R16" t="n">
-        <v>7008946</v>
+        <v>7008813</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2109,6 +2104,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1st födosökande</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -5648,32 +5648,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132934730</v>
+        <v>132934631</v>
       </c>
       <c r="B53" t="n">
-        <v>101338</v>
+        <v>79091</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521062</v>
+        <v>521241</v>
       </c>
       <c r="R53" t="n">
-        <v>7009070</v>
+        <v>7008805</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5745,32 +5745,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132934647</v>
+        <v>132934730</v>
       </c>
       <c r="B54" t="n">
-        <v>78345</v>
+        <v>101338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228579</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>521237</v>
+        <v>521062</v>
       </c>
       <c r="R54" t="n">
-        <v>7008806</v>
+        <v>7009070</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132934631</v>
+        <v>132934647</v>
       </c>
       <c r="B55" t="n">
-        <v>79091</v>
+        <v>78345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5853,21 +5853,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>228579</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>521241</v>
+        <v>521237</v>
       </c>
       <c r="R55" t="n">
-        <v>7008805</v>
+        <v>7008806</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6623,32 +6623,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132934729</v>
+        <v>132934670</v>
       </c>
       <c r="B63" t="n">
-        <v>83307</v>
+        <v>99130</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>521143</v>
+        <v>521175</v>
       </c>
       <c r="R63" t="n">
-        <v>7008975</v>
+        <v>7009071</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6688,12 +6688,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6720,45 +6725,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132934724</v>
+        <v>132934522</v>
       </c>
       <c r="B64" t="n">
-        <v>93206</v>
+        <v>79091</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>521161</v>
+        <v>520949</v>
       </c>
       <c r="R64" t="n">
-        <v>7008948</v>
+        <v>7008801</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6785,12 +6790,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6817,32 +6822,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132934660</v>
+        <v>132934633</v>
       </c>
       <c r="B65" t="n">
-        <v>91846</v>
+        <v>80438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2013</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6852,10 +6857,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>521085</v>
+        <v>521131</v>
       </c>
       <c r="R65" t="n">
-        <v>7008964</v>
+        <v>7009066</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6882,17 +6887,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Mikroskoperad</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6919,32 +6919,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132934709</v>
+        <v>132934602</v>
       </c>
       <c r="B66" t="n">
-        <v>79333</v>
+        <v>80342</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521086</v>
+        <v>521128</v>
       </c>
       <c r="R66" t="n">
-        <v>7009170</v>
+        <v>7009053</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7016,32 +7016,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132934670</v>
+        <v>132934729</v>
       </c>
       <c r="B67" t="n">
-        <v>99130</v>
+        <v>83307</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521175</v>
+        <v>521143</v>
       </c>
       <c r="R67" t="n">
-        <v>7009071</v>
+        <v>7008975</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7081,17 +7081,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>4st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7118,32 +7113,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934633</v>
+        <v>132934724</v>
       </c>
       <c r="B68" t="n">
-        <v>80438</v>
+        <v>93206</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7153,10 +7148,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521131</v>
+        <v>521161</v>
       </c>
       <c r="R68" t="n">
-        <v>7009066</v>
+        <v>7008948</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7215,32 +7210,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132934602</v>
+        <v>132934660</v>
       </c>
       <c r="B69" t="n">
-        <v>80342</v>
+        <v>91846</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>2013</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7250,10 +7245,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>521128</v>
+        <v>521085</v>
       </c>
       <c r="R69" t="n">
-        <v>7009053</v>
+        <v>7008964</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7280,12 +7275,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7312,10 +7312,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132934522</v>
+        <v>132934709</v>
       </c>
       <c r="B70" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7323,34 +7323,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520949</v>
+        <v>521086</v>
       </c>
       <c r="R70" t="n">
-        <v>7008801</v>
+        <v>7009170</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7409,10 +7409,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132934542</v>
+        <v>132934526</v>
       </c>
       <c r="B71" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7420,21 +7420,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520944</v>
+        <v>521142</v>
       </c>
       <c r="R71" t="n">
-        <v>7008802</v>
+        <v>7008938</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7506,10 +7506,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132934646</v>
+        <v>132934542</v>
       </c>
       <c r="B72" t="n">
-        <v>80438</v>
+        <v>79090</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7517,34 +7517,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>521053</v>
+        <v>520944</v>
       </c>
       <c r="R72" t="n">
-        <v>7008982</v>
+        <v>7008802</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7603,10 +7603,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132934618</v>
+        <v>132934646</v>
       </c>
       <c r="B73" t="n">
-        <v>91971</v>
+        <v>80438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7614,21 +7614,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520999</v>
+        <v>521053</v>
       </c>
       <c r="R73" t="n">
-        <v>7008967</v>
+        <v>7008982</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7700,10 +7700,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132934526</v>
+        <v>132934618</v>
       </c>
       <c r="B74" t="n">
-        <v>79091</v>
+        <v>91971</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7711,34 +7711,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>521142</v>
+        <v>520999</v>
       </c>
       <c r="R74" t="n">
-        <v>7008938</v>
+        <v>7008967</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8676,45 +8676,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132934701</v>
+        <v>132934552</v>
       </c>
       <c r="B84" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>521075</v>
+        <v>521056</v>
       </c>
       <c r="R84" t="n">
-        <v>7009147</v>
+        <v>7009135</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8747,6 +8747,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Över 40 plantor</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8773,32 +8778,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934611</v>
+        <v>132934674</v>
       </c>
       <c r="B85" t="n">
-        <v>80342</v>
+        <v>99130</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8808,10 +8813,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521191</v>
+        <v>521168</v>
       </c>
       <c r="R85" t="n">
-        <v>7008824</v>
+        <v>7009069</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8844,6 +8849,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8870,10 +8880,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132934641</v>
+        <v>132934529</v>
       </c>
       <c r="B86" t="n">
-        <v>80438</v>
+        <v>79091</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8881,34 +8891,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>521052</v>
+        <v>521186</v>
       </c>
       <c r="R86" t="n">
-        <v>7009135</v>
+        <v>7008836</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8967,7 +8977,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132934604</v>
+        <v>132934611</v>
       </c>
       <c r="B87" t="n">
         <v>80342</v>
@@ -9002,10 +9012,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>521079</v>
+        <v>521191</v>
       </c>
       <c r="R87" t="n">
-        <v>7008865</v>
+        <v>7008824</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9064,10 +9074,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132934548</v>
+        <v>132934641</v>
       </c>
       <c r="B88" t="n">
-        <v>79090</v>
+        <v>80438</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9075,34 +9085,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>521142</v>
+        <v>521052</v>
       </c>
       <c r="R88" t="n">
-        <v>7008938</v>
+        <v>7009135</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9161,7 +9171,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132934514</v>
+        <v>132934604</v>
       </c>
       <c r="B89" t="n">
         <v>80342</v>
@@ -9192,14 +9202,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>521008</v>
+        <v>521079</v>
       </c>
       <c r="R89" t="n">
-        <v>7008813</v>
+        <v>7008865</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9258,32 +9268,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132934552</v>
+        <v>132934548</v>
       </c>
       <c r="B90" t="n">
-        <v>99130</v>
+        <v>79090</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9293,10 +9303,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>521056</v>
+        <v>521142</v>
       </c>
       <c r="R90" t="n">
-        <v>7009135</v>
+        <v>7008938</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9329,11 +9339,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Över 40 plantor</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9360,45 +9365,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934674</v>
+        <v>132934514</v>
       </c>
       <c r="B91" t="n">
-        <v>99130</v>
+        <v>80342</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521168</v>
+        <v>521008</v>
       </c>
       <c r="R91" t="n">
-        <v>7009069</v>
+        <v>7008813</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9431,11 +9436,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9462,10 +9462,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934529</v>
+        <v>132934701</v>
       </c>
       <c r="B92" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9473,34 +9473,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521186</v>
+        <v>521075</v>
       </c>
       <c r="R92" t="n">
-        <v>7008836</v>
+        <v>7009147</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9661,45 +9661,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934616</v>
+        <v>132934530</v>
       </c>
       <c r="B94" t="n">
-        <v>79357</v>
+        <v>79091</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521117</v>
+        <v>521248</v>
       </c>
       <c r="R94" t="n">
-        <v>7009023</v>
+        <v>7008805</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9758,32 +9758,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132934586</v>
+        <v>132934616</v>
       </c>
       <c r="B95" t="n">
-        <v>91918</v>
+        <v>79357</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>6434</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9793,10 +9793,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521068</v>
+        <v>521117</v>
       </c>
       <c r="R95" t="n">
-        <v>7009176</v>
+        <v>7009023</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9855,10 +9855,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132934530</v>
+        <v>132934586</v>
       </c>
       <c r="B96" t="n">
-        <v>79091</v>
+        <v>91918</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9866,34 +9866,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521248</v>
+        <v>521068</v>
       </c>
       <c r="R96" t="n">
-        <v>7008805</v>
+        <v>7009176</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9952,10 +9952,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132934630</v>
+        <v>132934571</v>
       </c>
       <c r="B97" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9963,21 +9963,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>521203</v>
+        <v>521202</v>
       </c>
       <c r="R97" t="n">
-        <v>7008836</v>
+        <v>7008859</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10049,32 +10049,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132934571</v>
+        <v>132934681</v>
       </c>
       <c r="B98" t="n">
-        <v>79952</v>
+        <v>106258</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>521202</v>
+        <v>521191</v>
       </c>
       <c r="R98" t="n">
-        <v>7008859</v>
+        <v>7008908</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10146,32 +10146,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132934681</v>
+        <v>132934630</v>
       </c>
       <c r="B99" t="n">
-        <v>106258</v>
+        <v>79091</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221144</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>521191</v>
+        <v>521203</v>
       </c>
       <c r="R99" t="n">
-        <v>7008908</v>
+        <v>7008836</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132934576</v>
       </c>
       <c r="B2" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132934515</v>
+        <v>132934567</v>
       </c>
       <c r="B3" t="n">
-        <v>80342</v>
+        <v>91883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521069</v>
+        <v>521236</v>
       </c>
       <c r="R3" t="n">
-        <v>7009143</v>
+        <v>7008806</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132934567</v>
+        <v>132934515</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>80343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521236</v>
+        <v>521069</v>
       </c>
       <c r="R4" t="n">
-        <v>7008806</v>
+        <v>7009143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>132934583</v>
       </c>
       <c r="B5" t="n">
-        <v>79923</v>
+        <v>79924</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>132934523</v>
       </c>
       <c r="B6" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>132934521</v>
       </c>
       <c r="B7" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132934572</v>
+        <v>132934612</v>
       </c>
       <c r="B8" t="n">
-        <v>79952</v>
+        <v>92380</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521188</v>
+        <v>521071</v>
       </c>
       <c r="R8" t="n">
-        <v>7008858</v>
+        <v>7009121</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132934612</v>
+        <v>132934601</v>
       </c>
       <c r="B9" t="n">
-        <v>92378</v>
+        <v>80305</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>388</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521071</v>
+        <v>521184</v>
       </c>
       <c r="R9" t="n">
-        <v>7009121</v>
+        <v>7009065</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132934601</v>
+        <v>132934572</v>
       </c>
       <c r="B10" t="n">
-        <v>80304</v>
+        <v>79953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>388</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521184</v>
+        <v>521188</v>
       </c>
       <c r="R10" t="n">
-        <v>7009065</v>
+        <v>7008858</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132934666</v>
+        <v>132934525</v>
       </c>
       <c r="B11" t="n">
-        <v>79090</v>
+        <v>79092</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521215</v>
+        <v>521152</v>
       </c>
       <c r="R11" t="n">
-        <v>7008844</v>
+        <v>7008946</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132934547</v>
+        <v>132934666</v>
       </c>
       <c r="B12" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,14 +1676,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521140</v>
+        <v>521215</v>
       </c>
       <c r="R12" t="n">
-        <v>7008998</v>
+        <v>7008844</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132934634</v>
+        <v>132934547</v>
       </c>
       <c r="B13" t="n">
-        <v>80438</v>
+        <v>79091</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,34 +1753,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521157</v>
+        <v>521140</v>
       </c>
       <c r="R13" t="n">
-        <v>7008985</v>
+        <v>7008998</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132934557</v>
+        <v>132934634</v>
       </c>
       <c r="B14" t="n">
-        <v>83181</v>
+        <v>80439</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,34 +1850,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521183</v>
+        <v>521157</v>
       </c>
       <c r="R14" t="n">
-        <v>7009052</v>
+        <v>7008985</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132934525</v>
+        <v>132934557</v>
       </c>
       <c r="B15" t="n">
-        <v>79091</v>
+        <v>83182</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521152</v>
+        <v>521183</v>
       </c>
       <c r="R15" t="n">
-        <v>7008946</v>
+        <v>7009052</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,7 +2138,7 @@
         <v>132934507</v>
       </c>
       <c r="B17" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>132934573</v>
       </c>
       <c r="B18" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>132934549</v>
       </c>
       <c r="B19" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132934569</v>
+        <v>132934690</v>
       </c>
       <c r="B20" t="n">
-        <v>79952</v>
+        <v>92094</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521055</v>
+        <v>521012</v>
       </c>
       <c r="R20" t="n">
-        <v>7008912</v>
+        <v>7008951</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132934574</v>
+        <v>132934620</v>
       </c>
       <c r="B21" t="n">
-        <v>79952</v>
+        <v>91973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2534,21 +2534,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521228</v>
+        <v>521239</v>
       </c>
       <c r="R21" t="n">
-        <v>7008805</v>
+        <v>7008816</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132934607</v>
+        <v>132934569</v>
       </c>
       <c r="B22" t="n">
-        <v>80342</v>
+        <v>79953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521198</v>
+        <v>521055</v>
       </c>
       <c r="R22" t="n">
-        <v>7008890</v>
+        <v>7008912</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132934690</v>
+        <v>132934574</v>
       </c>
       <c r="B23" t="n">
-        <v>92092</v>
+        <v>79953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521012</v>
+        <v>521228</v>
       </c>
       <c r="R23" t="n">
-        <v>7008951</v>
+        <v>7008805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,32 +2814,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132934620</v>
+        <v>132934607</v>
       </c>
       <c r="B24" t="n">
-        <v>91971</v>
+        <v>80343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2079</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521239</v>
+        <v>521198</v>
       </c>
       <c r="R24" t="n">
-        <v>7008816</v>
+        <v>7008890</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,32 +2911,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132934564</v>
+        <v>132934676</v>
       </c>
       <c r="B25" t="n">
-        <v>97370</v>
+        <v>99132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521171</v>
+        <v>521068</v>
       </c>
       <c r="R25" t="n">
-        <v>7009063</v>
+        <v>7009134</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2976,12 +2976,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3008,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132934613</v>
+        <v>132934564</v>
       </c>
       <c r="B26" t="n">
-        <v>92217</v>
+        <v>97372</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3019,21 +3024,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3043,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521069</v>
+        <v>521171</v>
       </c>
       <c r="R26" t="n">
-        <v>7009117</v>
+        <v>7009063</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3073,12 +3078,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3105,45 +3110,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132934559</v>
+        <v>132934613</v>
       </c>
       <c r="B27" t="n">
-        <v>92192</v>
+        <v>92219</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>65</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521072</v>
+        <v>521069</v>
       </c>
       <c r="R27" t="n">
-        <v>7009164</v>
+        <v>7009117</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3202,10 +3207,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132934676</v>
+        <v>132934559</v>
       </c>
       <c r="B28" t="n">
-        <v>99130</v>
+        <v>92194</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3213,34 +3218,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521068</v>
+        <v>521072</v>
       </c>
       <c r="R28" t="n">
-        <v>7009134</v>
+        <v>7009164</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3273,11 +3278,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3307,7 +3307,7 @@
         <v>132934534</v>
       </c>
       <c r="B29" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>132934664</v>
       </c>
       <c r="B30" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3503,32 +3503,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132934588</v>
+        <v>132934725</v>
       </c>
       <c r="B31" t="n">
-        <v>91918</v>
+        <v>93208</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521065</v>
+        <v>521171</v>
       </c>
       <c r="R31" t="n">
-        <v>7009134</v>
+        <v>7008936</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3600,45 +3600,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132934517</v>
+        <v>132934673</v>
       </c>
       <c r="B32" t="n">
-        <v>92217</v>
+        <v>99132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521068</v>
+        <v>521159</v>
       </c>
       <c r="R32" t="n">
-        <v>7009094</v>
+        <v>7008976</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3665,12 +3665,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>12st bladrosetter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3697,32 +3702,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132934598</v>
+        <v>132934679</v>
       </c>
       <c r="B33" t="n">
-        <v>80304</v>
+        <v>99132</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3737,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521134</v>
+        <v>521159</v>
       </c>
       <c r="R33" t="n">
-        <v>7009060</v>
+        <v>7009071</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3762,12 +3767,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>3st bladrosetter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3776,7 +3786,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3795,32 +3804,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132934725</v>
+        <v>132934588</v>
       </c>
       <c r="B34" t="n">
-        <v>93206</v>
+        <v>91920</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3830,10 +3839,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521171</v>
+        <v>521065</v>
       </c>
       <c r="R34" t="n">
-        <v>7008936</v>
+        <v>7009134</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3892,45 +3901,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132934673</v>
+        <v>132934517</v>
       </c>
       <c r="B35" t="n">
-        <v>99130</v>
+        <v>92219</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521159</v>
+        <v>521068</v>
       </c>
       <c r="R35" t="n">
-        <v>7008976</v>
+        <v>7009094</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3957,17 +3966,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>12st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3994,32 +3998,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132934679</v>
+        <v>132934598</v>
       </c>
       <c r="B36" t="n">
-        <v>99130</v>
+        <v>80305</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4033,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521159</v>
+        <v>521134</v>
       </c>
       <c r="R36" t="n">
-        <v>7009071</v>
+        <v>7009060</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4059,17 +4063,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>3st bladrosetter</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4078,6 +4077,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4096,10 +4096,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132934614</v>
+        <v>132934585</v>
       </c>
       <c r="B37" t="n">
-        <v>75417</v>
+        <v>91920</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4107,21 +4107,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4131,10 +4131,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521110</v>
+        <v>521047</v>
       </c>
       <c r="R37" t="n">
-        <v>7009041</v>
+        <v>7009108</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4193,10 +4193,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132934585</v>
+        <v>132934627</v>
       </c>
       <c r="B38" t="n">
-        <v>91918</v>
+        <v>79092</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4204,21 +4204,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521047</v>
+        <v>521207</v>
       </c>
       <c r="R38" t="n">
-        <v>7009108</v>
+        <v>7008846</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132934510</v>
+        <v>132934541</v>
       </c>
       <c r="B39" t="n">
-        <v>91918</v>
+        <v>79091</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4301,21 +4301,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>521051</v>
+        <v>521045</v>
       </c>
       <c r="R39" t="n">
-        <v>7009102</v>
+        <v>7008824</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4387,32 +4387,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132934566</v>
+        <v>132934614</v>
       </c>
       <c r="B40" t="n">
-        <v>91881</v>
+        <v>75417</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>1460</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>521207</v>
+        <v>521110</v>
       </c>
       <c r="R40" t="n">
-        <v>7008851</v>
+        <v>7009041</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132934541</v>
+        <v>132934704</v>
       </c>
       <c r="B41" t="n">
-        <v>79090</v>
+        <v>79334</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4495,34 +4495,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521045</v>
+        <v>521125</v>
       </c>
       <c r="R41" t="n">
-        <v>7008824</v>
+        <v>7009007</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4581,10 +4581,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132934704</v>
+        <v>132934642</v>
       </c>
       <c r="B42" t="n">
-        <v>79333</v>
+        <v>80439</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4592,21 +4592,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521125</v>
+        <v>521241</v>
       </c>
       <c r="R42" t="n">
-        <v>7009007</v>
+        <v>7008806</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4678,32 +4678,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132934642</v>
+        <v>132934606</v>
       </c>
       <c r="B43" t="n">
-        <v>80438</v>
+        <v>80343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521241</v>
+        <v>521194</v>
       </c>
       <c r="R43" t="n">
-        <v>7008806</v>
+        <v>7008902</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4775,10 +4775,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132934606</v>
+        <v>132934566</v>
       </c>
       <c r="B44" t="n">
-        <v>80342</v>
+        <v>91883</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4786,21 +4786,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521194</v>
+        <v>521207</v>
       </c>
       <c r="R44" t="n">
-        <v>7008902</v>
+        <v>7008851</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4872,10 +4872,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132934627</v>
+        <v>132934510</v>
       </c>
       <c r="B45" t="n">
-        <v>79091</v>
+        <v>91920</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4883,34 +4883,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>521207</v>
+        <v>521051</v>
       </c>
       <c r="R45" t="n">
-        <v>7008846</v>
+        <v>7009102</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4969,10 +4969,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132934506</v>
+        <v>132934545</v>
       </c>
       <c r="B46" t="n">
-        <v>97370</v>
+        <v>79091</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4980,21 +4980,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>521125</v>
+        <v>521006</v>
       </c>
       <c r="R46" t="n">
-        <v>7009003</v>
+        <v>7009011</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5066,10 +5066,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132934619</v>
+        <v>132934570</v>
       </c>
       <c r="B47" t="n">
-        <v>91971</v>
+        <v>79953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5077,21 +5077,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>521192</v>
+        <v>520978</v>
       </c>
       <c r="R47" t="n">
-        <v>7008832</v>
+        <v>7008880</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5163,32 +5163,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132934565</v>
+        <v>132934619</v>
       </c>
       <c r="B48" t="n">
-        <v>91881</v>
+        <v>91973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>521199</v>
+        <v>521192</v>
       </c>
       <c r="R48" t="n">
-        <v>7008837</v>
+        <v>7008832</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,45 +5260,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132934545</v>
+        <v>132934565</v>
       </c>
       <c r="B49" t="n">
-        <v>79090</v>
+        <v>91883</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>521006</v>
+        <v>521199</v>
       </c>
       <c r="R49" t="n">
-        <v>7009011</v>
+        <v>7008837</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,10 +5357,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132934570</v>
+        <v>132934506</v>
       </c>
       <c r="B50" t="n">
-        <v>79952</v>
+        <v>97372</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5368,34 +5368,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520978</v>
+        <v>521125</v>
       </c>
       <c r="R50" t="n">
-        <v>7008880</v>
+        <v>7009003</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5457,7 +5457,7 @@
         <v>132934610</v>
       </c>
       <c r="B51" t="n">
-        <v>80342</v>
+        <v>80343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>132934562</v>
       </c>
       <c r="B52" t="n">
-        <v>83315</v>
+        <v>83316</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5648,32 +5648,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132934631</v>
+        <v>132934730</v>
       </c>
       <c r="B53" t="n">
-        <v>79091</v>
+        <v>101340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521241</v>
+        <v>521062</v>
       </c>
       <c r="R53" t="n">
-        <v>7008805</v>
+        <v>7009070</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5745,32 +5745,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132934730</v>
+        <v>132934631</v>
       </c>
       <c r="B54" t="n">
-        <v>101338</v>
+        <v>79092</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>521062</v>
+        <v>521241</v>
       </c>
       <c r="R54" t="n">
-        <v>7009070</v>
+        <v>7008805</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5845,7 +5845,7 @@
         <v>132934647</v>
       </c>
       <c r="B55" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5939,45 +5939,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132934626</v>
+        <v>132934558</v>
       </c>
       <c r="B56" t="n">
-        <v>79091</v>
+        <v>92194</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>521121</v>
+        <v>521052</v>
       </c>
       <c r="R56" t="n">
-        <v>7009153</v>
+        <v>7008845</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6036,45 +6036,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132934532</v>
+        <v>132934675</v>
       </c>
       <c r="B57" t="n">
-        <v>79091</v>
+        <v>99132</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>521183</v>
+        <v>521056</v>
       </c>
       <c r="R57" t="n">
-        <v>7008817</v>
+        <v>7009075</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6107,6 +6107,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>8st bladrosetter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6133,10 +6138,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132934615</v>
+        <v>132934626</v>
       </c>
       <c r="B58" t="n">
-        <v>75417</v>
+        <v>79092</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6144,21 +6149,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1460</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6168,10 +6173,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521138</v>
+        <v>521121</v>
       </c>
       <c r="R58" t="n">
-        <v>7008969</v>
+        <v>7009153</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6230,32 +6235,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132934558</v>
+        <v>132934532</v>
       </c>
       <c r="B59" t="n">
-        <v>92192</v>
+        <v>79092</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6265,10 +6270,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>521052</v>
+        <v>521183</v>
       </c>
       <c r="R59" t="n">
-        <v>7008845</v>
+        <v>7008817</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6327,32 +6332,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132934675</v>
+        <v>132934615</v>
       </c>
       <c r="B60" t="n">
-        <v>99130</v>
+        <v>75417</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>1460</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6362,10 +6367,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>521056</v>
+        <v>521138</v>
       </c>
       <c r="R60" t="n">
-        <v>7009075</v>
+        <v>7008969</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6398,11 +6403,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>8st bladrosetter</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6432,7 +6432,7 @@
         <v>132934640</v>
       </c>
       <c r="B61" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>132934544</v>
       </c>
       <c r="B62" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6623,32 +6623,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132934670</v>
+        <v>132934724</v>
       </c>
       <c r="B63" t="n">
-        <v>99130</v>
+        <v>93208</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>521175</v>
+        <v>521161</v>
       </c>
       <c r="R63" t="n">
-        <v>7009071</v>
+        <v>7008948</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6694,11 +6694,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6725,45 +6720,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132934522</v>
+        <v>132934660</v>
       </c>
       <c r="B64" t="n">
-        <v>79091</v>
+        <v>91848</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>2013</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520949</v>
+        <v>521085</v>
       </c>
       <c r="R64" t="n">
-        <v>7008801</v>
+        <v>7008964</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6796,6 +6791,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6822,10 +6822,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132934633</v>
+        <v>132934709</v>
       </c>
       <c r="B65" t="n">
-        <v>80438</v>
+        <v>79334</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6833,21 +6833,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>521131</v>
+        <v>521086</v>
       </c>
       <c r="R65" t="n">
-        <v>7009066</v>
+        <v>7009170</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6919,32 +6919,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132934602</v>
+        <v>132934633</v>
       </c>
       <c r="B66" t="n">
-        <v>80342</v>
+        <v>80439</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521128</v>
+        <v>521131</v>
       </c>
       <c r="R66" t="n">
-        <v>7009053</v>
+        <v>7009066</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7016,32 +7016,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132934729</v>
+        <v>132934602</v>
       </c>
       <c r="B67" t="n">
-        <v>83307</v>
+        <v>80343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>308</v>
+        <v>6456</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521143</v>
+        <v>521128</v>
       </c>
       <c r="R67" t="n">
-        <v>7008975</v>
+        <v>7009053</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7081,12 +7081,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7113,32 +7113,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934724</v>
+        <v>132934670</v>
       </c>
       <c r="B68" t="n">
-        <v>93206</v>
+        <v>99132</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521161</v>
+        <v>521175</v>
       </c>
       <c r="R68" t="n">
-        <v>7008948</v>
+        <v>7009071</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7184,6 +7184,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7210,45 +7215,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132934660</v>
+        <v>132934522</v>
       </c>
       <c r="B69" t="n">
-        <v>91846</v>
+        <v>79092</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2013</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>521085</v>
+        <v>520949</v>
       </c>
       <c r="R69" t="n">
-        <v>7008964</v>
+        <v>7008801</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7281,11 +7286,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7312,10 +7312,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132934709</v>
+        <v>132934729</v>
       </c>
       <c r="B70" t="n">
-        <v>79333</v>
+        <v>83308</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7323,21 +7323,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>521086</v>
+        <v>521143</v>
       </c>
       <c r="R70" t="n">
-        <v>7009170</v>
+        <v>7008975</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7409,7 +7409,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132934526</v>
+        <v>132934542</v>
       </c>
       <c r="B71" t="n">
         <v>79091</v>
@@ -7420,21 +7420,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>521142</v>
+        <v>520944</v>
       </c>
       <c r="R71" t="n">
-        <v>7008938</v>
+        <v>7008802</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7506,10 +7506,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132934542</v>
+        <v>132934618</v>
       </c>
       <c r="B72" t="n">
-        <v>79090</v>
+        <v>91973</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7517,34 +7517,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520944</v>
+        <v>520999</v>
       </c>
       <c r="R72" t="n">
-        <v>7008802</v>
+        <v>7008967</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7606,7 +7606,7 @@
         <v>132934646</v>
       </c>
       <c r="B73" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7700,10 +7700,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132934618</v>
+        <v>132934526</v>
       </c>
       <c r="B74" t="n">
-        <v>91971</v>
+        <v>79092</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7711,34 +7711,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520999</v>
+        <v>521142</v>
       </c>
       <c r="R74" t="n">
-        <v>7008967</v>
+        <v>7008938</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7797,32 +7797,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132934671</v>
+        <v>132934702</v>
       </c>
       <c r="B75" t="n">
-        <v>99130</v>
+        <v>79334</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7832,10 +7832,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>521125</v>
+        <v>521069</v>
       </c>
       <c r="R75" t="n">
-        <v>7009063</v>
+        <v>7009122</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7862,17 +7862,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7902,7 +7897,7 @@
         <v>132934582</v>
       </c>
       <c r="B76" t="n">
-        <v>79923</v>
+        <v>79924</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7999,7 +7994,7 @@
         <v>132934528</v>
       </c>
       <c r="B77" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8096,7 +8091,7 @@
         <v>132934629</v>
       </c>
       <c r="B78" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8190,32 +8185,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132934702</v>
+        <v>132934671</v>
       </c>
       <c r="B79" t="n">
-        <v>79333</v>
+        <v>99132</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8225,10 +8220,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>521069</v>
+        <v>521125</v>
       </c>
       <c r="R79" t="n">
-        <v>7009122</v>
+        <v>7009063</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8255,12 +8250,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8287,10 +8287,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132934550</v>
+        <v>132934599</v>
       </c>
       <c r="B80" t="n">
-        <v>79090</v>
+        <v>80305</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8298,34 +8298,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>388</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>521248</v>
+        <v>521196</v>
       </c>
       <c r="R80" t="n">
-        <v>7008806</v>
+        <v>7008906</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8366,6 +8366,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8384,10 +8385,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132934575</v>
+        <v>132934703</v>
       </c>
       <c r="B81" t="n">
-        <v>79952</v>
+        <v>79334</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8395,21 +8396,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8419,10 +8420,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>521035</v>
+        <v>521068</v>
       </c>
       <c r="R81" t="n">
-        <v>7008820</v>
+        <v>7009094</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8481,10 +8482,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132934703</v>
+        <v>132934550</v>
       </c>
       <c r="B82" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8492,34 +8493,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>521068</v>
+        <v>521248</v>
       </c>
       <c r="R82" t="n">
-        <v>7009094</v>
+        <v>7008806</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8578,10 +8579,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132934599</v>
+        <v>132934575</v>
       </c>
       <c r="B83" t="n">
-        <v>80304</v>
+        <v>79953</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8589,21 +8590,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>388</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8613,10 +8614,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>521196</v>
+        <v>521035</v>
       </c>
       <c r="R83" t="n">
-        <v>7008906</v>
+        <v>7008820</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8657,7 +8658,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8676,45 +8676,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132934552</v>
+        <v>132934611</v>
       </c>
       <c r="B84" t="n">
-        <v>99130</v>
+        <v>80343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>521056</v>
+        <v>521191</v>
       </c>
       <c r="R84" t="n">
-        <v>7009135</v>
+        <v>7008824</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8747,11 +8747,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Över 40 plantor</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8778,32 +8773,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934674</v>
+        <v>132934641</v>
       </c>
       <c r="B85" t="n">
-        <v>99130</v>
+        <v>80439</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8813,10 +8808,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521168</v>
+        <v>521052</v>
       </c>
       <c r="R85" t="n">
-        <v>7009069</v>
+        <v>7009135</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8849,11 +8844,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8880,45 +8870,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132934529</v>
+        <v>132934604</v>
       </c>
       <c r="B86" t="n">
-        <v>79091</v>
+        <v>80343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>521186</v>
+        <v>521079</v>
       </c>
       <c r="R86" t="n">
-        <v>7008836</v>
+        <v>7008865</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8977,45 +8967,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132934611</v>
+        <v>132934548</v>
       </c>
       <c r="B87" t="n">
-        <v>80342</v>
+        <v>79091</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>521191</v>
+        <v>521142</v>
       </c>
       <c r="R87" t="n">
-        <v>7008824</v>
+        <v>7008938</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9074,45 +9064,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132934641</v>
+        <v>132934514</v>
       </c>
       <c r="B88" t="n">
-        <v>80438</v>
+        <v>80343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>521052</v>
+        <v>521008</v>
       </c>
       <c r="R88" t="n">
-        <v>7009135</v>
+        <v>7008813</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9171,32 +9161,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132934604</v>
+        <v>132934701</v>
       </c>
       <c r="B89" t="n">
-        <v>80342</v>
+        <v>79334</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9206,10 +9196,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>521079</v>
+        <v>521075</v>
       </c>
       <c r="R89" t="n">
-        <v>7008865</v>
+        <v>7009147</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9268,32 +9258,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132934548</v>
+        <v>132934552</v>
       </c>
       <c r="B90" t="n">
-        <v>79090</v>
+        <v>99132</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9303,10 +9293,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>521142</v>
+        <v>521056</v>
       </c>
       <c r="R90" t="n">
-        <v>7008938</v>
+        <v>7009135</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9339,6 +9329,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Över 40 plantor</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9365,45 +9360,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934514</v>
+        <v>132934674</v>
       </c>
       <c r="B91" t="n">
-        <v>80342</v>
+        <v>99132</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521008</v>
+        <v>521168</v>
       </c>
       <c r="R91" t="n">
-        <v>7008813</v>
+        <v>7009069</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9436,6 +9431,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9462,10 +9462,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934701</v>
+        <v>132934529</v>
       </c>
       <c r="B92" t="n">
-        <v>79333</v>
+        <v>79092</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9473,34 +9473,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521075</v>
+        <v>521186</v>
       </c>
       <c r="R92" t="n">
-        <v>7009147</v>
+        <v>7008836</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9562,7 +9562,7 @@
         <v>132934678</v>
       </c>
       <c r="B93" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>132934530</v>
       </c>
       <c r="B94" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>132934616</v>
       </c>
       <c r="B95" t="n">
-        <v>79357</v>
+        <v>79358</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>132934586</v>
       </c>
       <c r="B96" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>132934571</v>
       </c>
       <c r="B97" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>132934681</v>
       </c>
       <c r="B98" t="n">
-        <v>106258</v>
+        <v>106260</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>132934630</v>
       </c>
       <c r="B99" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>132934605</v>
       </c>
       <c r="B100" t="n">
-        <v>80342</v>
+        <v>80343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>132934728</v>
       </c>
       <c r="B101" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>132934533</v>
       </c>
       <c r="B102" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>132934551</v>
       </c>
       <c r="B103" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
         <v>132934600</v>
       </c>
       <c r="B104" t="n">
-        <v>80304</v>
+        <v>80305</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>132934513</v>
       </c>
       <c r="B105" t="n">
-        <v>80304</v>
+        <v>80305</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>132934677</v>
       </c>
       <c r="B106" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10933,10 +10933,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132934662</v>
+        <v>132934535</v>
       </c>
       <c r="B107" t="n">
-        <v>79090</v>
+        <v>78346</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10944,34 +10944,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>228579</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>520935</v>
+        <v>521079</v>
       </c>
       <c r="R107" t="n">
-        <v>7008801</v>
+        <v>7009088</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11030,10 +11030,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132934535</v>
+        <v>132934662</v>
       </c>
       <c r="B108" t="n">
-        <v>78345</v>
+        <v>79091</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11041,34 +11041,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228579</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>521079</v>
+        <v>520935</v>
       </c>
       <c r="R108" t="n">
-        <v>7009088</v>
+        <v>7008801</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11130,7 +11130,7 @@
         <v>132934691</v>
       </c>
       <c r="B109" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11224,45 +11224,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132934587</v>
+        <v>132934516</v>
       </c>
       <c r="B110" t="n">
-        <v>91918</v>
+        <v>80343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>521077</v>
+        <v>521131</v>
       </c>
       <c r="R110" t="n">
-        <v>7009118</v>
+        <v>7008987</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11324,7 +11324,7 @@
         <v>132934554</v>
       </c>
       <c r="B111" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>132934555</v>
       </c>
       <c r="B112" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11515,10 +11515,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132934516</v>
+        <v>132934609</v>
       </c>
       <c r="B113" t="n">
-        <v>80342</v>
+        <v>80343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11546,14 +11546,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>521131</v>
+        <v>521140</v>
       </c>
       <c r="R113" t="n">
-        <v>7008987</v>
+        <v>7009061</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11612,10 +11612,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132934609</v>
+        <v>132934726</v>
       </c>
       <c r="B114" t="n">
-        <v>80342</v>
+        <v>80474</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11623,21 +11623,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11647,10 +11647,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>521140</v>
+        <v>521240</v>
       </c>
       <c r="R114" t="n">
-        <v>7009061</v>
+        <v>7008810</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11677,12 +11677,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11709,32 +11709,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132934726</v>
+        <v>132934587</v>
       </c>
       <c r="B115" t="n">
-        <v>80473</v>
+        <v>91920</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11744,10 +11744,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>521240</v>
+        <v>521077</v>
       </c>
       <c r="R115" t="n">
-        <v>7008810</v>
+        <v>7009118</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11809,7 +11809,7 @@
         <v>132934524</v>
       </c>
       <c r="B116" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>132934531</v>
       </c>
       <c r="B117" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132934612</v>
+        <v>132934572</v>
       </c>
       <c r="B8" t="n">
-        <v>92380</v>
+        <v>79953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521071</v>
+        <v>521188</v>
       </c>
       <c r="R8" t="n">
-        <v>7009121</v>
+        <v>7008858</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132934601</v>
+        <v>132934612</v>
       </c>
       <c r="B9" t="n">
-        <v>80305</v>
+        <v>92380</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>388</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521184</v>
+        <v>521071</v>
       </c>
       <c r="R9" t="n">
-        <v>7009065</v>
+        <v>7009121</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132934572</v>
+        <v>132934601</v>
       </c>
       <c r="B10" t="n">
-        <v>79953</v>
+        <v>80305</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>388</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521188</v>
+        <v>521184</v>
       </c>
       <c r="R10" t="n">
-        <v>7008858</v>
+        <v>7009065</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132934525</v>
+        <v>132934666</v>
       </c>
       <c r="B11" t="n">
-        <v>79092</v>
+        <v>79091</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521152</v>
+        <v>521215</v>
       </c>
       <c r="R11" t="n">
-        <v>7008946</v>
+        <v>7008844</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132934666</v>
+        <v>132934547</v>
       </c>
       <c r="B12" t="n">
         <v>79091</v>
@@ -1676,14 +1676,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521215</v>
+        <v>521140</v>
       </c>
       <c r="R12" t="n">
-        <v>7008844</v>
+        <v>7008998</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132934547</v>
+        <v>132934634</v>
       </c>
       <c r="B13" t="n">
-        <v>79091</v>
+        <v>80439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,34 +1753,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521140</v>
+        <v>521157</v>
       </c>
       <c r="R13" t="n">
-        <v>7008998</v>
+        <v>7008985</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132934634</v>
+        <v>132934525</v>
       </c>
       <c r="B14" t="n">
-        <v>80439</v>
+        <v>79092</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,34 +1850,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521157</v>
+        <v>521152</v>
       </c>
       <c r="R14" t="n">
-        <v>7008985</v>
+        <v>7008946</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -4096,10 +4096,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132934585</v>
+        <v>132934541</v>
       </c>
       <c r="B37" t="n">
-        <v>91920</v>
+        <v>79091</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4107,34 +4107,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521047</v>
+        <v>521045</v>
       </c>
       <c r="R37" t="n">
-        <v>7009108</v>
+        <v>7008824</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4193,10 +4193,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132934627</v>
+        <v>132934614</v>
       </c>
       <c r="B38" t="n">
-        <v>79092</v>
+        <v>75417</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4204,21 +4204,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>1460</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521207</v>
+        <v>521110</v>
       </c>
       <c r="R38" t="n">
-        <v>7008846</v>
+        <v>7009041</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132934541</v>
+        <v>132934704</v>
       </c>
       <c r="B39" t="n">
-        <v>79091</v>
+        <v>79334</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4301,34 +4301,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>521045</v>
+        <v>521125</v>
       </c>
       <c r="R39" t="n">
-        <v>7008824</v>
+        <v>7009007</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4387,10 +4387,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132934614</v>
+        <v>132934642</v>
       </c>
       <c r="B40" t="n">
-        <v>75417</v>
+        <v>80439</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4398,21 +4398,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>521110</v>
+        <v>521241</v>
       </c>
       <c r="R40" t="n">
-        <v>7009041</v>
+        <v>7008806</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4484,32 +4484,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132934704</v>
+        <v>132934606</v>
       </c>
       <c r="B41" t="n">
-        <v>79334</v>
+        <v>80343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521125</v>
+        <v>521194</v>
       </c>
       <c r="R41" t="n">
-        <v>7009007</v>
+        <v>7008902</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4581,32 +4581,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132934642</v>
+        <v>132934566</v>
       </c>
       <c r="B42" t="n">
-        <v>80439</v>
+        <v>91883</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521241</v>
+        <v>521207</v>
       </c>
       <c r="R42" t="n">
-        <v>7008806</v>
+        <v>7008851</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4678,32 +4678,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132934606</v>
+        <v>132934627</v>
       </c>
       <c r="B43" t="n">
-        <v>80343</v>
+        <v>79092</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521194</v>
+        <v>521207</v>
       </c>
       <c r="R43" t="n">
-        <v>7008902</v>
+        <v>7008846</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4775,32 +4775,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132934566</v>
+        <v>132934585</v>
       </c>
       <c r="B44" t="n">
-        <v>91883</v>
+        <v>91920</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521207</v>
+        <v>521047</v>
       </c>
       <c r="R44" t="n">
-        <v>7008851</v>
+        <v>7009108</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -7113,32 +7113,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934670</v>
+        <v>132934729</v>
       </c>
       <c r="B68" t="n">
-        <v>99132</v>
+        <v>83308</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521175</v>
+        <v>521143</v>
       </c>
       <c r="R68" t="n">
-        <v>7009071</v>
+        <v>7008975</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7178,17 +7178,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>4st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7312,32 +7307,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132934729</v>
+        <v>132934670</v>
       </c>
       <c r="B70" t="n">
-        <v>83308</v>
+        <v>99132</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7347,10 +7342,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>521143</v>
+        <v>521175</v>
       </c>
       <c r="R70" t="n">
-        <v>7008975</v>
+        <v>7009071</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7377,12 +7372,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7894,32 +7894,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132934582</v>
+        <v>132934671</v>
       </c>
       <c r="B76" t="n">
-        <v>79924</v>
+        <v>99132</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>521102</v>
+        <v>521125</v>
       </c>
       <c r="R76" t="n">
-        <v>7009031</v>
+        <v>7009063</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7959,12 +7959,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -7991,10 +7996,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132934528</v>
+        <v>132934582</v>
       </c>
       <c r="B77" t="n">
-        <v>79092</v>
+        <v>79924</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8002,34 +8007,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>521188</v>
+        <v>521102</v>
       </c>
       <c r="R77" t="n">
-        <v>7008858</v>
+        <v>7009031</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8088,7 +8093,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132934629</v>
+        <v>132934528</v>
       </c>
       <c r="B78" t="n">
         <v>79092</v>
@@ -8119,14 +8124,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>521115</v>
+        <v>521188</v>
       </c>
       <c r="R78" t="n">
-        <v>7009027</v>
+        <v>7008858</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8185,32 +8190,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132934671</v>
+        <v>132934629</v>
       </c>
       <c r="B79" t="n">
-        <v>99132</v>
+        <v>79092</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8220,10 +8225,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>521125</v>
+        <v>521115</v>
       </c>
       <c r="R79" t="n">
-        <v>7009063</v>
+        <v>7009027</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8250,17 +8255,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9559,32 +9559,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934678</v>
+        <v>132934616</v>
       </c>
       <c r="B93" t="n">
-        <v>99132</v>
+        <v>79358</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521234</v>
+        <v>521117</v>
       </c>
       <c r="R93" t="n">
-        <v>7009077</v>
+        <v>7009023</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9630,11 +9630,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9661,45 +9656,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934530</v>
+        <v>132934678</v>
       </c>
       <c r="B94" t="n">
-        <v>79092</v>
+        <v>99132</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521248</v>
+        <v>521234</v>
       </c>
       <c r="R94" t="n">
-        <v>7008805</v>
+        <v>7009077</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9732,6 +9727,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9758,32 +9758,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132934616</v>
+        <v>132934586</v>
       </c>
       <c r="B95" t="n">
-        <v>79358</v>
+        <v>91920</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6434</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9793,10 +9793,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521117</v>
+        <v>521068</v>
       </c>
       <c r="R95" t="n">
-        <v>7009023</v>
+        <v>7009176</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9855,10 +9855,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132934586</v>
+        <v>132934530</v>
       </c>
       <c r="B96" t="n">
-        <v>91920</v>
+        <v>79092</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9866,34 +9866,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521068</v>
+        <v>521248</v>
       </c>
       <c r="R96" t="n">
-        <v>7009176</v>
+        <v>7008805</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10933,10 +10933,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132934535</v>
+        <v>132934662</v>
       </c>
       <c r="B107" t="n">
-        <v>78346</v>
+        <v>79091</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10944,34 +10944,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228579</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>521079</v>
+        <v>520935</v>
       </c>
       <c r="R107" t="n">
-        <v>7009088</v>
+        <v>7008801</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11030,10 +11030,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132934662</v>
+        <v>132934535</v>
       </c>
       <c r="B108" t="n">
-        <v>79091</v>
+        <v>78346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11041,34 +11041,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>228579</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>520935</v>
+        <v>521079</v>
       </c>
       <c r="R108" t="n">
-        <v>7008801</v>
+        <v>7009088</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11709,10 +11709,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132934587</v>
+        <v>132934524</v>
       </c>
       <c r="B115" t="n">
-        <v>91920</v>
+        <v>79092</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11720,34 +11720,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>521077</v>
+        <v>521010</v>
       </c>
       <c r="R115" t="n">
-        <v>7009118</v>
+        <v>7008924</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11806,7 +11806,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132934524</v>
+        <v>132934531</v>
       </c>
       <c r="B116" t="n">
         <v>79092</v>
@@ -11841,10 +11841,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>521010</v>
+        <v>521212</v>
       </c>
       <c r="R116" t="n">
-        <v>7008924</v>
+        <v>7008824</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11903,10 +11903,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132934531</v>
+        <v>132934587</v>
       </c>
       <c r="B117" t="n">
-        <v>79092</v>
+        <v>91920</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11914,34 +11914,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>521212</v>
+        <v>521077</v>
       </c>
       <c r="R117" t="n">
-        <v>7008824</v>
+        <v>7009118</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132934572</v>
+        <v>132934612</v>
       </c>
       <c r="B8" t="n">
-        <v>79953</v>
+        <v>92380</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521188</v>
+        <v>521071</v>
       </c>
       <c r="R8" t="n">
-        <v>7008858</v>
+        <v>7009121</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132934612</v>
+        <v>132934601</v>
       </c>
       <c r="B9" t="n">
-        <v>92380</v>
+        <v>80305</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>388</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521071</v>
+        <v>521184</v>
       </c>
       <c r="R9" t="n">
-        <v>7009121</v>
+        <v>7009065</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132934601</v>
+        <v>132934572</v>
       </c>
       <c r="B10" t="n">
-        <v>80305</v>
+        <v>79953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>388</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521184</v>
+        <v>521188</v>
       </c>
       <c r="R10" t="n">
-        <v>7009065</v>
+        <v>7008858</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2911,32 +2911,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132934676</v>
+        <v>132934564</v>
       </c>
       <c r="B25" t="n">
-        <v>99132</v>
+        <v>97372</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521068</v>
+        <v>521171</v>
       </c>
       <c r="R25" t="n">
-        <v>7009134</v>
+        <v>7009063</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2976,17 +2976,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3013,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132934564</v>
+        <v>132934613</v>
       </c>
       <c r="B26" t="n">
-        <v>97372</v>
+        <v>92219</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,21 +3019,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3048,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521171</v>
+        <v>521069</v>
       </c>
       <c r="R26" t="n">
-        <v>7009063</v>
+        <v>7009117</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3078,12 +3073,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3110,45 +3105,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132934613</v>
+        <v>132934559</v>
       </c>
       <c r="B27" t="n">
-        <v>92219</v>
+        <v>92194</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>65</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521069</v>
+        <v>521072</v>
       </c>
       <c r="R27" t="n">
-        <v>7009117</v>
+        <v>7009164</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3207,10 +3202,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132934559</v>
+        <v>132934676</v>
       </c>
       <c r="B28" t="n">
-        <v>92194</v>
+        <v>99132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3218,34 +3213,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>65</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521072</v>
+        <v>521068</v>
       </c>
       <c r="R28" t="n">
-        <v>7009164</v>
+        <v>7009134</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3278,6 +3273,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3304,10 +3304,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132934534</v>
+        <v>132934588</v>
       </c>
       <c r="B29" t="n">
-        <v>80439</v>
+        <v>91920</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3315,34 +3315,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521190</v>
+        <v>521065</v>
       </c>
       <c r="R29" t="n">
-        <v>7008892</v>
+        <v>7009134</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3375,11 +3375,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På sälghögstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3406,10 +3401,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132934664</v>
+        <v>132934517</v>
       </c>
       <c r="B30" t="n">
-        <v>79091</v>
+        <v>92219</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,34 +3412,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521186</v>
+        <v>521068</v>
       </c>
       <c r="R30" t="n">
-        <v>7008837</v>
+        <v>7009094</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,32 +3498,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132934725</v>
+        <v>132934598</v>
       </c>
       <c r="B31" t="n">
-        <v>93208</v>
+        <v>80305</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>388</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3533,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521171</v>
+        <v>521134</v>
       </c>
       <c r="R31" t="n">
-        <v>7008936</v>
+        <v>7009060</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3568,12 +3563,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3582,6 +3577,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3600,45 +3596,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132934673</v>
+        <v>132934534</v>
       </c>
       <c r="B32" t="n">
-        <v>99132</v>
+        <v>80439</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521159</v>
+        <v>521190</v>
       </c>
       <c r="R32" t="n">
-        <v>7008976</v>
+        <v>7008892</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3665,17 +3661,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>12st bladrosetter</t>
+          <t>På sälghögstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3702,32 +3698,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132934679</v>
+        <v>132934664</v>
       </c>
       <c r="B33" t="n">
-        <v>99132</v>
+        <v>79091</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3737,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521159</v>
+        <v>521186</v>
       </c>
       <c r="R33" t="n">
-        <v>7009071</v>
+        <v>7008837</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3773,11 +3769,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>3st bladrosetter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3804,32 +3795,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132934588</v>
+        <v>132934725</v>
       </c>
       <c r="B34" t="n">
-        <v>91920</v>
+        <v>93208</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3839,10 +3830,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521065</v>
+        <v>521171</v>
       </c>
       <c r="R34" t="n">
-        <v>7009134</v>
+        <v>7008936</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3901,45 +3892,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132934517</v>
+        <v>132934673</v>
       </c>
       <c r="B35" t="n">
-        <v>92219</v>
+        <v>99132</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521068</v>
+        <v>521159</v>
       </c>
       <c r="R35" t="n">
-        <v>7009094</v>
+        <v>7008976</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3966,12 +3957,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>12st bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3998,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132934598</v>
+        <v>132934679</v>
       </c>
       <c r="B36" t="n">
-        <v>80305</v>
+        <v>99132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4033,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521134</v>
+        <v>521159</v>
       </c>
       <c r="R36" t="n">
-        <v>7009060</v>
+        <v>7009071</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4063,12 +4059,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>3st bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4077,7 +4078,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -7113,32 +7113,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934729</v>
+        <v>132934670</v>
       </c>
       <c r="B68" t="n">
-        <v>83308</v>
+        <v>99132</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521143</v>
+        <v>521175</v>
       </c>
       <c r="R68" t="n">
-        <v>7008975</v>
+        <v>7009071</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7178,12 +7178,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7307,32 +7312,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132934670</v>
+        <v>132934729</v>
       </c>
       <c r="B70" t="n">
-        <v>99132</v>
+        <v>83308</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7342,10 +7347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>521175</v>
+        <v>521143</v>
       </c>
       <c r="R70" t="n">
-        <v>7009071</v>
+        <v>7008975</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7372,17 +7377,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>4st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7894,32 +7894,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132934671</v>
+        <v>132934582</v>
       </c>
       <c r="B76" t="n">
-        <v>99132</v>
+        <v>79924</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>521125</v>
+        <v>521102</v>
       </c>
       <c r="R76" t="n">
-        <v>7009063</v>
+        <v>7009031</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7959,17 +7959,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -7996,10 +7991,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132934582</v>
+        <v>132934528</v>
       </c>
       <c r="B77" t="n">
-        <v>79924</v>
+        <v>79092</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8007,34 +8002,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>521102</v>
+        <v>521188</v>
       </c>
       <c r="R77" t="n">
-        <v>7009031</v>
+        <v>7008858</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8093,7 +8088,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132934528</v>
+        <v>132934629</v>
       </c>
       <c r="B78" t="n">
         <v>79092</v>
@@ -8124,14 +8119,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>521188</v>
+        <v>521115</v>
       </c>
       <c r="R78" t="n">
-        <v>7008858</v>
+        <v>7009027</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8190,32 +8185,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132934629</v>
+        <v>132934671</v>
       </c>
       <c r="B79" t="n">
-        <v>79092</v>
+        <v>99132</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8225,10 +8220,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>521115</v>
+        <v>521125</v>
       </c>
       <c r="R79" t="n">
-        <v>7009027</v>
+        <v>7009063</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8255,12 +8250,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8287,10 +8287,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132934599</v>
+        <v>132934703</v>
       </c>
       <c r="B80" t="n">
-        <v>80305</v>
+        <v>79334</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8298,21 +8298,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8322,10 +8322,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>521196</v>
+        <v>521068</v>
       </c>
       <c r="R80" t="n">
-        <v>7008906</v>
+        <v>7009094</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8366,7 +8366,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8385,10 +8384,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132934703</v>
+        <v>132934550</v>
       </c>
       <c r="B81" t="n">
-        <v>79334</v>
+        <v>79091</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8396,34 +8395,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>521068</v>
+        <v>521248</v>
       </c>
       <c r="R81" t="n">
-        <v>7009094</v>
+        <v>7008806</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8482,10 +8481,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132934550</v>
+        <v>132934575</v>
       </c>
       <c r="B82" t="n">
-        <v>79091</v>
+        <v>79953</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8493,34 +8492,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>521248</v>
+        <v>521035</v>
       </c>
       <c r="R82" t="n">
-        <v>7008806</v>
+        <v>7008820</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8579,10 +8578,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132934575</v>
+        <v>132934599</v>
       </c>
       <c r="B83" t="n">
-        <v>79953</v>
+        <v>80305</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8590,21 +8589,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>388</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8614,10 +8613,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>521035</v>
+        <v>521196</v>
       </c>
       <c r="R83" t="n">
-        <v>7008820</v>
+        <v>7008906</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8658,6 +8657,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8676,45 +8676,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132934611</v>
+        <v>132934552</v>
       </c>
       <c r="B84" t="n">
-        <v>80343</v>
+        <v>99132</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>521191</v>
+        <v>521056</v>
       </c>
       <c r="R84" t="n">
-        <v>7008824</v>
+        <v>7009135</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8747,6 +8747,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Över 40 plantor</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8773,32 +8778,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934641</v>
+        <v>132934674</v>
       </c>
       <c r="B85" t="n">
-        <v>80439</v>
+        <v>99132</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8808,10 +8813,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521052</v>
+        <v>521168</v>
       </c>
       <c r="R85" t="n">
-        <v>7009135</v>
+        <v>7009069</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8844,6 +8849,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8870,45 +8880,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132934604</v>
+        <v>132934529</v>
       </c>
       <c r="B86" t="n">
-        <v>80343</v>
+        <v>79092</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>521079</v>
+        <v>521186</v>
       </c>
       <c r="R86" t="n">
-        <v>7008865</v>
+        <v>7008836</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8967,45 +8977,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132934548</v>
+        <v>132934611</v>
       </c>
       <c r="B87" t="n">
-        <v>79091</v>
+        <v>80343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>521142</v>
+        <v>521191</v>
       </c>
       <c r="R87" t="n">
-        <v>7008938</v>
+        <v>7008824</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9064,45 +9074,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132934514</v>
+        <v>132934641</v>
       </c>
       <c r="B88" t="n">
-        <v>80343</v>
+        <v>80439</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>521008</v>
+        <v>521052</v>
       </c>
       <c r="R88" t="n">
-        <v>7008813</v>
+        <v>7009135</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9161,32 +9171,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132934701</v>
+        <v>132934604</v>
       </c>
       <c r="B89" t="n">
-        <v>79334</v>
+        <v>80343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9196,10 +9206,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>521075</v>
+        <v>521079</v>
       </c>
       <c r="R89" t="n">
-        <v>7009147</v>
+        <v>7008865</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9258,32 +9268,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132934552</v>
+        <v>132934548</v>
       </c>
       <c r="B90" t="n">
-        <v>99132</v>
+        <v>79091</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9293,10 +9303,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>521056</v>
+        <v>521142</v>
       </c>
       <c r="R90" t="n">
-        <v>7009135</v>
+        <v>7008938</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9329,11 +9339,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Över 40 plantor</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9360,45 +9365,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934674</v>
+        <v>132934514</v>
       </c>
       <c r="B91" t="n">
-        <v>99132</v>
+        <v>80343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521168</v>
+        <v>521008</v>
       </c>
       <c r="R91" t="n">
-        <v>7009069</v>
+        <v>7008813</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9431,11 +9436,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9462,10 +9462,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934529</v>
+        <v>132934701</v>
       </c>
       <c r="B92" t="n">
-        <v>79092</v>
+        <v>79334</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9473,34 +9473,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521186</v>
+        <v>521075</v>
       </c>
       <c r="R92" t="n">
-        <v>7008836</v>
+        <v>7009147</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9559,32 +9559,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934616</v>
+        <v>132934678</v>
       </c>
       <c r="B93" t="n">
-        <v>79358</v>
+        <v>99132</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521117</v>
+        <v>521234</v>
       </c>
       <c r="R93" t="n">
-        <v>7009023</v>
+        <v>7009077</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9630,6 +9630,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9656,45 +9661,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934678</v>
+        <v>132934530</v>
       </c>
       <c r="B94" t="n">
-        <v>99132</v>
+        <v>79092</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521234</v>
+        <v>521248</v>
       </c>
       <c r="R94" t="n">
-        <v>7009077</v>
+        <v>7008805</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9727,11 +9732,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9758,32 +9758,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132934586</v>
+        <v>132934616</v>
       </c>
       <c r="B95" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>6434</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9793,10 +9793,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521068</v>
+        <v>521117</v>
       </c>
       <c r="R95" t="n">
-        <v>7009176</v>
+        <v>7009023</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9855,10 +9855,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132934530</v>
+        <v>132934586</v>
       </c>
       <c r="B96" t="n">
-        <v>79092</v>
+        <v>91920</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9866,34 +9866,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521248</v>
+        <v>521068</v>
       </c>
       <c r="R96" t="n">
-        <v>7008805</v>
+        <v>7009176</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10049,32 +10049,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132934681</v>
+        <v>132934630</v>
       </c>
       <c r="B98" t="n">
-        <v>106260</v>
+        <v>79092</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221144</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>521191</v>
+        <v>521203</v>
       </c>
       <c r="R98" t="n">
-        <v>7008908</v>
+        <v>7008836</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10146,32 +10146,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132934630</v>
+        <v>132934681</v>
       </c>
       <c r="B99" t="n">
-        <v>79092</v>
+        <v>106260</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>221144</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>521203</v>
+        <v>521191</v>
       </c>
       <c r="R99" t="n">
-        <v>7008836</v>
+        <v>7008908</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11709,10 +11709,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132934524</v>
+        <v>132934587</v>
       </c>
       <c r="B115" t="n">
-        <v>79092</v>
+        <v>91920</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11720,34 +11720,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>521010</v>
+        <v>521077</v>
       </c>
       <c r="R115" t="n">
-        <v>7008924</v>
+        <v>7009118</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11806,7 +11806,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132934531</v>
+        <v>132934524</v>
       </c>
       <c r="B116" t="n">
         <v>79092</v>
@@ -11841,10 +11841,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>521212</v>
+        <v>521010</v>
       </c>
       <c r="R116" t="n">
-        <v>7008824</v>
+        <v>7008924</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11903,10 +11903,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132934587</v>
+        <v>132934531</v>
       </c>
       <c r="B117" t="n">
-        <v>91920</v>
+        <v>79092</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11914,34 +11914,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>521077</v>
+        <v>521212</v>
       </c>
       <c r="R117" t="n">
-        <v>7009118</v>
+        <v>7008824</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132934576</v>
+        <v>132934567</v>
       </c>
       <c r="B2" t="n">
-        <v>79953</v>
+        <v>91891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521217</v>
+        <v>521236</v>
       </c>
       <c r="R2" t="n">
-        <v>7008823</v>
+        <v>7008806</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132934567</v>
+        <v>132934576</v>
       </c>
       <c r="B3" t="n">
-        <v>91883</v>
+        <v>79953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521236</v>
+        <v>521217</v>
       </c>
       <c r="R3" t="n">
-        <v>7008806</v>
+        <v>7008823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132934612</v>
+        <v>132934572</v>
       </c>
       <c r="B8" t="n">
-        <v>92380</v>
+        <v>79953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521071</v>
+        <v>521188</v>
       </c>
       <c r="R8" t="n">
-        <v>7009121</v>
+        <v>7008858</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132934601</v>
+        <v>132934612</v>
       </c>
       <c r="B9" t="n">
-        <v>80305</v>
+        <v>92388</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>388</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521184</v>
+        <v>521071</v>
       </c>
       <c r="R9" t="n">
-        <v>7009065</v>
+        <v>7009121</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132934572</v>
+        <v>132934601</v>
       </c>
       <c r="B10" t="n">
-        <v>79953</v>
+        <v>80305</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>388</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521188</v>
+        <v>521184</v>
       </c>
       <c r="R10" t="n">
-        <v>7008858</v>
+        <v>7009065</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132934666</v>
+        <v>132934634</v>
       </c>
       <c r="B11" t="n">
-        <v>79091</v>
+        <v>80439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521215</v>
+        <v>521157</v>
       </c>
       <c r="R11" t="n">
-        <v>7008844</v>
+        <v>7008985</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132934547</v>
+        <v>132934525</v>
       </c>
       <c r="B12" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521140</v>
+        <v>521152</v>
       </c>
       <c r="R12" t="n">
-        <v>7008998</v>
+        <v>7008946</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132934634</v>
+        <v>132934666</v>
       </c>
       <c r="B13" t="n">
-        <v>80439</v>
+        <v>79091</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521157</v>
+        <v>521215</v>
       </c>
       <c r="R13" t="n">
-        <v>7008985</v>
+        <v>7008844</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132934525</v>
+        <v>132934680</v>
       </c>
       <c r="B14" t="n">
-        <v>79092</v>
+        <v>57136</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,34 +1850,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521152</v>
+        <v>521010</v>
       </c>
       <c r="R14" t="n">
-        <v>7008946</v>
+        <v>7008813</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1910,6 +1910,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1st födosökande</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1936,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132934557</v>
+        <v>132934547</v>
       </c>
       <c r="B15" t="n">
-        <v>83182</v>
+        <v>79091</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521183</v>
+        <v>521140</v>
       </c>
       <c r="R15" t="n">
-        <v>7009052</v>
+        <v>7008998</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132934680</v>
+        <v>132934557</v>
       </c>
       <c r="B16" t="n">
-        <v>57136</v>
+        <v>83183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,34 +2049,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521010</v>
+        <v>521183</v>
       </c>
       <c r="R16" t="n">
-        <v>7008813</v>
+        <v>7009052</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2104,11 +2109,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1st födosökande</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2429,7 +2429,7 @@
         <v>132934690</v>
       </c>
       <c r="B20" t="n">
-        <v>92094</v>
+        <v>92102</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>132934620</v>
       </c>
       <c r="B21" t="n">
-        <v>91973</v>
+        <v>91981</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132934569</v>
+        <v>132934564</v>
       </c>
       <c r="B22" t="n">
-        <v>79953</v>
+        <v>97380</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521055</v>
+        <v>521171</v>
       </c>
       <c r="R22" t="n">
-        <v>7008912</v>
+        <v>7009063</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132934574</v>
+        <v>132934613</v>
       </c>
       <c r="B23" t="n">
-        <v>79953</v>
+        <v>92227</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521228</v>
+        <v>521069</v>
       </c>
       <c r="R23" t="n">
-        <v>7008805</v>
+        <v>7009117</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,45 +2814,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132934607</v>
+        <v>132934559</v>
       </c>
       <c r="B24" t="n">
-        <v>80343</v>
+        <v>92202</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>65</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521198</v>
+        <v>521072</v>
       </c>
       <c r="R24" t="n">
-        <v>7008890</v>
+        <v>7009164</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132934564</v>
+        <v>132934569</v>
       </c>
       <c r="B25" t="n">
-        <v>97372</v>
+        <v>79953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521171</v>
+        <v>521055</v>
       </c>
       <c r="R25" t="n">
-        <v>7009063</v>
+        <v>7008912</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2976,12 +2976,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3008,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132934613</v>
+        <v>132934574</v>
       </c>
       <c r="B26" t="n">
-        <v>92219</v>
+        <v>79953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3019,21 +3019,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521069</v>
+        <v>521228</v>
       </c>
       <c r="R26" t="n">
-        <v>7009117</v>
+        <v>7008805</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3105,45 +3105,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132934559</v>
+        <v>132934607</v>
       </c>
       <c r="B27" t="n">
-        <v>92194</v>
+        <v>80343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>65</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521072</v>
+        <v>521198</v>
       </c>
       <c r="R27" t="n">
-        <v>7009164</v>
+        <v>7008890</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3205,7 +3205,7 @@
         <v>132934676</v>
       </c>
       <c r="B28" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3304,10 +3304,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132934588</v>
+        <v>132934534</v>
       </c>
       <c r="B29" t="n">
-        <v>91920</v>
+        <v>80439</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3315,34 +3315,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521065</v>
+        <v>521190</v>
       </c>
       <c r="R29" t="n">
-        <v>7009134</v>
+        <v>7008892</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3375,6 +3375,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På sälghögstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3401,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132934517</v>
+        <v>132934664</v>
       </c>
       <c r="B30" t="n">
-        <v>92219</v>
+        <v>79091</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3412,34 +3417,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521068</v>
+        <v>521186</v>
       </c>
       <c r="R30" t="n">
-        <v>7009094</v>
+        <v>7008837</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3498,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132934598</v>
+        <v>132934588</v>
       </c>
       <c r="B31" t="n">
-        <v>80305</v>
+        <v>91928</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3509,21 +3514,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>388</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3533,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521134</v>
+        <v>521065</v>
       </c>
       <c r="R31" t="n">
-        <v>7009060</v>
+        <v>7009134</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3563,12 +3568,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3577,7 +3582,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3596,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132934534</v>
+        <v>132934517</v>
       </c>
       <c r="B32" t="n">
-        <v>80439</v>
+        <v>92227</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3607,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3631,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521190</v>
+        <v>521068</v>
       </c>
       <c r="R32" t="n">
-        <v>7008892</v>
+        <v>7009094</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3667,11 +3671,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På sälghögstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3698,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132934664</v>
+        <v>132934598</v>
       </c>
       <c r="B33" t="n">
-        <v>79091</v>
+        <v>80305</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3709,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>388</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3733,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521186</v>
+        <v>521134</v>
       </c>
       <c r="R33" t="n">
-        <v>7008837</v>
+        <v>7009060</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3763,12 +3762,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3777,6 +3776,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>132934725</v>
       </c>
       <c r="B34" t="n">
-        <v>93208</v>
+        <v>93216</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3892,10 +3892,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132934673</v>
+        <v>132934679</v>
       </c>
       <c r="B35" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>521159</v>
       </c>
       <c r="R35" t="n">
-        <v>7008976</v>
+        <v>7009071</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3957,17 +3957,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>12st bladrosetter</t>
+          <t>3st bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3994,10 +3994,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132934679</v>
+        <v>132934673</v>
       </c>
       <c r="B36" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>521159</v>
       </c>
       <c r="R36" t="n">
-        <v>7009071</v>
+        <v>7008976</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4059,17 +4059,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>3st bladrosetter</t>
+          <t>12st bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4193,10 +4193,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132934614</v>
+        <v>132934642</v>
       </c>
       <c r="B38" t="n">
-        <v>75417</v>
+        <v>80439</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4204,21 +4204,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521110</v>
+        <v>521241</v>
       </c>
       <c r="R38" t="n">
-        <v>7009041</v>
+        <v>7008806</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4290,32 +4290,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132934704</v>
+        <v>132934606</v>
       </c>
       <c r="B39" t="n">
-        <v>79334</v>
+        <v>80343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>521125</v>
+        <v>521194</v>
       </c>
       <c r="R39" t="n">
-        <v>7009007</v>
+        <v>7008902</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4387,10 +4387,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132934642</v>
+        <v>132934614</v>
       </c>
       <c r="B40" t="n">
-        <v>80439</v>
+        <v>75417</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4398,21 +4398,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>521241</v>
+        <v>521110</v>
       </c>
       <c r="R40" t="n">
-        <v>7008806</v>
+        <v>7009041</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4484,32 +4484,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132934606</v>
+        <v>132934585</v>
       </c>
       <c r="B41" t="n">
-        <v>80343</v>
+        <v>91928</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521194</v>
+        <v>521047</v>
       </c>
       <c r="R41" t="n">
-        <v>7008902</v>
+        <v>7009108</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4581,45 +4581,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132934566</v>
+        <v>132934510</v>
       </c>
       <c r="B42" t="n">
-        <v>91883</v>
+        <v>91928</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521207</v>
+        <v>521051</v>
       </c>
       <c r="R42" t="n">
-        <v>7008851</v>
+        <v>7009102</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132934627</v>
+        <v>132934704</v>
       </c>
       <c r="B43" t="n">
-        <v>79092</v>
+        <v>79334</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4689,21 +4689,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521207</v>
+        <v>521125</v>
       </c>
       <c r="R43" t="n">
-        <v>7008846</v>
+        <v>7009007</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4775,32 +4775,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132934585</v>
+        <v>132934566</v>
       </c>
       <c r="B44" t="n">
-        <v>91920</v>
+        <v>91891</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521047</v>
+        <v>521207</v>
       </c>
       <c r="R44" t="n">
-        <v>7009108</v>
+        <v>7008851</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4872,10 +4872,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132934510</v>
+        <v>132934627</v>
       </c>
       <c r="B45" t="n">
-        <v>91920</v>
+        <v>79092</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4883,34 +4883,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>521051</v>
+        <v>521207</v>
       </c>
       <c r="R45" t="n">
-        <v>7009102</v>
+        <v>7008846</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5163,10 +5163,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132934619</v>
+        <v>132934506</v>
       </c>
       <c r="B48" t="n">
-        <v>91973</v>
+        <v>97380</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5174,34 +5174,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>521192</v>
+        <v>521125</v>
       </c>
       <c r="R48" t="n">
-        <v>7008832</v>
+        <v>7009003</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,32 +5260,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132934565</v>
+        <v>132934619</v>
       </c>
       <c r="B49" t="n">
-        <v>91883</v>
+        <v>91981</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5295,10 +5295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>521199</v>
+        <v>521192</v>
       </c>
       <c r="R49" t="n">
-        <v>7008837</v>
+        <v>7008832</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,45 +5357,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132934506</v>
+        <v>132934565</v>
       </c>
       <c r="B50" t="n">
-        <v>97372</v>
+        <v>91891</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>521125</v>
+        <v>521199</v>
       </c>
       <c r="R50" t="n">
-        <v>7009003</v>
+        <v>7008837</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5554,7 +5554,7 @@
         <v>132934562</v>
       </c>
       <c r="B52" t="n">
-        <v>83316</v>
+        <v>83319</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>132934730</v>
       </c>
       <c r="B53" t="n">
-        <v>101340</v>
+        <v>101348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5939,45 +5939,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132934558</v>
+        <v>132934640</v>
       </c>
       <c r="B56" t="n">
-        <v>92194</v>
+        <v>80439</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>521052</v>
+        <v>521171</v>
       </c>
       <c r="R56" t="n">
-        <v>7008845</v>
+        <v>7009092</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6036,45 +6036,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132934675</v>
+        <v>132934544</v>
       </c>
       <c r="B57" t="n">
-        <v>99132</v>
+        <v>79091</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>521056</v>
+        <v>521030</v>
       </c>
       <c r="R57" t="n">
-        <v>7009075</v>
+        <v>7008914</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6107,11 +6107,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>8st bladrosetter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6138,10 +6133,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132934626</v>
+        <v>132934615</v>
       </c>
       <c r="B58" t="n">
-        <v>79092</v>
+        <v>75417</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6149,21 +6144,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>1460</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6173,10 +6168,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521121</v>
+        <v>521138</v>
       </c>
       <c r="R58" t="n">
-        <v>7009153</v>
+        <v>7008969</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6235,32 +6230,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132934532</v>
+        <v>132934558</v>
       </c>
       <c r="B59" t="n">
-        <v>79092</v>
+        <v>92202</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6270,10 +6265,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>521183</v>
+        <v>521052</v>
       </c>
       <c r="R59" t="n">
-        <v>7008817</v>
+        <v>7008845</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6332,32 +6327,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132934615</v>
+        <v>132934675</v>
       </c>
       <c r="B60" t="n">
-        <v>75417</v>
+        <v>99140</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1460</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6367,10 +6362,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>521138</v>
+        <v>521056</v>
       </c>
       <c r="R60" t="n">
-        <v>7008969</v>
+        <v>7009075</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6403,6 +6398,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>8st bladrosetter</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6429,10 +6429,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132934640</v>
+        <v>132934626</v>
       </c>
       <c r="B61" t="n">
-        <v>80439</v>
+        <v>79092</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6440,21 +6440,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6464,10 +6464,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>521171</v>
+        <v>521121</v>
       </c>
       <c r="R61" t="n">
-        <v>7009092</v>
+        <v>7009153</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6526,10 +6526,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132934544</v>
+        <v>132934532</v>
       </c>
       <c r="B62" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6537,21 +6537,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>521030</v>
+        <v>521183</v>
       </c>
       <c r="R62" t="n">
-        <v>7008914</v>
+        <v>7008817</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6623,32 +6623,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132934724</v>
+        <v>132934709</v>
       </c>
       <c r="B63" t="n">
-        <v>93208</v>
+        <v>79334</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>521161</v>
+        <v>521086</v>
       </c>
       <c r="R63" t="n">
-        <v>7008948</v>
+        <v>7009170</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6720,32 +6720,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132934660</v>
+        <v>132934633</v>
       </c>
       <c r="B64" t="n">
-        <v>91848</v>
+        <v>80439</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2013</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>521085</v>
+        <v>521131</v>
       </c>
       <c r="R64" t="n">
-        <v>7008964</v>
+        <v>7009066</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6785,17 +6785,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Mikroskoperad</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6822,32 +6817,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132934709</v>
+        <v>132934602</v>
       </c>
       <c r="B65" t="n">
-        <v>79334</v>
+        <v>80343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6857,10 +6852,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>521086</v>
+        <v>521128</v>
       </c>
       <c r="R65" t="n">
-        <v>7009170</v>
+        <v>7009053</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6887,12 +6882,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6919,10 +6914,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132934633</v>
+        <v>132934729</v>
       </c>
       <c r="B66" t="n">
-        <v>80439</v>
+        <v>83311</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6930,21 +6925,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6954,10 +6949,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521131</v>
+        <v>521143</v>
       </c>
       <c r="R66" t="n">
-        <v>7009066</v>
+        <v>7008975</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6984,12 +6979,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7016,10 +7011,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132934602</v>
+        <v>132934724</v>
       </c>
       <c r="B67" t="n">
-        <v>80343</v>
+        <v>93216</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7027,21 +7022,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7051,10 +7046,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521128</v>
+        <v>521161</v>
       </c>
       <c r="R67" t="n">
-        <v>7009053</v>
+        <v>7008948</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7113,32 +7108,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934670</v>
+        <v>132934660</v>
       </c>
       <c r="B68" t="n">
-        <v>99132</v>
+        <v>91856</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>2013</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7148,10 +7143,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521175</v>
+        <v>521085</v>
       </c>
       <c r="R68" t="n">
-        <v>7009071</v>
+        <v>7008964</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7178,17 +7173,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>4st bladrosetter</t>
+          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7215,45 +7210,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132934522</v>
+        <v>132934670</v>
       </c>
       <c r="B69" t="n">
-        <v>79092</v>
+        <v>99140</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520949</v>
+        <v>521175</v>
       </c>
       <c r="R69" t="n">
-        <v>7008801</v>
+        <v>7009071</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7280,12 +7275,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7312,10 +7312,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132934729</v>
+        <v>132934522</v>
       </c>
       <c r="B70" t="n">
-        <v>83308</v>
+        <v>79092</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7323,34 +7323,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>308</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>521143</v>
+        <v>520949</v>
       </c>
       <c r="R70" t="n">
-        <v>7008975</v>
+        <v>7008801</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7506,10 +7506,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132934618</v>
+        <v>132934646</v>
       </c>
       <c r="B72" t="n">
-        <v>91973</v>
+        <v>80439</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7517,21 +7517,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520999</v>
+        <v>521053</v>
       </c>
       <c r="R72" t="n">
-        <v>7008967</v>
+        <v>7008982</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7603,10 +7603,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132934646</v>
+        <v>132934618</v>
       </c>
       <c r="B73" t="n">
-        <v>80439</v>
+        <v>91981</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7614,21 +7614,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>521053</v>
+        <v>520999</v>
       </c>
       <c r="R73" t="n">
-        <v>7008982</v>
+        <v>7008967</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7894,32 +7894,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132934582</v>
+        <v>132934671</v>
       </c>
       <c r="B76" t="n">
-        <v>79924</v>
+        <v>99140</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>521102</v>
+        <v>521125</v>
       </c>
       <c r="R76" t="n">
-        <v>7009031</v>
+        <v>7009063</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7959,12 +7959,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -7991,10 +7996,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132934528</v>
+        <v>132934582</v>
       </c>
       <c r="B77" t="n">
-        <v>79092</v>
+        <v>79924</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8002,34 +8007,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>521188</v>
+        <v>521102</v>
       </c>
       <c r="R77" t="n">
-        <v>7008858</v>
+        <v>7009031</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8088,7 +8093,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132934629</v>
+        <v>132934528</v>
       </c>
       <c r="B78" t="n">
         <v>79092</v>
@@ -8119,14 +8124,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>521115</v>
+        <v>521188</v>
       </c>
       <c r="R78" t="n">
-        <v>7009027</v>
+        <v>7008858</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8185,32 +8190,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132934671</v>
+        <v>132934629</v>
       </c>
       <c r="B79" t="n">
-        <v>99132</v>
+        <v>79092</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8220,10 +8225,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>521125</v>
+        <v>521115</v>
       </c>
       <c r="R79" t="n">
-        <v>7009063</v>
+        <v>7009027</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8250,17 +8255,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8287,10 +8287,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132934703</v>
+        <v>132934575</v>
       </c>
       <c r="B80" t="n">
-        <v>79334</v>
+        <v>79953</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8298,21 +8298,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8322,10 +8322,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>521068</v>
+        <v>521035</v>
       </c>
       <c r="R80" t="n">
-        <v>7009094</v>
+        <v>7008820</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8384,10 +8384,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132934550</v>
+        <v>132934703</v>
       </c>
       <c r="B81" t="n">
-        <v>79091</v>
+        <v>79334</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8395,34 +8395,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>521248</v>
+        <v>521068</v>
       </c>
       <c r="R81" t="n">
-        <v>7008806</v>
+        <v>7009094</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8481,10 +8481,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132934575</v>
+        <v>132934599</v>
       </c>
       <c r="B82" t="n">
-        <v>79953</v>
+        <v>80305</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8492,21 +8492,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>388</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8516,10 +8516,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>521035</v>
+        <v>521196</v>
       </c>
       <c r="R82" t="n">
-        <v>7008820</v>
+        <v>7008906</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8560,6 +8560,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8578,10 +8579,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132934599</v>
+        <v>132934550</v>
       </c>
       <c r="B83" t="n">
-        <v>80305</v>
+        <v>79091</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8589,34 +8590,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>388</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>521196</v>
+        <v>521248</v>
       </c>
       <c r="R83" t="n">
-        <v>7008906</v>
+        <v>7008806</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8657,7 +8658,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8676,45 +8676,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132934552</v>
+        <v>132934611</v>
       </c>
       <c r="B84" t="n">
-        <v>99132</v>
+        <v>80343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>521056</v>
+        <v>521191</v>
       </c>
       <c r="R84" t="n">
-        <v>7009135</v>
+        <v>7008824</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8747,11 +8747,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Över 40 plantor</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8778,32 +8773,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934674</v>
+        <v>132934641</v>
       </c>
       <c r="B85" t="n">
-        <v>99132</v>
+        <v>80439</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8813,10 +8808,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521168</v>
+        <v>521052</v>
       </c>
       <c r="R85" t="n">
-        <v>7009069</v>
+        <v>7009135</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8849,11 +8844,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8880,45 +8870,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132934529</v>
+        <v>132934604</v>
       </c>
       <c r="B86" t="n">
-        <v>79092</v>
+        <v>80343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>521186</v>
+        <v>521079</v>
       </c>
       <c r="R86" t="n">
-        <v>7008836</v>
+        <v>7008865</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8977,45 +8967,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132934611</v>
+        <v>132934548</v>
       </c>
       <c r="B87" t="n">
-        <v>80343</v>
+        <v>79091</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>521191</v>
+        <v>521142</v>
       </c>
       <c r="R87" t="n">
-        <v>7008824</v>
+        <v>7008938</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9074,45 +9064,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132934641</v>
+        <v>132934514</v>
       </c>
       <c r="B88" t="n">
-        <v>80439</v>
+        <v>80343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>521052</v>
+        <v>521008</v>
       </c>
       <c r="R88" t="n">
-        <v>7009135</v>
+        <v>7008813</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9171,32 +9161,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132934604</v>
+        <v>132934701</v>
       </c>
       <c r="B89" t="n">
-        <v>80343</v>
+        <v>79334</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9206,10 +9196,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>521079</v>
+        <v>521075</v>
       </c>
       <c r="R89" t="n">
-        <v>7008865</v>
+        <v>7009147</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9268,45 +9258,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132934548</v>
+        <v>132934674</v>
       </c>
       <c r="B90" t="n">
-        <v>79091</v>
+        <v>99140</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>521142</v>
+        <v>521168</v>
       </c>
       <c r="R90" t="n">
-        <v>7008938</v>
+        <v>7009069</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9339,6 +9329,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9365,32 +9360,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934514</v>
+        <v>132934552</v>
       </c>
       <c r="B91" t="n">
-        <v>80343</v>
+        <v>99140</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9400,10 +9395,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521008</v>
+        <v>521056</v>
       </c>
       <c r="R91" t="n">
-        <v>7008813</v>
+        <v>7009135</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9436,6 +9431,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Över 40 plantor</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9462,10 +9462,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934701</v>
+        <v>132934529</v>
       </c>
       <c r="B92" t="n">
-        <v>79334</v>
+        <v>79092</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9473,34 +9473,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521075</v>
+        <v>521186</v>
       </c>
       <c r="R92" t="n">
-        <v>7009147</v>
+        <v>7008836</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9559,32 +9559,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934678</v>
+        <v>132934616</v>
       </c>
       <c r="B93" t="n">
-        <v>99132</v>
+        <v>79358</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521234</v>
+        <v>521117</v>
       </c>
       <c r="R93" t="n">
-        <v>7009077</v>
+        <v>7009023</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9630,11 +9630,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9661,45 +9656,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934530</v>
+        <v>132934678</v>
       </c>
       <c r="B94" t="n">
-        <v>79092</v>
+        <v>99140</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521248</v>
+        <v>521234</v>
       </c>
       <c r="R94" t="n">
-        <v>7008805</v>
+        <v>7009077</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9732,6 +9727,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9758,45 +9758,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132934616</v>
+        <v>132934530</v>
       </c>
       <c r="B95" t="n">
-        <v>79358</v>
+        <v>79092</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521117</v>
+        <v>521248</v>
       </c>
       <c r="R95" t="n">
-        <v>7009023</v>
+        <v>7008805</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9858,7 +9858,7 @@
         <v>132934586</v>
       </c>
       <c r="B96" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9952,32 +9952,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132934571</v>
+        <v>132934681</v>
       </c>
       <c r="B97" t="n">
-        <v>79953</v>
+        <v>106268</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>521202</v>
+        <v>521191</v>
       </c>
       <c r="R97" t="n">
-        <v>7008859</v>
+        <v>7008908</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10146,32 +10146,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132934681</v>
+        <v>132934571</v>
       </c>
       <c r="B99" t="n">
-        <v>106260</v>
+        <v>79953</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>521191</v>
+        <v>521202</v>
       </c>
       <c r="R99" t="n">
-        <v>7008908</v>
+        <v>7008859</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10437,45 +10437,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132934533</v>
+        <v>132934677</v>
       </c>
       <c r="B102" t="n">
-        <v>80439</v>
+        <v>99140</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>521124</v>
+        <v>521070</v>
       </c>
       <c r="R102" t="n">
-        <v>7008989</v>
+        <v>7009057</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10512,7 +10512,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>På låga av sälg</t>
+          <t>&gt;30 bladrosetter</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10539,10 +10539,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132934551</v>
+        <v>132934533</v>
       </c>
       <c r="B103" t="n">
-        <v>79091</v>
+        <v>80439</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10550,21 +10550,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10574,10 +10574,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>521211</v>
+        <v>521124</v>
       </c>
       <c r="R103" t="n">
-        <v>7008824</v>
+        <v>7008989</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10610,6 +10610,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På låga av sälg</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10636,10 +10641,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132934600</v>
+        <v>132934551</v>
       </c>
       <c r="B104" t="n">
-        <v>80305</v>
+        <v>79091</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10647,34 +10652,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>388</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>521188</v>
+        <v>521211</v>
       </c>
       <c r="R104" t="n">
-        <v>7008835</v>
+        <v>7008824</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10715,7 +10720,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -10734,7 +10738,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132934513</v>
+        <v>132934600</v>
       </c>
       <c r="B105" t="n">
         <v>80305</v>
@@ -10765,14 +10769,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>521186</v>
+        <v>521188</v>
       </c>
       <c r="R105" t="n">
-        <v>7009049</v>
+        <v>7008835</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10813,6 +10817,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -10831,45 +10836,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132934677</v>
+        <v>132934513</v>
       </c>
       <c r="B106" t="n">
-        <v>99132</v>
+        <v>80305</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>521070</v>
+        <v>521186</v>
       </c>
       <c r="R106" t="n">
-        <v>7009057</v>
+        <v>7009049</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10902,11 +10907,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>&gt;30 bladrosetter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11127,45 +11127,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132934691</v>
+        <v>132934516</v>
       </c>
       <c r="B109" t="n">
-        <v>92094</v>
+        <v>80343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1503</v>
+        <v>6456</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>521092</v>
+        <v>521131</v>
       </c>
       <c r="R109" t="n">
-        <v>7009170</v>
+        <v>7008987</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11224,7 +11224,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132934516</v>
+        <v>132934609</v>
       </c>
       <c r="B110" t="n">
         <v>80343</v>
@@ -11255,14 +11255,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>521131</v>
+        <v>521140</v>
       </c>
       <c r="R110" t="n">
-        <v>7008987</v>
+        <v>7009061</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11289,12 +11289,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11321,45 +11321,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132934554</v>
+        <v>132934726</v>
       </c>
       <c r="B111" t="n">
-        <v>92094</v>
+        <v>80474</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1503</v>
+        <v>6463</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>521105</v>
+        <v>521240</v>
       </c>
       <c r="R111" t="n">
-        <v>7009010</v>
+        <v>7008810</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11418,10 +11418,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132934555</v>
+        <v>132934691</v>
       </c>
       <c r="B112" t="n">
-        <v>92094</v>
+        <v>92102</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11449,14 +11449,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>521211</v>
+        <v>521092</v>
       </c>
       <c r="R112" t="n">
-        <v>7008839</v>
+        <v>7009170</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11515,32 +11515,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132934609</v>
+        <v>132934587</v>
       </c>
       <c r="B113" t="n">
-        <v>80343</v>
+        <v>91928</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11550,10 +11550,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>521140</v>
+        <v>521077</v>
       </c>
       <c r="R113" t="n">
-        <v>7009061</v>
+        <v>7009118</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11612,45 +11612,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132934726</v>
+        <v>132934554</v>
       </c>
       <c r="B114" t="n">
-        <v>80474</v>
+        <v>92102</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6463</v>
+        <v>1503</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>521240</v>
+        <v>521105</v>
       </c>
       <c r="R114" t="n">
-        <v>7008810</v>
+        <v>7009010</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11709,45 +11709,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132934587</v>
+        <v>132934555</v>
       </c>
       <c r="B115" t="n">
-        <v>91920</v>
+        <v>92102</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>1503</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>521077</v>
+        <v>521211</v>
       </c>
       <c r="R115" t="n">
-        <v>7009118</v>
+        <v>7008839</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -12003,7 +12003,7 @@
         <v>132934592</v>
       </c>
       <c r="B118" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>132934594</v>
       </c>
       <c r="B119" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>132934590</v>
       </c>
       <c r="B120" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>132934591</v>
       </c>
       <c r="B121" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>132934593</v>
       </c>
       <c r="B122" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -12003,7 +12003,7 @@
         <v>132934592</v>
       </c>
       <c r="B118" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>132934594</v>
       </c>
       <c r="B119" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>132934590</v>
       </c>
       <c r="B120" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>132934591</v>
       </c>
       <c r="B121" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>132934593</v>
       </c>
       <c r="B122" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY122"/>
+  <dimension ref="A1:AY132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132934567</v>
+        <v>132934506</v>
       </c>
       <c r="B2" t="n">
-        <v>91891</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521236</v>
+        <v>521125</v>
       </c>
       <c r="R2" t="n">
-        <v>7008806</v>
+        <v>7009003</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132934576</v>
+        <v>132934564</v>
       </c>
       <c r="B3" t="n">
-        <v>79953</v>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521217</v>
+        <v>521171</v>
       </c>
       <c r="R3" t="n">
-        <v>7008823</v>
+        <v>7009063</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132934515</v>
+        <v>132934558</v>
       </c>
       <c r="B4" t="n">
-        <v>80343</v>
+        <v>92220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521069</v>
+        <v>521052</v>
       </c>
       <c r="R4" t="n">
-        <v>7009143</v>
+        <v>7008845</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,45 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132934583</v>
+        <v>132934559</v>
       </c>
       <c r="B5" t="n">
-        <v>79924</v>
+        <v>92220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521109</v>
+        <v>521072</v>
       </c>
       <c r="R5" t="n">
-        <v>7009014</v>
+        <v>7009164</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132934523</v>
+        <v>132934729</v>
       </c>
       <c r="B6" t="n">
-        <v>79092</v>
+        <v>83350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521025</v>
+        <v>521143</v>
       </c>
       <c r="R6" t="n">
-        <v>7008930</v>
+        <v>7008975</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132934521</v>
+        <v>132934513</v>
       </c>
       <c r="B7" t="n">
-        <v>79092</v>
+        <v>80344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>388</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521045</v>
+        <v>521186</v>
       </c>
       <c r="R7" t="n">
-        <v>7008824</v>
+        <v>7009049</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132934572</v>
+        <v>132934598</v>
       </c>
       <c r="B8" t="n">
-        <v>79953</v>
+        <v>80344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>388</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521188</v>
+        <v>521134</v>
       </c>
       <c r="R8" t="n">
-        <v>7008858</v>
+        <v>7009060</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1336,6 +1336,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1354,32 +1355,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132934612</v>
+        <v>132934599</v>
       </c>
       <c r="B9" t="n">
-        <v>92388</v>
+        <v>80344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>388</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521071</v>
+        <v>521196</v>
       </c>
       <c r="R9" t="n">
-        <v>7009121</v>
+        <v>7008906</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1433,6 +1434,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1451,10 +1453,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132934601</v>
+        <v>132934600</v>
       </c>
       <c r="B10" t="n">
-        <v>80305</v>
+        <v>80344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1488,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521184</v>
+        <v>521188</v>
       </c>
       <c r="R10" t="n">
-        <v>7009065</v>
+        <v>7008835</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1530,6 +1532,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1548,10 +1551,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132934634</v>
+        <v>132934601</v>
       </c>
       <c r="B11" t="n">
-        <v>80439</v>
+        <v>80344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1562,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1586,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521157</v>
+        <v>521184</v>
       </c>
       <c r="R11" t="n">
-        <v>7008985</v>
+        <v>7009065</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1613,12 +1616,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1645,10 +1648,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132934525</v>
+        <v>132934517</v>
       </c>
       <c r="B12" t="n">
-        <v>79092</v>
+        <v>92245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1659,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1683,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521152</v>
+        <v>521068</v>
       </c>
       <c r="R12" t="n">
-        <v>7008946</v>
+        <v>7009094</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1745,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132934666</v>
+        <v>132934613</v>
       </c>
       <c r="B13" t="n">
-        <v>79091</v>
+        <v>92245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1756,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1780,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521215</v>
+        <v>521069</v>
       </c>
       <c r="R13" t="n">
-        <v>7008844</v>
+        <v>7009117</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1842,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132934680</v>
+        <v>132934510</v>
       </c>
       <c r="B14" t="n">
-        <v>57136</v>
+        <v>91974</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,34 +1853,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521010</v>
+        <v>521051</v>
       </c>
       <c r="R14" t="n">
-        <v>7008813</v>
+        <v>7009102</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1910,11 +1913,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1st födosökande</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,10 +1939,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132934547</v>
+        <v>132934585</v>
       </c>
       <c r="B15" t="n">
-        <v>79091</v>
+        <v>91974</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,34 +1950,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521140</v>
+        <v>521047</v>
       </c>
       <c r="R15" t="n">
-        <v>7008998</v>
+        <v>7009108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,10 +2036,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132934557</v>
+        <v>132934586</v>
       </c>
       <c r="B16" t="n">
-        <v>83183</v>
+        <v>91974</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,34 +2047,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521183</v>
+        <v>521068</v>
       </c>
       <c r="R16" t="n">
-        <v>7009052</v>
+        <v>7009176</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,10 +2133,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132934507</v>
+        <v>132934587</v>
       </c>
       <c r="B17" t="n">
-        <v>79953</v>
+        <v>91974</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,34 +2144,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521249</v>
+        <v>521077</v>
       </c>
       <c r="R17" t="n">
-        <v>7008816</v>
+        <v>7009118</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2230,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132934573</v>
+        <v>132934588</v>
       </c>
       <c r="B18" t="n">
-        <v>79953</v>
+        <v>91974</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2241,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2265,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521194</v>
+        <v>521065</v>
       </c>
       <c r="R18" t="n">
-        <v>7008852</v>
+        <v>7009134</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,10 +2327,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132934549</v>
+        <v>132934612</v>
       </c>
       <c r="B19" t="n">
-        <v>79091</v>
+        <v>92406</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,34 +2338,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521186</v>
+        <v>521071</v>
       </c>
       <c r="R19" t="n">
-        <v>7008836</v>
+        <v>7009121</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2426,45 +2424,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132934690</v>
+        <v>132934557</v>
       </c>
       <c r="B20" t="n">
-        <v>92102</v>
+        <v>83222</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1503</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521012</v>
+        <v>521183</v>
       </c>
       <c r="R20" t="n">
-        <v>7008951</v>
+        <v>7009052</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2523,10 +2521,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132934620</v>
+        <v>132934614</v>
       </c>
       <c r="B21" t="n">
-        <v>91981</v>
+        <v>75452</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2534,21 +2532,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2079</v>
+        <v>1460</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2556,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521239</v>
+        <v>521110</v>
       </c>
       <c r="R21" t="n">
-        <v>7008816</v>
+        <v>7009041</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2620,10 +2618,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132934564</v>
+        <v>132934615</v>
       </c>
       <c r="B22" t="n">
-        <v>97380</v>
+        <v>75452</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2631,21 +2629,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1460</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2653,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521171</v>
+        <v>521138</v>
       </c>
       <c r="R22" t="n">
-        <v>7009063</v>
+        <v>7008969</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,12 +2683,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2717,45 +2715,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132934613</v>
+        <v>132934554</v>
       </c>
       <c r="B23" t="n">
-        <v>92227</v>
+        <v>92153</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1503</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521069</v>
+        <v>521105</v>
       </c>
       <c r="R23" t="n">
-        <v>7009117</v>
+        <v>7009010</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,10 +2812,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132934559</v>
+        <v>132934555</v>
       </c>
       <c r="B24" t="n">
-        <v>92202</v>
+        <v>92153</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2825,21 +2823,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2847,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521072</v>
+        <v>521211</v>
       </c>
       <c r="R24" t="n">
-        <v>7009164</v>
+        <v>7008839</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,32 +2909,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132934569</v>
+        <v>132934690</v>
       </c>
       <c r="B25" t="n">
-        <v>79953</v>
+        <v>92153</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,10 +2944,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521055</v>
+        <v>521012</v>
       </c>
       <c r="R25" t="n">
-        <v>7008912</v>
+        <v>7008951</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3008,32 +3006,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132934574</v>
+        <v>132934691</v>
       </c>
       <c r="B26" t="n">
-        <v>79953</v>
+        <v>92153</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3043,10 +3041,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521228</v>
+        <v>521092</v>
       </c>
       <c r="R26" t="n">
-        <v>7008805</v>
+        <v>7009170</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3105,32 +3103,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132934607</v>
+        <v>132934660</v>
       </c>
       <c r="B27" t="n">
-        <v>80343</v>
+        <v>91902</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>2013</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3140,10 +3138,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521198</v>
+        <v>521085</v>
       </c>
       <c r="R27" t="n">
-        <v>7008890</v>
+        <v>7008964</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3176,6 +3174,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3202,32 +3205,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132934676</v>
+        <v>132934618</v>
       </c>
       <c r="B28" t="n">
-        <v>99140</v>
+        <v>92027</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3237,10 +3240,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521068</v>
+        <v>520999</v>
       </c>
       <c r="R28" t="n">
-        <v>7009134</v>
+        <v>7008967</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3273,11 +3276,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3304,10 +3302,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132934534</v>
+        <v>132934619</v>
       </c>
       <c r="B29" t="n">
-        <v>80439</v>
+        <v>92027</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3315,34 +3313,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521190</v>
+        <v>521192</v>
       </c>
       <c r="R29" t="n">
-        <v>7008892</v>
+        <v>7008832</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3375,11 +3373,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På sälghögstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3406,10 +3399,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132934664</v>
+        <v>132934620</v>
       </c>
       <c r="B30" t="n">
-        <v>79091</v>
+        <v>92027</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3410,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3434,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521186</v>
+        <v>521239</v>
       </c>
       <c r="R30" t="n">
-        <v>7008837</v>
+        <v>7008816</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,10 +3496,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132934588</v>
+        <v>132934724</v>
       </c>
       <c r="B31" t="n">
-        <v>91928</v>
+        <v>93271</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,21 +3507,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3531,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521065</v>
+        <v>521161</v>
       </c>
       <c r="R31" t="n">
-        <v>7009134</v>
+        <v>7008948</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3568,12 +3561,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3600,10 +3593,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132934517</v>
+        <v>132934725</v>
       </c>
       <c r="B32" t="n">
-        <v>92227</v>
+        <v>93271</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,34 +3604,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521068</v>
+        <v>521171</v>
       </c>
       <c r="R32" t="n">
-        <v>7009094</v>
+        <v>7008936</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,32 +3690,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132934598</v>
+        <v>132934565</v>
       </c>
       <c r="B33" t="n">
-        <v>80305</v>
+        <v>91937</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>388</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3725,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521134</v>
+        <v>521199</v>
       </c>
       <c r="R33" t="n">
-        <v>7009060</v>
+        <v>7008837</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3762,12 +3755,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3776,7 +3769,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3795,10 +3787,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132934725</v>
+        <v>132934566</v>
       </c>
       <c r="B34" t="n">
-        <v>93216</v>
+        <v>91937</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3806,21 +3798,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3830,10 +3822,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521171</v>
+        <v>521207</v>
       </c>
       <c r="R34" t="n">
-        <v>7008936</v>
+        <v>7008851</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3892,32 +3884,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132934679</v>
+        <v>132934567</v>
       </c>
       <c r="B35" t="n">
-        <v>99140</v>
+        <v>91937</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3927,10 +3919,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521159</v>
+        <v>521236</v>
       </c>
       <c r="R35" t="n">
-        <v>7009071</v>
+        <v>7008806</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3963,11 +3955,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>3st bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3994,10 +3981,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132934673</v>
+        <v>132934701</v>
       </c>
       <c r="B36" t="n">
-        <v>99140</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4005,21 +3992,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4016,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521159</v>
+        <v>521075</v>
       </c>
       <c r="R36" t="n">
-        <v>7008976</v>
+        <v>7009147</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4059,17 +4046,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>12st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4096,45 +4078,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132934541</v>
+        <v>132934702</v>
       </c>
       <c r="B37" t="n">
-        <v>79091</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521045</v>
+        <v>521069</v>
       </c>
       <c r="R37" t="n">
-        <v>7008824</v>
+        <v>7009122</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4193,32 +4175,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132934642</v>
+        <v>132934703</v>
       </c>
       <c r="B38" t="n">
-        <v>80439</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4228,10 +4210,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521241</v>
+        <v>521068</v>
       </c>
       <c r="R38" t="n">
-        <v>7008806</v>
+        <v>7009094</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4290,32 +4272,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132934606</v>
+        <v>132934704</v>
       </c>
       <c r="B39" t="n">
-        <v>80343</v>
+        <v>79373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4325,10 +4307,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>521194</v>
+        <v>521125</v>
       </c>
       <c r="R39" t="n">
-        <v>7008902</v>
+        <v>7009007</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4387,32 +4369,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132934614</v>
+        <v>132934709</v>
       </c>
       <c r="B40" t="n">
-        <v>75417</v>
+        <v>79373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1460</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4422,10 +4404,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>521110</v>
+        <v>521086</v>
       </c>
       <c r="R40" t="n">
-        <v>7009041</v>
+        <v>7009170</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4484,32 +4466,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132934585</v>
+        <v>132934616</v>
       </c>
       <c r="B41" t="n">
-        <v>91928</v>
+        <v>79397</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6434</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4519,10 +4501,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521047</v>
+        <v>521117</v>
       </c>
       <c r="R41" t="n">
-        <v>7009108</v>
+        <v>7009023</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4581,10 +4563,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132934510</v>
+        <v>132934562</v>
       </c>
       <c r="B42" t="n">
-        <v>91928</v>
+        <v>83358</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4592,34 +4574,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521051</v>
+        <v>521180</v>
       </c>
       <c r="R42" t="n">
-        <v>7009102</v>
+        <v>7009050</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4678,10 +4660,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132934704</v>
+        <v>132934541</v>
       </c>
       <c r="B43" t="n">
-        <v>79334</v>
+        <v>79130</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4689,34 +4671,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521125</v>
+        <v>521045</v>
       </c>
       <c r="R43" t="n">
-        <v>7009007</v>
+        <v>7008824</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4775,45 +4757,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132934566</v>
+        <v>132934542</v>
       </c>
       <c r="B44" t="n">
-        <v>91891</v>
+        <v>79130</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521207</v>
+        <v>520944</v>
       </c>
       <c r="R44" t="n">
-        <v>7008851</v>
+        <v>7008802</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4872,10 +4854,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132934627</v>
+        <v>132934544</v>
       </c>
       <c r="B45" t="n">
-        <v>79092</v>
+        <v>79130</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4883,34 +4865,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>521207</v>
+        <v>521030</v>
       </c>
       <c r="R45" t="n">
-        <v>7008846</v>
+        <v>7008914</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4972,7 +4954,7 @@
         <v>132934545</v>
       </c>
       <c r="B46" t="n">
-        <v>79091</v>
+        <v>79130</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5066,10 +5048,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132934570</v>
+        <v>132934546</v>
       </c>
       <c r="B47" t="n">
-        <v>79953</v>
+        <v>79130</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5077,34 +5059,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520978</v>
+        <v>521102</v>
       </c>
       <c r="R47" t="n">
-        <v>7008880</v>
+        <v>7009124</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5163,10 +5145,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132934506</v>
+        <v>132934547</v>
       </c>
       <c r="B48" t="n">
-        <v>97380</v>
+        <v>79130</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5174,21 +5156,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5198,10 +5180,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>521125</v>
+        <v>521140</v>
       </c>
       <c r="R48" t="n">
-        <v>7009003</v>
+        <v>7008998</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5260,10 +5242,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132934619</v>
+        <v>132934548</v>
       </c>
       <c r="B49" t="n">
-        <v>91981</v>
+        <v>79130</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5271,34 +5253,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>521192</v>
+        <v>521142</v>
       </c>
       <c r="R49" t="n">
-        <v>7008832</v>
+        <v>7008938</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5357,45 +5339,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132934565</v>
+        <v>132934549</v>
       </c>
       <c r="B50" t="n">
-        <v>91891</v>
+        <v>79130</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>521199</v>
+        <v>521186</v>
       </c>
       <c r="R50" t="n">
-        <v>7008837</v>
+        <v>7008836</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5454,45 +5436,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132934610</v>
+        <v>132934550</v>
       </c>
       <c r="B51" t="n">
-        <v>80343</v>
+        <v>79130</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>521212</v>
+        <v>521248</v>
       </c>
       <c r="R51" t="n">
-        <v>7009093</v>
+        <v>7008806</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5551,10 +5533,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132934562</v>
+        <v>132934551</v>
       </c>
       <c r="B52" t="n">
-        <v>83319</v>
+        <v>79130</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5562,34 +5544,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>521180</v>
+        <v>521211</v>
       </c>
       <c r="R52" t="n">
-        <v>7009050</v>
+        <v>7008824</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5648,32 +5630,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132934730</v>
+        <v>132934662</v>
       </c>
       <c r="B53" t="n">
-        <v>101348</v>
+        <v>79130</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5683,10 +5665,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521062</v>
+        <v>520935</v>
       </c>
       <c r="R53" t="n">
-        <v>7009070</v>
+        <v>7008801</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5745,10 +5727,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132934631</v>
+        <v>132934664</v>
       </c>
       <c r="B54" t="n">
-        <v>79092</v>
+        <v>79130</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5756,21 +5738,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5780,10 +5762,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>521241</v>
+        <v>521186</v>
       </c>
       <c r="R54" t="n">
-        <v>7008805</v>
+        <v>7008837</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5842,10 +5824,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132934647</v>
+        <v>132934666</v>
       </c>
       <c r="B55" t="n">
-        <v>78346</v>
+        <v>79130</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5853,21 +5835,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228579</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5877,10 +5859,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>521237</v>
+        <v>521215</v>
       </c>
       <c r="R55" t="n">
-        <v>7008806</v>
+        <v>7008844</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5939,10 +5921,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132934640</v>
+        <v>132934667</v>
       </c>
       <c r="B56" t="n">
-        <v>80439</v>
+        <v>79130</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5950,21 +5932,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5974,10 +5956,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>521171</v>
+        <v>521180</v>
       </c>
       <c r="R56" t="n">
-        <v>7009092</v>
+        <v>7008814</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6036,10 +6018,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132934544</v>
+        <v>132934507</v>
       </c>
       <c r="B57" t="n">
-        <v>79091</v>
+        <v>79992</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6047,21 +6029,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6071,10 +6053,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>521030</v>
+        <v>521249</v>
       </c>
       <c r="R57" t="n">
-        <v>7008914</v>
+        <v>7008816</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6133,10 +6115,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132934615</v>
+        <v>132934569</v>
       </c>
       <c r="B58" t="n">
-        <v>75417</v>
+        <v>79992</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6144,21 +6126,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1460</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6168,10 +6150,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521138</v>
+        <v>521055</v>
       </c>
       <c r="R58" t="n">
-        <v>7008969</v>
+        <v>7008912</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6230,45 +6212,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132934558</v>
+        <v>132934570</v>
       </c>
       <c r="B59" t="n">
-        <v>92202</v>
+        <v>79992</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>521052</v>
+        <v>520978</v>
       </c>
       <c r="R59" t="n">
-        <v>7008845</v>
+        <v>7008880</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6327,32 +6309,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132934675</v>
+        <v>132934571</v>
       </c>
       <c r="B60" t="n">
-        <v>99140</v>
+        <v>79992</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6362,10 +6344,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>521056</v>
+        <v>521202</v>
       </c>
       <c r="R60" t="n">
-        <v>7009075</v>
+        <v>7008859</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6398,11 +6380,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>8st bladrosetter</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6429,10 +6406,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132934626</v>
+        <v>132934572</v>
       </c>
       <c r="B61" t="n">
-        <v>79092</v>
+        <v>79992</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6440,21 +6417,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6464,10 +6441,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>521121</v>
+        <v>521188</v>
       </c>
       <c r="R61" t="n">
-        <v>7009153</v>
+        <v>7008858</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6526,10 +6503,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132934532</v>
+        <v>132934573</v>
       </c>
       <c r="B62" t="n">
-        <v>79092</v>
+        <v>79992</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6537,34 +6514,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>521183</v>
+        <v>521194</v>
       </c>
       <c r="R62" t="n">
-        <v>7008817</v>
+        <v>7008852</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6623,10 +6600,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132934709</v>
+        <v>132934574</v>
       </c>
       <c r="B63" t="n">
-        <v>79334</v>
+        <v>79992</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6634,21 +6611,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6658,10 +6635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>521086</v>
+        <v>521228</v>
       </c>
       <c r="R63" t="n">
-        <v>7009170</v>
+        <v>7008805</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6720,10 +6697,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132934633</v>
+        <v>132934575</v>
       </c>
       <c r="B64" t="n">
-        <v>80439</v>
+        <v>79992</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6731,21 +6708,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6755,10 +6732,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>521131</v>
+        <v>521035</v>
       </c>
       <c r="R64" t="n">
-        <v>7009066</v>
+        <v>7008820</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6785,12 +6762,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6817,32 +6794,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132934602</v>
+        <v>132934576</v>
       </c>
       <c r="B65" t="n">
-        <v>80343</v>
+        <v>79992</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6852,10 +6829,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>521128</v>
+        <v>521217</v>
       </c>
       <c r="R65" t="n">
-        <v>7009053</v>
+        <v>7008823</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6882,12 +6859,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6914,10 +6891,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132934729</v>
+        <v>132934577</v>
       </c>
       <c r="B66" t="n">
-        <v>83311</v>
+        <v>79992</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6925,21 +6902,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6949,10 +6926,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521143</v>
+        <v>521178</v>
       </c>
       <c r="R66" t="n">
-        <v>7008975</v>
+        <v>7008813</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7011,10 +6988,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132934724</v>
+        <v>132934514</v>
       </c>
       <c r="B67" t="n">
-        <v>93216</v>
+        <v>80382</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7022,34 +6999,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521161</v>
+        <v>521008</v>
       </c>
       <c r="R67" t="n">
-        <v>7008948</v>
+        <v>7008813</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7076,12 +7053,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7108,45 +7085,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934660</v>
+        <v>132934515</v>
       </c>
       <c r="B68" t="n">
-        <v>91856</v>
+        <v>80382</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2013</v>
+        <v>6456</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521085</v>
+        <v>521069</v>
       </c>
       <c r="R68" t="n">
-        <v>7008964</v>
+        <v>7009143</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7179,11 +7156,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Mikroskoperad</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7210,45 +7182,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132934670</v>
+        <v>132934516</v>
       </c>
       <c r="B69" t="n">
-        <v>99140</v>
+        <v>80382</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>521175</v>
+        <v>521131</v>
       </c>
       <c r="R69" t="n">
-        <v>7009071</v>
+        <v>7008987</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7275,17 +7247,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>4st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7312,45 +7279,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132934522</v>
+        <v>132934602</v>
       </c>
       <c r="B70" t="n">
-        <v>79092</v>
+        <v>80382</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520949</v>
+        <v>521128</v>
       </c>
       <c r="R70" t="n">
-        <v>7008801</v>
+        <v>7009053</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7377,12 +7344,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7409,45 +7376,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132934542</v>
+        <v>132934604</v>
       </c>
       <c r="B71" t="n">
-        <v>79091</v>
+        <v>80382</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520944</v>
+        <v>521079</v>
       </c>
       <c r="R71" t="n">
-        <v>7008802</v>
+        <v>7008865</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7506,32 +7473,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132934646</v>
+        <v>132934605</v>
       </c>
       <c r="B72" t="n">
-        <v>80439</v>
+        <v>80382</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7541,10 +7508,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>521053</v>
+        <v>521000</v>
       </c>
       <c r="R72" t="n">
-        <v>7008982</v>
+        <v>7008814</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7603,32 +7570,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132934618</v>
+        <v>132934606</v>
       </c>
       <c r="B73" t="n">
-        <v>91981</v>
+        <v>80382</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>6456</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7638,10 +7605,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520999</v>
+        <v>521194</v>
       </c>
       <c r="R73" t="n">
-        <v>7008967</v>
+        <v>7008902</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7700,45 +7667,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132934526</v>
+        <v>132934607</v>
       </c>
       <c r="B74" t="n">
-        <v>79092</v>
+        <v>80382</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>521142</v>
+        <v>521198</v>
       </c>
       <c r="R74" t="n">
-        <v>7008938</v>
+        <v>7008890</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7797,32 +7764,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132934702</v>
+        <v>132934609</v>
       </c>
       <c r="B75" t="n">
-        <v>79334</v>
+        <v>80382</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7832,10 +7799,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>521069</v>
+        <v>521140</v>
       </c>
       <c r="R75" t="n">
-        <v>7009122</v>
+        <v>7009061</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7862,12 +7829,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7894,32 +7861,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132934671</v>
+        <v>132934610</v>
       </c>
       <c r="B76" t="n">
-        <v>99140</v>
+        <v>80382</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7929,10 +7896,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>521125</v>
+        <v>521212</v>
       </c>
       <c r="R76" t="n">
-        <v>7009063</v>
+        <v>7009093</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7959,17 +7926,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -7996,32 +7958,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132934582</v>
+        <v>132934611</v>
       </c>
       <c r="B77" t="n">
-        <v>79924</v>
+        <v>80382</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>6456</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8031,10 +7993,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>521102</v>
+        <v>521191</v>
       </c>
       <c r="R77" t="n">
-        <v>7009031</v>
+        <v>7008824</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8093,10 +8055,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132934528</v>
+        <v>104846619</v>
       </c>
       <c r="B78" t="n">
-        <v>79092</v>
+        <v>80432</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8104,37 +8066,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>Öberget, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>521188</v>
+        <v>521036</v>
       </c>
       <c r="R78" t="n">
-        <v>7008858</v>
+        <v>7009132</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8158,12 +8120,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2022-09-19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2022-09-19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8178,22 +8140,26 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132934629</v>
+        <v>132934533</v>
       </c>
       <c r="B79" t="n">
-        <v>79092</v>
+        <v>80488</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8201,34 +8167,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>521115</v>
+        <v>521124</v>
       </c>
       <c r="R79" t="n">
-        <v>7009027</v>
+        <v>7008989</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8261,6 +8227,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På låga av sälg</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8287,10 +8258,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132934575</v>
+        <v>132934534</v>
       </c>
       <c r="B80" t="n">
-        <v>79953</v>
+        <v>80488</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8298,34 +8269,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>521035</v>
+        <v>521190</v>
       </c>
       <c r="R80" t="n">
-        <v>7008820</v>
+        <v>7008892</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8358,6 +8329,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På sälghögstubbe</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8384,10 +8360,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132934703</v>
+        <v>132934633</v>
       </c>
       <c r="B81" t="n">
-        <v>79334</v>
+        <v>80488</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8395,21 +8371,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8419,10 +8395,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>521068</v>
+        <v>521131</v>
       </c>
       <c r="R81" t="n">
-        <v>7009094</v>
+        <v>7009066</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8449,12 +8425,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8481,10 +8457,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132934599</v>
+        <v>132934634</v>
       </c>
       <c r="B82" t="n">
-        <v>80305</v>
+        <v>80488</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8492,21 +8468,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8516,10 +8492,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>521196</v>
+        <v>521157</v>
       </c>
       <c r="R82" t="n">
-        <v>7008906</v>
+        <v>7008985</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8546,12 +8522,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8560,7 +8536,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8579,10 +8554,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132934550</v>
+        <v>132934640</v>
       </c>
       <c r="B83" t="n">
-        <v>79091</v>
+        <v>80488</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8590,34 +8565,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>521248</v>
+        <v>521171</v>
       </c>
       <c r="R83" t="n">
-        <v>7008806</v>
+        <v>7009092</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8676,32 +8651,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132934611</v>
+        <v>132934641</v>
       </c>
       <c r="B84" t="n">
-        <v>80343</v>
+        <v>80488</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8711,10 +8686,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>521191</v>
+        <v>521052</v>
       </c>
       <c r="R84" t="n">
-        <v>7008824</v>
+        <v>7009135</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8773,10 +8748,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934641</v>
+        <v>132934642</v>
       </c>
       <c r="B85" t="n">
-        <v>80439</v>
+        <v>80488</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8808,10 +8783,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521052</v>
+        <v>521241</v>
       </c>
       <c r="R85" t="n">
-        <v>7009135</v>
+        <v>7008806</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8870,32 +8845,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132934604</v>
+        <v>132934646</v>
       </c>
       <c r="B86" t="n">
-        <v>80343</v>
+        <v>80488</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8905,10 +8880,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>521079</v>
+        <v>521053</v>
       </c>
       <c r="R86" t="n">
-        <v>7008865</v>
+        <v>7008982</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8967,45 +8942,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132934548</v>
+        <v>132934726</v>
       </c>
       <c r="B87" t="n">
-        <v>79091</v>
+        <v>80499</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>521142</v>
+        <v>521240</v>
       </c>
       <c r="R87" t="n">
-        <v>7008938</v>
+        <v>7008810</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9064,10 +9039,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132934514</v>
+        <v>132934728</v>
       </c>
       <c r="B88" t="n">
-        <v>80343</v>
+        <v>80499</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9075,34 +9050,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>521008</v>
+        <v>521142</v>
       </c>
       <c r="R88" t="n">
-        <v>7008813</v>
+        <v>7008987</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9161,10 +9136,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132934701</v>
+        <v>132934590</v>
       </c>
       <c r="B89" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9172,21 +9147,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9196,10 +9171,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>521075</v>
+        <v>521100</v>
       </c>
       <c r="R89" t="n">
-        <v>7009147</v>
+        <v>7009149</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9232,6 +9207,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9258,32 +9238,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132934674</v>
+        <v>132934591</v>
       </c>
       <c r="B90" t="n">
-        <v>99140</v>
+        <v>57975</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9293,10 +9273,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>521168</v>
+        <v>521094</v>
       </c>
       <c r="R90" t="n">
-        <v>7009069</v>
+        <v>7009140</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9333,7 +9313,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>4st bladrosetter</t>
+          <t>Färska och gamla ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9360,45 +9340,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934552</v>
+        <v>132934592</v>
       </c>
       <c r="B91" t="n">
-        <v>99140</v>
+        <v>57975</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521056</v>
+        <v>521070</v>
       </c>
       <c r="R91" t="n">
-        <v>7009135</v>
+        <v>7009153</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9435,7 +9415,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Över 40 plantor</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9462,10 +9442,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934529</v>
+        <v>132934593</v>
       </c>
       <c r="B92" t="n">
-        <v>79092</v>
+        <v>57975</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9473,34 +9453,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521186</v>
+        <v>521205</v>
       </c>
       <c r="R92" t="n">
-        <v>7008836</v>
+        <v>7008831</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9533,6 +9513,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9559,32 +9544,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934616</v>
+        <v>132934594</v>
       </c>
       <c r="B93" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9594,10 +9579,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521117</v>
+        <v>521208</v>
       </c>
       <c r="R93" t="n">
-        <v>7009023</v>
+        <v>7008822</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9630,6 +9615,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9656,32 +9646,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934678</v>
+        <v>132934680</v>
       </c>
       <c r="B94" t="n">
-        <v>99140</v>
+        <v>57153</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9691,10 +9681,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521234</v>
+        <v>521010</v>
       </c>
       <c r="R94" t="n">
-        <v>7009077</v>
+        <v>7008813</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9731,7 +9721,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>5st bladrosetter</t>
+          <t>1st födosökande</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9758,45 +9748,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132934530</v>
+        <v>132934595</v>
       </c>
       <c r="B95" t="n">
-        <v>79092</v>
+        <v>58131</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>103023</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521248</v>
+        <v>521204</v>
       </c>
       <c r="R95" t="n">
-        <v>7008805</v>
+        <v>7008854</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9829,6 +9819,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>1st födosökande</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9855,45 +9850,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132934586</v>
+        <v>132934552</v>
       </c>
       <c r="B96" t="n">
-        <v>91928</v>
+        <v>99195</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521068</v>
+        <v>521056</v>
       </c>
       <c r="R96" t="n">
-        <v>7009176</v>
+        <v>7009135</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9926,6 +9921,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Över 40 plantor</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -9952,32 +9952,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132934681</v>
+        <v>132934670</v>
       </c>
       <c r="B97" t="n">
-        <v>106268</v>
+        <v>99195</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>521191</v>
+        <v>521175</v>
       </c>
       <c r="R97" t="n">
-        <v>7008908</v>
+        <v>7009071</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10017,12 +10017,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10049,32 +10054,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132934630</v>
+        <v>132934671</v>
       </c>
       <c r="B98" t="n">
-        <v>79092</v>
+        <v>99195</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10084,10 +10089,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>521203</v>
+        <v>521125</v>
       </c>
       <c r="R98" t="n">
-        <v>7008836</v>
+        <v>7009063</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10114,12 +10119,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10146,32 +10156,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132934571</v>
+        <v>132934673</v>
       </c>
       <c r="B99" t="n">
-        <v>79953</v>
+        <v>99195</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10181,10 +10191,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>521202</v>
+        <v>521159</v>
       </c>
       <c r="R99" t="n">
-        <v>7008859</v>
+        <v>7008976</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10211,12 +10221,17 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>12st bladrosetter</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10243,32 +10258,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132934605</v>
+        <v>132934674</v>
       </c>
       <c r="B100" t="n">
-        <v>80343</v>
+        <v>99195</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10278,10 +10293,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>521000</v>
+        <v>521168</v>
       </c>
       <c r="R100" t="n">
-        <v>7008814</v>
+        <v>7009069</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10314,6 +10329,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>4st bladrosetter</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10340,32 +10360,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132934728</v>
+        <v>132934675</v>
       </c>
       <c r="B101" t="n">
-        <v>80474</v>
+        <v>99195</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10375,10 +10395,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>521142</v>
+        <v>521056</v>
       </c>
       <c r="R101" t="n">
-        <v>7008987</v>
+        <v>7009075</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10411,6 +10431,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>8st bladrosetter</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10437,10 +10462,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132934677</v>
+        <v>132934676</v>
       </c>
       <c r="B102" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10472,10 +10497,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>521070</v>
+        <v>521068</v>
       </c>
       <c r="R102" t="n">
-        <v>7009057</v>
+        <v>7009134</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10512,7 +10537,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>&gt;30 bladrosetter</t>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10539,45 +10564,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132934533</v>
+        <v>132934677</v>
       </c>
       <c r="B103" t="n">
-        <v>80439</v>
+        <v>99195</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>521124</v>
+        <v>521070</v>
       </c>
       <c r="R103" t="n">
-        <v>7008989</v>
+        <v>7009057</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10614,7 +10639,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>På låga av sälg</t>
+          <t>&gt;30 bladrosetter</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10641,45 +10666,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132934551</v>
+        <v>132934678</v>
       </c>
       <c r="B104" t="n">
-        <v>79091</v>
+        <v>99195</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>521211</v>
+        <v>521234</v>
       </c>
       <c r="R104" t="n">
-        <v>7008824</v>
+        <v>7009077</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10712,6 +10737,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10738,32 +10768,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132934600</v>
+        <v>132934679</v>
       </c>
       <c r="B105" t="n">
-        <v>80305</v>
+        <v>99195</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10773,10 +10803,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>521188</v>
+        <v>521159</v>
       </c>
       <c r="R105" t="n">
-        <v>7008835</v>
+        <v>7009071</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10811,13 +10841,17 @@
           <t>2026-04-25</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>3st bladrosetter</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -10836,45 +10870,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132934513</v>
+        <v>132934681</v>
       </c>
       <c r="B106" t="n">
-        <v>80305</v>
+        <v>106324</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>388</v>
+        <v>221144</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>521186</v>
+        <v>521191</v>
       </c>
       <c r="R106" t="n">
-        <v>7009049</v>
+        <v>7008908</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10933,32 +10967,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132934662</v>
+        <v>132934730</v>
       </c>
       <c r="B107" t="n">
-        <v>79091</v>
+        <v>101403</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>222498</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10968,10 +11002,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>520935</v>
+        <v>521062</v>
       </c>
       <c r="R107" t="n">
-        <v>7008801</v>
+        <v>7009070</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11033,7 +11067,7 @@
         <v>132934535</v>
       </c>
       <c r="B108" t="n">
-        <v>78346</v>
+        <v>78382</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11127,45 +11161,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132934516</v>
+        <v>132934647</v>
       </c>
       <c r="B109" t="n">
-        <v>80343</v>
+        <v>78382</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6456</v>
+        <v>228579</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>521131</v>
+        <v>521237</v>
       </c>
       <c r="R109" t="n">
-        <v>7008987</v>
+        <v>7008806</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11224,45 +11258,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132934609</v>
+        <v>132934521</v>
       </c>
       <c r="B110" t="n">
-        <v>80343</v>
+        <v>79131</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>521140</v>
+        <v>521045</v>
       </c>
       <c r="R110" t="n">
-        <v>7009061</v>
+        <v>7008824</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11289,12 +11323,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11321,45 +11355,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132934726</v>
+        <v>132934522</v>
       </c>
       <c r="B111" t="n">
-        <v>80474</v>
+        <v>79131</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>521240</v>
+        <v>520949</v>
       </c>
       <c r="R111" t="n">
-        <v>7008810</v>
+        <v>7008801</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11418,45 +11452,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132934691</v>
+        <v>132934523</v>
       </c>
       <c r="B112" t="n">
-        <v>92102</v>
+        <v>79131</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>521092</v>
+        <v>521025</v>
       </c>
       <c r="R112" t="n">
-        <v>7009170</v>
+        <v>7008930</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11515,10 +11549,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132934587</v>
+        <v>132934524</v>
       </c>
       <c r="B113" t="n">
-        <v>91928</v>
+        <v>79131</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11526,34 +11560,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>521077</v>
+        <v>521010</v>
       </c>
       <c r="R113" t="n">
-        <v>7009118</v>
+        <v>7008924</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11612,32 +11646,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132934554</v>
+        <v>132934525</v>
       </c>
       <c r="B114" t="n">
-        <v>92102</v>
+        <v>79131</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11647,10 +11681,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>521105</v>
+        <v>521152</v>
       </c>
       <c r="R114" t="n">
-        <v>7009010</v>
+        <v>7008946</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11709,32 +11743,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132934555</v>
+        <v>132934526</v>
       </c>
       <c r="B115" t="n">
-        <v>92102</v>
+        <v>79131</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11744,10 +11778,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>521211</v>
+        <v>521142</v>
       </c>
       <c r="R115" t="n">
-        <v>7008839</v>
+        <v>7008938</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11806,10 +11840,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132934524</v>
+        <v>132934528</v>
       </c>
       <c r="B116" t="n">
-        <v>79092</v>
+        <v>79131</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11841,10 +11875,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>521010</v>
+        <v>521188</v>
       </c>
       <c r="R116" t="n">
-        <v>7008924</v>
+        <v>7008858</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11903,10 +11937,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132934531</v>
+        <v>132934529</v>
       </c>
       <c r="B117" t="n">
-        <v>79092</v>
+        <v>79131</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11938,10 +11972,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>521212</v>
+        <v>521186</v>
       </c>
       <c r="R117" t="n">
-        <v>7008824</v>
+        <v>7008836</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12000,10 +12034,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132934592</v>
+        <v>132934530</v>
       </c>
       <c r="B118" t="n">
-        <v>57975</v>
+        <v>79131</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12011,34 +12045,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>521070</v>
+        <v>521248</v>
       </c>
       <c r="R118" t="n">
-        <v>7009153</v>
+        <v>7008805</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12071,11 +12105,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12102,10 +12131,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132934594</v>
+        <v>132934531</v>
       </c>
       <c r="B119" t="n">
-        <v>57975</v>
+        <v>79131</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12113,34 +12142,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>521208</v>
+        <v>521212</v>
       </c>
       <c r="R119" t="n">
-        <v>7008822</v>
+        <v>7008824</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12173,11 +12202,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12204,10 +12228,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>132934590</v>
+        <v>132934532</v>
       </c>
       <c r="B120" t="n">
-        <v>57975</v>
+        <v>79131</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12215,34 +12239,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>521100</v>
+        <v>521183</v>
       </c>
       <c r="R120" t="n">
-        <v>7009149</v>
+        <v>7008817</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12275,11 +12299,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12306,10 +12325,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132934591</v>
+        <v>132934625</v>
       </c>
       <c r="B121" t="n">
-        <v>57975</v>
+        <v>79131</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12317,21 +12336,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12341,10 +12360,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>521094</v>
+        <v>521212</v>
       </c>
       <c r="R121" t="n">
-        <v>7009140</v>
+        <v>7009056</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12377,11 +12396,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Färska och gamla ringhack på tall</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12408,10 +12422,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>132934593</v>
+        <v>132934626</v>
       </c>
       <c r="B122" t="n">
-        <v>57975</v>
+        <v>79131</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12419,21 +12433,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12443,10 +12457,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>521205</v>
+        <v>521121</v>
       </c>
       <c r="R122" t="n">
-        <v>7008831</v>
+        <v>7009153</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12481,11 +12495,6 @@
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -12507,6 +12516,986 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>132934627</v>
+      </c>
+      <c r="B123" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>AA, Jmt</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>521207</v>
+      </c>
+      <c r="R123" t="n">
+        <v>7008846</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>132934628</v>
+      </c>
+      <c r="B124" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>AA, Jmt</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>521179</v>
+      </c>
+      <c r="R124" t="n">
+        <v>7008825</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>132934629</v>
+      </c>
+      <c r="B125" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>AA, Jmt</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>521115</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7009027</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>132934630</v>
+      </c>
+      <c r="B126" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>AA, Jmt</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>521203</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7008836</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>132934631</v>
+      </c>
+      <c r="B127" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>AA, Jmt</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>521241</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7008805</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>132934582</v>
+      </c>
+      <c r="B128" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>AA, Jmt</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>521102</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7009031</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>132934583</v>
+      </c>
+      <c r="B129" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>AA, Jmt</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>521109</v>
+      </c>
+      <c r="R129" t="n">
+        <v>7009014</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>132934511</v>
+      </c>
+      <c r="B130" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>AB, Jmt</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>521016</v>
+      </c>
+      <c r="R130" t="n">
+        <v>7008910</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>132934596</v>
+      </c>
+      <c r="B131" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>AA, Jmt</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>521116</v>
+      </c>
+      <c r="R131" t="n">
+        <v>7009148</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Med soral</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>132934597</v>
+      </c>
+      <c r="B132" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>AA, Jmt</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>521085</v>
+      </c>
+      <c r="R132" t="n">
+        <v>7009041</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Med soral</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57915-2025 artfynd.xlsx
+++ b/artfynd/A 57915-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY132"/>
+  <dimension ref="A1:AZ132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934506</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934564</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934558</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934559</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934729</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934513</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934598</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1450,6 +1490,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934599</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1548,6 +1593,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934600</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1645,6 +1695,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934601</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1742,6 +1797,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934517</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1839,6 +1899,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934613</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1936,6 +2001,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934510</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2033,6 +2103,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934585</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2130,6 +2205,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934586</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2227,6 +2307,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934587</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2324,6 +2409,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934588</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2421,6 +2511,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934612</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2518,6 +2613,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934557</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2615,6 +2715,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934614</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2712,6 +2817,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934615</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2809,6 +2919,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934554</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2906,6 +3021,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934555</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3003,6 +3123,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934690</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3100,6 +3225,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934691</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3202,6 +3332,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934660</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3299,6 +3434,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934618</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3396,6 +3536,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934619</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3493,6 +3638,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934620</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3590,6 +3740,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934724</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3687,6 +3842,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934725</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3784,6 +3944,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934565</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3881,6 +4046,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934566</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3978,6 +4148,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934567</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4075,6 +4250,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934701</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4172,6 +4352,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934702</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4269,6 +4454,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934703</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4366,6 +4556,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934704</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4463,6 +4658,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934709</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4560,6 +4760,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934616</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4657,6 +4862,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934562</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4754,6 +4964,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934541</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4851,6 +5066,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934542</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4948,6 +5168,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934544</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5045,6 +5270,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934545</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5142,6 +5372,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934546</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5239,6 +5474,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934547</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5336,6 +5576,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934548</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5433,6 +5678,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934549</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5530,6 +5780,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934550</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5627,6 +5882,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934551</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5724,6 +5984,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934662</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5821,6 +6086,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934664</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5918,6 +6188,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934666</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6015,6 +6290,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934667</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6112,6 +6392,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934507</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6209,6 +6494,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934569</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6306,6 +6596,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934570</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6403,6 +6698,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934571</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6500,6 +6800,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934572</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6597,6 +6902,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934573</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6694,6 +7004,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934574</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6791,6 +7106,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934575</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6888,6 +7208,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934576</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6985,6 +7310,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934577</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7082,6 +7412,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934514</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7179,6 +7514,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934515</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7276,6 +7616,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934516</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7373,6 +7718,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934602</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7470,6 +7820,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934604</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7567,6 +7922,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934605</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7664,6 +8024,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934606</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7761,6 +8126,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934607</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7858,6 +8228,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934609</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7955,6 +8330,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934610</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8052,6 +8432,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934611</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8153,6 +8538,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104846619</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8255,6 +8645,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934533</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8357,6 +8752,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934534</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8454,6 +8854,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934633</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8551,6 +8956,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934634</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8648,6 +9058,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934640</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8745,6 +9160,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934641</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8842,6 +9262,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934642</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8939,6 +9364,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934646</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9036,6 +9466,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934726</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9133,6 +9568,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934728</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9235,6 +9675,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934590</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9337,6 +9782,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934591</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9439,6 +9889,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934592</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9541,6 +9996,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934593</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9643,6 +10103,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934594</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9745,6 +10210,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934680</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9847,6 +10317,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934595</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9949,6 +10424,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934552</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10051,6 +10531,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934670</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10153,6 +10638,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934671</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10255,6 +10745,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934673</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10357,6 +10852,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934674</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10459,6 +10959,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934675</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10561,6 +11066,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934676</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10663,6 +11173,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934677</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10765,6 +11280,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934678</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10867,6 +11387,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934679</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10964,6 +11489,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934681</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11061,6 +11591,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934730</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11158,6 +11693,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934535</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11255,6 +11795,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934647</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11352,6 +11897,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934521</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11449,6 +11999,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934522</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11546,6 +12101,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934523</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11643,6 +12203,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934524</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11740,6 +12305,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934525</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11837,6 +12407,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934526</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11934,6 +12509,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934528</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12031,6 +12611,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934529</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12128,6 +12713,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934530</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12225,6 +12815,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934531</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12322,6 +12917,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934532</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12419,6 +13019,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934625</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12516,6 +13121,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934626</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12613,6 +13223,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934627</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12710,6 +13325,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934628</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12807,6 +13427,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934629</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12904,6 +13529,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934630</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13001,6 +13631,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934631</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13098,6 +13733,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934582</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13195,6 +13835,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934583</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13292,6 +13937,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934511</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13394,6 +14044,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934596</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13496,8 +14151,146 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934597</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>